--- a/test/published_reports/pmq_client_dashboard.xlsx
+++ b/test/published_reports/pmq_client_dashboard.xlsx
@@ -17,6 +17,10 @@
     <sheet name="executive_roster" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="jecrc_batch_performance" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="galgotias_batch_performance" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="college_batch_weekly_performance" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="college_track_weekly_performance" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="college_weekly_signal_counts" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="college_batch_weekly_attendance" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,6 +620,9 @@
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -635,7 +642,204 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>JECRC Batches</a:t>
+                  <a:t>Batch</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="100"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Average Attendance Percentage</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>JECRC Batch-wise Performance Bucket Mix</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'jecrc_batch_performance'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="10B981"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'jecrc_batch_performance'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'jecrc_batch_performance'!$E$2:$E$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'jecrc_batch_performance'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="7C3AED"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'jecrc_batch_performance'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'jecrc_batch_performance'!$F$2:$F$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'jecrc_batch_performance'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="0EA5E9"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'jecrc_batch_performance'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'jecrc_batch_performance'!$G$2:$G$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'jecrc_batch_performance'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EF4444"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'jecrc_batch_performance'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'jecrc_batch_performance'!$H$2:$H$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Student Count</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -662,7 +866,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Attendance %</a:t>
+                  <a:t>Batch</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -674,7 +878,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -682,9 +886,8 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -695,23 +898,21 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>JECRC Batch-wise Average Overall Performance</a:t>
+              <a:t>JECRC Week-on-Week Attendance Progress</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
+      <lineChart>
+        <grouping val="standard"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'jecrc_batch_performance'!D1</f>
+              <f>'jecrc_batch_performance'!U2</f>
             </strRef>
           </tx>
           <spPr>
@@ -719,76 +920,156 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <dPt>
-            <idx val="0"/>
+          <marker>
+            <symbol val="none"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="1D4ED8"/>
-              </a:solidFill>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
-          </dPt>
-          <dPt>
-            <idx val="1"/>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'jecrc_batch_performance'!$T$3:$T$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'jecrc_batch_performance'!$U$3:$U$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'jecrc_batch_performance'!V2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="7C3AED"/>
-              </a:solidFill>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
-          </dPt>
-          <dPt>
-            <idx val="2"/>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'jecrc_batch_performance'!$T$3:$T$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'jecrc_batch_performance'!$V$3:$V$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'jecrc_batch_performance'!W2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="0EA5E9"/>
-              </a:solidFill>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
-          </dPt>
-          <dPt>
-            <idx val="3"/>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'jecrc_batch_performance'!$T$3:$T$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'jecrc_batch_performance'!$W$3:$W$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'jecrc_batch_performance'!X2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="10B981"/>
-              </a:solidFill>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
-          </dPt>
-          <dPt>
-            <idx val="4"/>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'jecrc_batch_performance'!$T$3:$T$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'jecrc_batch_performance'!$X$3:$X$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'jecrc_batch_performance'!Y2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="F59E0B"/>
-              </a:solidFill>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
-          </dPt>
+          </marker>
           <cat>
             <numRef>
-              <f>'jecrc_batch_performance'!$A$2:$A$6</f>
+              <f>'jecrc_batch_performance'!$T$3:$T$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'jecrc_batch_performance'!$D$2:$D$6</f>
+              <f>'jecrc_batch_performance'!$Y$3:$Y$25</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
-      </barChart>
+      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -804,7 +1085,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>JECRC Batches</a:t>
+                  <a:t>Week</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -819,6 +1100,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="100"/>
+          <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -831,7 +1114,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Overall Performance Score</a:t>
+                  <a:t>Average Attendance Percentage</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -843,7 +1126,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -851,7 +1134,127 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>JECRC Week-on-Week Performance Progress</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'jecrc_batch_performance'!U24</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'jecrc_batch_performance'!$T$25:$T$31</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'jecrc_batch_performance'!$U$25:$U$31</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Week</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="100"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Average Score</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
@@ -944,6 +1347,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="100"/>
+          <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -976,7 +1381,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="11"/>
   <chart>
@@ -1069,6 +1474,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="100"/>
+          <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -1132,12 +1539,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3960000" cy="2700000"/>
+    <ext cx="5040000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1154,12 +1561,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3960000" cy="2700000"/>
+    <ext cx="5400000" cy="3420000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1169,6 +1576,50 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2215,7 +2666,6 @@
       <c r="C42" s="30" t="inlineStr">
         <is>
           <t>3702040 - Shivangi Rajput
-5027213 - daksh sharma
 6183978 - Saksham Tapadia
 6206803 - Shivam Dhanuka
 6206892 - Aastha bilochi
@@ -2276,18 +2726,19 @@
 6398773 - Arjun Pal
 6399051 - Shivendera Pratap Singh
 6400724 - kumar jaywardhan
+6400859 - Shabbu Parveen
 6401087 - Shruti Mishra
 6401588 - Priyanshu Kumar Sah
 6404281 - Vanshika Gangwar
 6410948 - Arnav Chauhan
 6411390 - Ankit Raj
 6412630 - Harshita Dwivedi
-6416851 - Siddharth
 6419785 - Satyam Kumar
 6422829 - Saurabh Yadav
 6430994 - Archana Maurya
 6432705 - Kushagra Chandra
 6434797 - Shivank singh chandel
+6437947 - Vivek Shrotriya
 6540727 - Indresh Mehta
 6741222 - Sidhi Bhagat
 6743195 - Priya Saini
@@ -2353,11 +2804,11 @@
         <is>
           <t>5025465 - Prince Tomer
 5026498 - Himani Singh
+5027213 - daksh sharma
 6208764 - Aditya Paliwal
-6400859 - Shabbu Parveen
 6400955 - Mrinal Mayank
-6433735 - Mohammad  Ayan
-6437947 - Vivek Shrotriya</t>
+6413621 - Aman Kumar Singh
+6433735 - Mohammad  Ayan</t>
         </is>
       </c>
       <c r="D46" s="30" t="n"/>
@@ -2409,7 +2860,7 @@
         <is>
           <t>6394706 - Prince dixit
 6413483 - Ravi Kumar Tiwari
-6413621 - Aman Kumar Singh
+6416851 - Siddharth
 6758587 - Kirti Singh
 7116051 - Aryan</t>
         </is>
@@ -2819,7 +3270,7 @@
         <v>33</v>
       </c>
       <c r="C2" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="D2" s="31" t="n">
         <v>69.90000000000001</v>
@@ -2828,6 +3279,4033 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000EA5E9"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Assigned Batch</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Assessment Week</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Average Score</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Submission Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="inlineStr"/>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="D2" s="31" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="E2" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr"/>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="E3" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr"/>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="E4" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr"/>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="E5" s="31" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr"/>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr"/>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr"/>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr"/>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr"/>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr"/>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr"/>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr"/>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr"/>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr"/>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="E15" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr"/>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007C3AED"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Track</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Assessment Week</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Average Score</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Submission Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="D2" s="31" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="E2" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="E3" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="E4" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="E5" s="31" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="E15" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="E18" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Assessment Week</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Assessments Done</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Assignments Done</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Trainer Feedback Provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="n">
+        <v>140</v>
+      </c>
+      <c r="D2" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="n">
+        <v>140</v>
+      </c>
+      <c r="D3" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="n">
+        <v>140</v>
+      </c>
+      <c r="D4" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>139</v>
+      </c>
+      <c r="D5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="31" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>140</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>81</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>47</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>140</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="31" t="n">
+        <v>23</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="D14" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="D17" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="D18" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0010B981"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D139"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Assigned Batch</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>Attendance Week</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Average Attendance %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="D2" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="n">
+        <v>99.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="n">
+        <v>97.40000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>91.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>99.09999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="n">
+        <v>82.59999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Week 10</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>Week 11</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>99.09999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="n">
+        <v>94.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Week 14</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>Week 16</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>84.09999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>Week 18</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="n">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>Week 19</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="n">
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>Week 20</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>Week 21</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>Week 22</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="n">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>Week 23</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="n">
+        <v>94.59999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>Week 25</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="n">
+        <v>89.90000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>Week 26</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="n">
+        <v>98.59999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="n">
+        <v>97.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="n">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="n">
+        <v>98.59999999999999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>Week 10</t>
+        </is>
+      </c>
+      <c r="D34" s="31" t="n">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B35" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>Week 11</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="n">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="D36" s="31" t="n">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C38" s="31" t="inlineStr">
+        <is>
+          <t>Week 14</t>
+        </is>
+      </c>
+      <c r="D38" s="31" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B39" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>Week 16</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>Week 18</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>Week 19</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B42" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>Week 20</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>Week 21</t>
+        </is>
+      </c>
+      <c r="D43" s="31" t="n">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C44" s="31" t="inlineStr">
+        <is>
+          <t>Week 22</t>
+        </is>
+      </c>
+      <c r="D44" s="31" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>Week 23</t>
+        </is>
+      </c>
+      <c r="D45" s="31" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B46" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C46" s="31" t="inlineStr">
+        <is>
+          <t>Week 25</t>
+        </is>
+      </c>
+      <c r="D46" s="31" t="n">
+        <v>97.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>Week 26</t>
+        </is>
+      </c>
+      <c r="D47" s="31" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B48" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C48" s="31" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="D48" s="31" t="n">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B49" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C49" s="31" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="D49" s="31" t="n">
+        <v>98.09999999999999</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B50" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C50" s="31" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="D50" s="31" t="n">
+        <v>98.09999999999999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C51" s="31" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="D51" s="31" t="n">
+        <v>95.40000000000001</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B52" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C52" s="31" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="D52" s="31" t="n">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B53" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C53" s="31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="D53" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B54" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C54" s="31" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="D54" s="31" t="n">
+        <v>99.40000000000001</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B55" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C55" s="31" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="D55" s="31" t="n">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B56" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C56" s="31" t="inlineStr">
+        <is>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="D56" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B57" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C57" s="31" t="inlineStr">
+        <is>
+          <t>Week 10</t>
+        </is>
+      </c>
+      <c r="D57" s="31" t="n">
+        <v>91.40000000000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B58" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C58" s="31" t="inlineStr">
+        <is>
+          <t>Week 11</t>
+        </is>
+      </c>
+      <c r="D58" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B59" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C59" s="31" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="D59" s="31" t="n">
+        <v>98.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B60" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C60" s="31" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="D60" s="31" t="n">
+        <v>97.09999999999999</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B61" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C61" s="31" t="inlineStr">
+        <is>
+          <t>Week 14</t>
+        </is>
+      </c>
+      <c r="D61" s="31" t="n">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B62" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C62" s="31" t="inlineStr">
+        <is>
+          <t>Week 16</t>
+        </is>
+      </c>
+      <c r="D62" s="31" t="n">
+        <v>88.59999999999999</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C63" s="31" t="inlineStr">
+        <is>
+          <t>Week 18</t>
+        </is>
+      </c>
+      <c r="D63" s="31" t="n">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C64" s="31" t="inlineStr">
+        <is>
+          <t>Week 19</t>
+        </is>
+      </c>
+      <c r="D64" s="31" t="n">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B65" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C65" s="31" t="inlineStr">
+        <is>
+          <t>Week 20</t>
+        </is>
+      </c>
+      <c r="D65" s="31" t="n">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B66" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C66" s="31" t="inlineStr">
+        <is>
+          <t>Week 21</t>
+        </is>
+      </c>
+      <c r="D66" s="31" t="n">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B67" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C67" s="31" t="inlineStr">
+        <is>
+          <t>Week 22</t>
+        </is>
+      </c>
+      <c r="D67" s="31" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C68" s="31" t="inlineStr">
+        <is>
+          <t>Week 23</t>
+        </is>
+      </c>
+      <c r="D68" s="31" t="n">
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C69" s="31" t="inlineStr">
+        <is>
+          <t>Week 25</t>
+        </is>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>97.09999999999999</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="C70" s="31" t="inlineStr">
+        <is>
+          <t>Week 26</t>
+        </is>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>97.09999999999999</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B71" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C71" s="31" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B72" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C72" s="31" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="D72" s="31" t="n">
+        <v>97.09999999999999</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B73" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C73" s="31" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C74" s="31" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>98.8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C75" s="31" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="D75" s="31" t="n">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B76" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C76" s="31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="D76" s="31" t="n">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C77" s="31" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>99.40000000000001</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C78" s="31" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="D78" s="31" t="n">
+        <v>97.09999999999999</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B79" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C79" s="31" t="inlineStr">
+        <is>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B80" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C80" s="31" t="inlineStr">
+        <is>
+          <t>Week 10</t>
+        </is>
+      </c>
+      <c r="D80" s="31" t="n">
+        <v>91.2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B81" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C81" s="31" t="inlineStr">
+        <is>
+          <t>Week 11</t>
+        </is>
+      </c>
+      <c r="D81" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C82" s="31" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="D82" s="31" t="n">
+        <v>98.8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B83" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C83" s="31" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="D83" s="31" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B84" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C84" s="31" t="inlineStr">
+        <is>
+          <t>Week 14</t>
+        </is>
+      </c>
+      <c r="D84" s="31" t="n">
+        <v>70.59999999999999</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B85" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C85" s="31" t="inlineStr">
+        <is>
+          <t>Week 16</t>
+        </is>
+      </c>
+      <c r="D85" s="31" t="n">
+        <v>94.09999999999999</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B86" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C86" s="31" t="inlineStr">
+        <is>
+          <t>Week 18</t>
+        </is>
+      </c>
+      <c r="D86" s="31" t="n">
+        <v>96.3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B87" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C87" s="31" t="inlineStr">
+        <is>
+          <t>Week 19</t>
+        </is>
+      </c>
+      <c r="D87" s="31" t="n">
+        <v>97.8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B88" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C88" s="31" t="inlineStr">
+        <is>
+          <t>Week 20</t>
+        </is>
+      </c>
+      <c r="D88" s="31" t="n">
+        <v>97.09999999999999</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B89" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C89" s="31" t="inlineStr">
+        <is>
+          <t>Week 21</t>
+        </is>
+      </c>
+      <c r="D89" s="31" t="n">
+        <v>88.2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B90" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C90" s="31" t="inlineStr">
+        <is>
+          <t>Week 22</t>
+        </is>
+      </c>
+      <c r="D90" s="31" t="n">
+        <v>92.59999999999999</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B91" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C91" s="31" t="inlineStr">
+        <is>
+          <t>Week 23</t>
+        </is>
+      </c>
+      <c r="D91" s="31" t="n">
+        <v>94.90000000000001</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B92" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C92" s="31" t="inlineStr">
+        <is>
+          <t>Week 25</t>
+        </is>
+      </c>
+      <c r="D92" s="31" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B93" s="31" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="C93" s="31" t="inlineStr">
+        <is>
+          <t>Week 26</t>
+        </is>
+      </c>
+      <c r="D93" s="31" t="n">
+        <v>96.09999999999999</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B94" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C94" s="31" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="D94" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B95" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C95" s="31" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="D95" s="31" t="n">
+        <v>98.59999999999999</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B96" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C96" s="31" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="D96" s="31" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B97" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C97" s="31" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="D97" s="31" t="n">
+        <v>90.8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B98" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C98" s="31" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="D98" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B99" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C99" s="31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="D99" s="31" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B100" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C100" s="31" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="D100" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B101" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C101" s="31" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="D101" s="31" t="n">
+        <v>97.2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B102" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C102" s="31" t="inlineStr">
+        <is>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="D102" s="31" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B103" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C103" s="31" t="inlineStr">
+        <is>
+          <t>Week 10</t>
+        </is>
+      </c>
+      <c r="D103" s="31" t="n">
+        <v>81.2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B104" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C104" s="31" t="inlineStr">
+        <is>
+          <t>Week 11</t>
+        </is>
+      </c>
+      <c r="D104" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B105" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C105" s="31" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="D105" s="31" t="n">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B106" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C106" s="31" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="D106" s="31" t="n">
+        <v>97.2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B107" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C107" s="31" t="inlineStr">
+        <is>
+          <t>Week 14</t>
+        </is>
+      </c>
+      <c r="D107" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B108" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C108" s="31" t="inlineStr">
+        <is>
+          <t>Week 16</t>
+        </is>
+      </c>
+      <c r="D108" s="31" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B109" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C109" s="31" t="inlineStr">
+        <is>
+          <t>Week 18</t>
+        </is>
+      </c>
+      <c r="D109" s="31" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B110" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C110" s="31" t="inlineStr">
+        <is>
+          <t>Week 19</t>
+        </is>
+      </c>
+      <c r="D110" s="31" t="n">
+        <v>96.90000000000001</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B111" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C111" s="31" t="inlineStr">
+        <is>
+          <t>Week 20</t>
+        </is>
+      </c>
+      <c r="D111" s="31" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B112" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C112" s="31" t="inlineStr">
+        <is>
+          <t>Week 21</t>
+        </is>
+      </c>
+      <c r="D112" s="31" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B113" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C113" s="31" t="inlineStr">
+        <is>
+          <t>Week 22</t>
+        </is>
+      </c>
+      <c r="D113" s="31" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B114" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C114" s="31" t="inlineStr">
+        <is>
+          <t>Week 23</t>
+        </is>
+      </c>
+      <c r="D114" s="31" t="n">
+        <v>96.90000000000001</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B115" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C115" s="31" t="inlineStr">
+        <is>
+          <t>Week 25</t>
+        </is>
+      </c>
+      <c r="D115" s="31" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="31" t="inlineStr">
+        <is>
+          <t>JECRC</t>
+        </is>
+      </c>
+      <c r="B116" s="31" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
+      <c r="C116" s="31" t="inlineStr">
+        <is>
+          <t>Week 26</t>
+        </is>
+      </c>
+      <c r="D116" s="31" t="n">
+        <v>94.40000000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B117" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C117" s="31" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="D117" s="31" t="n">
+        <v>87.90000000000001</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B118" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C118" s="31" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="D118" s="31" t="n">
+        <v>92.40000000000001</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B119" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C119" s="31" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="D119" s="31" t="n">
+        <v>93.90000000000001</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B120" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C120" s="31" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="D120" s="31" t="n">
+        <v>84.09999999999999</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B121" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C121" s="31" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="D121" s="31" t="n">
+        <v>84.8</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B122" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C122" s="31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="D122" s="31" t="n">
+        <v>87.90000000000001</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B123" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C123" s="31" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="D123" s="31" t="n">
+        <v>84.3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B124" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C124" s="31" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="D124" s="31" t="n">
+        <v>85.90000000000001</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B125" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C125" s="31" t="inlineStr">
+        <is>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="D125" s="31" t="n">
+        <v>92.40000000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B126" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C126" s="31" t="inlineStr">
+        <is>
+          <t>Week 10</t>
+        </is>
+      </c>
+      <c r="D126" s="31" t="n">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B127" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C127" s="31" t="inlineStr">
+        <is>
+          <t>Week 11</t>
+        </is>
+      </c>
+      <c r="D127" s="31" t="n">
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B128" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C128" s="31" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="D128" s="31" t="n">
+        <v>84.8</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B129" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C129" s="31" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="D129" s="31" t="n">
+        <v>84.8</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B130" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C130" s="31" t="inlineStr">
+        <is>
+          <t>Week 14</t>
+        </is>
+      </c>
+      <c r="D130" s="31" t="n">
+        <v>93.3</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B131" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C131" s="31" t="inlineStr">
+        <is>
+          <t>Week 15</t>
+        </is>
+      </c>
+      <c r="D131" s="31" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B132" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C132" s="31" t="inlineStr">
+        <is>
+          <t>Week 16</t>
+        </is>
+      </c>
+      <c r="D132" s="31" t="n">
+        <v>93.90000000000001</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B133" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C133" s="31" t="inlineStr">
+        <is>
+          <t>Week 18</t>
+        </is>
+      </c>
+      <c r="D133" s="31" t="n">
+        <v>87.90000000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B134" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C134" s="31" t="inlineStr">
+        <is>
+          <t>Week 19</t>
+        </is>
+      </c>
+      <c r="D134" s="31" t="n">
+        <v>84.8</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B135" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C135" s="31" t="inlineStr">
+        <is>
+          <t>Week 21</t>
+        </is>
+      </c>
+      <c r="D135" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B136" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C136" s="31" t="inlineStr">
+        <is>
+          <t>Week 22</t>
+        </is>
+      </c>
+      <c r="D136" s="31" t="n">
+        <v>89.90000000000001</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B137" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C137" s="31" t="inlineStr">
+        <is>
+          <t>Week 23</t>
+        </is>
+      </c>
+      <c r="D137" s="31" t="n">
+        <v>82.8</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B138" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C138" s="31" t="inlineStr">
+        <is>
+          <t>Week 25</t>
+        </is>
+      </c>
+      <c r="D138" s="31" t="n">
+        <v>85.90000000000001</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="31" t="inlineStr">
+        <is>
+          <t>Galgotias University</t>
+        </is>
+      </c>
+      <c r="B139" s="31" t="inlineStr">
+        <is>
+          <t>Batch 1</t>
+        </is>
+      </c>
+      <c r="C139" s="31" t="inlineStr">
+        <is>
+          <t>Week 26</t>
+        </is>
+      </c>
+      <c r="D139" s="31" t="n">
+        <v>84.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2966,7 +7444,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="12">
@@ -3468,7 +7946,6 @@
       <c r="C3" s="31" t="inlineStr">
         <is>
           <t>3702040 - Shivangi Rajput
-5027213 - daksh sharma
 6183978 - Saksham Tapadia
 6206803 - Shivam Dhanuka
 6206892 - Aastha bilochi
@@ -3529,18 +8006,19 @@
 6398773 - Arjun Pal
 6399051 - Shivendera Pratap Singh
 6400724 - kumar jaywardhan
+6400859 - Shabbu Parveen
 6401087 - Shruti Mishra
 6401588 - Priyanshu Kumar Sah
 6404281 - Vanshika Gangwar
 6410948 - Arnav Chauhan
 6411390 - Ankit Raj
 6412630 - Harshita Dwivedi
-6416851 - Siddharth
 6419785 - Satyam Kumar
 6422829 - Saurabh Yadav
 6430994 - Archana Maurya
 6432705 - Kushagra Chandra
 6434797 - Shivank singh chandel
+6437947 - Vivek Shrotriya
 6540727 - Indresh Mehta
 6741222 - Sidhi Bhagat
 6743195 - Priya Saini
@@ -3571,11 +8049,11 @@
         <is>
           <t>5025465 - Prince Tomer
 5026498 - Himani Singh
+5027213 - daksh sharma
 6208764 - Aditya Paliwal
-6400859 - Shabbu Parveen
 6400955 - Mrinal Mayank
-6433735 - Mohammad  Ayan
-6437947 - Vivek Shrotriya</t>
+6413621 - Aman Kumar Singh
+6433735 - Mohammad  Ayan</t>
         </is>
       </c>
     </row>
@@ -3592,7 +8070,7 @@
         <is>
           <t>6394706 - Prince dixit
 6413483 - Ravi Kumar Tiwari
-6413621 - Aman Kumar Singh
+6416851 - Siddharth
 6758587 - Kirti Singh
 7116051 - Aryan</t>
         </is>
@@ -3771,22 +8249,22 @@
         </is>
       </c>
       <c r="G3" s="31" t="n">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H3" s="31" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="I3" s="31" t="n">
-        <v>77.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="J3" s="31" t="n">
         <v>58</v>
       </c>
       <c r="K3" s="31" t="n">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="L3" s="31" t="n">
-        <v>65</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="4">
@@ -3821,22 +8299,22 @@
         </is>
       </c>
       <c r="G4" s="31" t="n">
-        <v>66.5</v>
+        <v>68</v>
       </c>
       <c r="H4" s="31" t="n">
-        <v>68.8</v>
+        <v>70</v>
       </c>
       <c r="I4" s="31" t="n">
-        <v>73.2</v>
+        <v>75.7</v>
       </c>
       <c r="J4" s="31" t="n">
         <v>57</v>
       </c>
       <c r="K4" s="31" t="n">
-        <v>90.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="L4" s="31" t="n">
-        <v>65</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -3867,26 +8345,26 @@
       </c>
       <c r="F5" s="31" t="inlineStr">
         <is>
-          <t>Progressing Candidates</t>
+          <t>Basic Competency</t>
         </is>
       </c>
       <c r="G5" s="31" t="n">
-        <v>75.5</v>
+        <v>61.8</v>
       </c>
       <c r="H5" s="31" t="n">
-        <v>73.5</v>
+        <v>61.9</v>
       </c>
       <c r="I5" s="31" t="n">
-        <v>82.8</v>
+        <v>59.5</v>
       </c>
       <c r="J5" s="31" t="n">
         <v>65</v>
       </c>
       <c r="K5" s="31" t="n">
-        <v>70.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="L5" s="31" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="6">
@@ -9021,19 +13499,19 @@
         </is>
       </c>
       <c r="G108" s="31" t="n">
-        <v>52.8</v>
+        <v>55.4</v>
       </c>
       <c r="H108" s="31" t="n">
-        <v>56.3</v>
+        <v>58.6</v>
       </c>
       <c r="I108" s="31" t="n">
-        <v>49.8</v>
+        <v>54.2</v>
       </c>
       <c r="J108" s="31" t="n">
         <v>57</v>
       </c>
       <c r="K108" s="31" t="n">
-        <v>84.5</v>
+        <v>85.5</v>
       </c>
       <c r="L108" s="31" t="n">
         <v>60</v>
@@ -9071,19 +13549,19 @@
         </is>
       </c>
       <c r="G109" s="31" t="n">
-        <v>70.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H109" s="31" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="I109" s="31" t="n">
-        <v>80.7</v>
+        <v>81.2</v>
       </c>
       <c r="J109" s="31" t="n">
         <v>55</v>
       </c>
       <c r="K109" s="31" t="n">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="L109" s="31" t="n">
         <v>78.40000000000001</v>
@@ -9121,22 +13599,22 @@
         </is>
       </c>
       <c r="G110" s="31" t="n">
-        <v>71.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H110" s="31" t="n">
-        <v>72.8</v>
+        <v>73.2</v>
       </c>
       <c r="I110" s="31" t="n">
-        <v>80.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="J110" s="31" t="n">
         <v>58</v>
       </c>
       <c r="K110" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="L110" s="31" t="n">
-        <v>68.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -9171,22 +13649,22 @@
         </is>
       </c>
       <c r="G111" s="31" t="n">
-        <v>72.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H111" s="31" t="n">
-        <v>73.5</v>
+        <v>73.8</v>
       </c>
       <c r="I111" s="31" t="n">
-        <v>82.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="J111" s="31" t="n">
         <v>58</v>
       </c>
       <c r="K111" s="31" t="n">
-        <v>91.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="L111" s="31" t="n">
-        <v>56.6</v>
+        <v>57</v>
       </c>
     </row>
     <row r="112">
@@ -9221,22 +13699,22 @@
         </is>
       </c>
       <c r="G112" s="31" t="n">
-        <v>73</v>
+        <v>73.7</v>
       </c>
       <c r="H112" s="31" t="n">
-        <v>68.5</v>
+        <v>69.3</v>
       </c>
       <c r="I112" s="31" t="n">
-        <v>75.8</v>
+        <v>77</v>
       </c>
       <c r="J112" s="31" t="n">
         <v>69</v>
       </c>
       <c r="K112" s="31" t="n">
-        <v>50.7</v>
+        <v>53.9</v>
       </c>
       <c r="L112" s="31" t="n">
-        <v>28.4</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="113">
@@ -9271,22 +13749,22 @@
         </is>
       </c>
       <c r="G113" s="31" t="n">
-        <v>72.8</v>
+        <v>73.2</v>
       </c>
       <c r="H113" s="31" t="n">
-        <v>74</v>
+        <v>74.5</v>
       </c>
       <c r="I113" s="31" t="n">
-        <v>81.7</v>
+        <v>82.5</v>
       </c>
       <c r="J113" s="31" t="n">
         <v>60</v>
       </c>
       <c r="K113" s="31" t="n">
-        <v>90.09999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="L113" s="31" t="n">
-        <v>63.4</v>
+        <v>63</v>
       </c>
     </row>
     <row r="114">
@@ -9321,22 +13799,22 @@
         </is>
       </c>
       <c r="G114" s="31" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="H114" s="31" t="n">
-        <v>74</v>
+        <v>73.7</v>
       </c>
       <c r="I114" s="31" t="n">
-        <v>82.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="J114" s="31" t="n">
         <v>66</v>
       </c>
       <c r="K114" s="31" t="n">
-        <v>73.2</v>
+        <v>73.7</v>
       </c>
       <c r="L114" s="31" t="n">
-        <v>46.6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="115">
@@ -9371,22 +13849,22 @@
         </is>
       </c>
       <c r="G115" s="31" t="n">
-        <v>73.2</v>
+        <v>73.5</v>
       </c>
       <c r="H115" s="31" t="n">
-        <v>75</v>
+        <v>75.3</v>
       </c>
       <c r="I115" s="31" t="n">
-        <v>83.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J115" s="31" t="n">
         <v>58</v>
       </c>
       <c r="K115" s="31" t="n">
-        <v>93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L115" s="31" t="n">
-        <v>70</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="116">
@@ -9421,22 +13899,22 @@
         </is>
       </c>
       <c r="G116" s="31" t="n">
-        <v>71.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H116" s="31" t="n">
-        <v>71.7</v>
+        <v>72.3</v>
       </c>
       <c r="I116" s="31" t="n">
-        <v>81.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="J116" s="31" t="n">
         <v>57</v>
       </c>
       <c r="K116" s="31" t="n">
-        <v>81.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L116" s="31" t="n">
-        <v>55</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="117">
@@ -9467,26 +13945,26 @@
       </c>
       <c r="F117" s="31" t="inlineStr">
         <is>
-          <t>Basic Competency</t>
+          <t>Progressing Candidates</t>
         </is>
       </c>
       <c r="G117" s="31" t="n">
-        <v>69.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H117" s="31" t="n">
-        <v>70.2</v>
+        <v>71</v>
       </c>
       <c r="I117" s="31" t="n">
-        <v>78.5</v>
+        <v>79.8</v>
       </c>
       <c r="J117" s="31" t="n">
         <v>57</v>
       </c>
       <c r="K117" s="31" t="n">
-        <v>84.5</v>
+        <v>85.5</v>
       </c>
       <c r="L117" s="31" t="n">
-        <v>51.6</v>
+        <v>52.40000000000001</v>
       </c>
     </row>
     <row r="118">
@@ -9521,22 +13999,22 @@
         </is>
       </c>
       <c r="G118" s="31" t="n">
-        <v>67.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H118" s="31" t="n">
-        <v>70.5</v>
+        <v>71.3</v>
       </c>
       <c r="I118" s="31" t="n">
-        <v>78.3</v>
+        <v>79.8</v>
       </c>
       <c r="J118" s="31" t="n">
         <v>52</v>
       </c>
       <c r="K118" s="31" t="n">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="L118" s="31" t="n">
-        <v>75</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="119">
@@ -9571,22 +14049,22 @@
         </is>
       </c>
       <c r="G119" s="31" t="n">
-        <v>72.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H119" s="31" t="n">
-        <v>73.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I119" s="31" t="n">
-        <v>82.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="J119" s="31" t="n">
         <v>58</v>
       </c>
       <c r="K119" s="31" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L119" s="31" t="n">
-        <v>48.4</v>
+        <v>47.59999999999999</v>
       </c>
     </row>
     <row r="120">
@@ -9624,7 +14102,7 @@
         <v>75.8</v>
       </c>
       <c r="H120" s="31" t="n">
-        <v>72</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I120" s="31" t="n">
         <v>81.90000000000001</v>
@@ -9633,10 +14111,10 @@
         <v>67</v>
       </c>
       <c r="K120" s="31" t="n">
-        <v>63.4</v>
+        <v>65.8</v>
       </c>
       <c r="L120" s="31" t="n">
-        <v>25</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="121">
@@ -9671,22 +14149,22 @@
         </is>
       </c>
       <c r="G121" s="31" t="n">
-        <v>71.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H121" s="31" t="n">
-        <v>73.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="I121" s="31" t="n">
-        <v>83</v>
+        <v>83.8</v>
       </c>
       <c r="J121" s="31" t="n">
         <v>56</v>
       </c>
       <c r="K121" s="31" t="n">
-        <v>95.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="L121" s="31" t="n">
-        <v>65</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="122">
@@ -9721,22 +14199,22 @@
         </is>
       </c>
       <c r="G122" s="31" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="H122" s="31" t="n">
-        <v>72.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="I122" s="31" t="n">
-        <v>81.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="J122" s="31" t="n">
         <v>58</v>
       </c>
       <c r="K122" s="31" t="n">
-        <v>91.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="L122" s="31" t="n">
-        <v>55</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="123">
@@ -9771,22 +14249,22 @@
         </is>
       </c>
       <c r="G123" s="31" t="n">
-        <v>71.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H123" s="31" t="n">
-        <v>71</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I123" s="31" t="n">
-        <v>81</v>
+        <v>81.8</v>
       </c>
       <c r="J123" s="31" t="n">
         <v>57</v>
       </c>
       <c r="K123" s="31" t="n">
-        <v>87.3</v>
+        <v>88.2</v>
       </c>
       <c r="L123" s="31" t="n">
-        <v>36.6</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="124">
@@ -9821,22 +14299,22 @@
         </is>
       </c>
       <c r="G124" s="31" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H124" s="31" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="I124" s="31" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="J124" s="31" t="n">
         <v>58</v>
       </c>
       <c r="K124" s="31" t="n">
-        <v>95.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="L124" s="31" t="n">
-        <v>56.6</v>
+        <v>57</v>
       </c>
     </row>
     <row r="125">
@@ -9871,22 +14349,22 @@
         </is>
       </c>
       <c r="G125" s="31" t="n">
-        <v>30.3</v>
+        <v>33.4</v>
       </c>
       <c r="H125" s="31" t="n">
-        <v>34.5</v>
+        <v>37.4</v>
       </c>
       <c r="I125" s="31" t="n">
-        <v>51.5</v>
+        <v>56.8</v>
       </c>
       <c r="J125" s="31" t="n">
         <v>0</v>
       </c>
       <c r="K125" s="31" t="n">
-        <v>69</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="L125" s="31" t="n">
-        <v>36.6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="126">
@@ -9917,23 +14395,23 @@
       </c>
       <c r="F126" s="31" t="inlineStr">
         <is>
-          <t>Critical Intervention</t>
+          <t>Basic Competency</t>
         </is>
       </c>
       <c r="G126" s="31" t="n">
-        <v>58.9</v>
+        <v>60.9</v>
       </c>
       <c r="H126" s="31" t="n">
-        <v>62.2</v>
+        <v>63.8</v>
       </c>
       <c r="I126" s="31" t="n">
-        <v>58.1</v>
+        <v>61.5</v>
       </c>
       <c r="J126" s="31" t="n">
         <v>60</v>
       </c>
       <c r="K126" s="31" t="n">
-        <v>91.5</v>
+        <v>90.8</v>
       </c>
       <c r="L126" s="31" t="n">
         <v>60</v>
@@ -9967,17 +14445,17 @@
       </c>
       <c r="F127" s="31" t="inlineStr">
         <is>
-          <t>Progressing Candidates</t>
+          <t>Critical Intervention</t>
         </is>
       </c>
       <c r="G127" s="31" t="n">
-        <v>72.8</v>
+        <v>59.3</v>
       </c>
       <c r="H127" s="31" t="n">
-        <v>75.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I127" s="31" t="n">
-        <v>82.40000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="J127" s="31" t="n">
         <v>59</v>
@@ -10021,22 +14499,22 @@
         </is>
       </c>
       <c r="G128" s="31" t="n">
-        <v>72.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H128" s="31" t="n">
-        <v>73.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I128" s="31" t="n">
-        <v>82.8</v>
+        <v>83.7</v>
       </c>
       <c r="J128" s="31" t="n">
         <v>58</v>
       </c>
       <c r="K128" s="31" t="n">
-        <v>87.3</v>
+        <v>86.8</v>
       </c>
       <c r="L128" s="31" t="n">
-        <v>65</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="129">
@@ -10071,22 +14549,22 @@
         </is>
       </c>
       <c r="G129" s="31" t="n">
-        <v>74.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H129" s="31" t="n">
-        <v>76.7</v>
+        <v>77</v>
       </c>
       <c r="I129" s="31" t="n">
-        <v>84.2</v>
+        <v>84.8</v>
       </c>
       <c r="J129" s="31" t="n">
         <v>60</v>
       </c>
       <c r="K129" s="31" t="n">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="L129" s="31" t="n">
-        <v>75</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="130">
@@ -10121,22 +14599,22 @@
         </is>
       </c>
       <c r="G130" s="31" t="n">
-        <v>71.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="H130" s="31" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="I130" s="31" t="n">
-        <v>83</v>
+        <v>83.2</v>
       </c>
       <c r="J130" s="31" t="n">
         <v>56</v>
       </c>
       <c r="K130" s="31" t="n">
-        <v>93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="L130" s="31" t="n">
-        <v>45</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="131">
@@ -10171,19 +14649,19 @@
         </is>
       </c>
       <c r="G131" s="31" t="n">
-        <v>74.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="H131" s="31" t="n">
-        <v>75.8</v>
+        <v>76.2</v>
       </c>
       <c r="I131" s="31" t="n">
-        <v>84.5</v>
+        <v>85.2</v>
       </c>
       <c r="J131" s="31" t="n">
         <v>60</v>
       </c>
       <c r="K131" s="31" t="n">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="L131" s="31" t="n">
         <v>61.6</v>
@@ -10221,19 +14699,19 @@
         </is>
       </c>
       <c r="G132" s="31" t="n">
-        <v>68.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H132" s="31" t="n">
-        <v>68.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I132" s="31" t="n">
-        <v>76.5</v>
+        <v>78.3</v>
       </c>
       <c r="J132" s="31" t="n">
         <v>58</v>
       </c>
       <c r="K132" s="31" t="n">
-        <v>73.2</v>
+        <v>75</v>
       </c>
       <c r="L132" s="31" t="n">
         <v>60</v>
@@ -10271,19 +14749,19 @@
         </is>
       </c>
       <c r="G133" s="31" t="n">
-        <v>72.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H133" s="31" t="n">
-        <v>73.8</v>
+        <v>74.2</v>
       </c>
       <c r="I133" s="31" t="n">
-        <v>83.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="J133" s="31" t="n">
         <v>56</v>
       </c>
       <c r="K133" s="31" t="n">
-        <v>95.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="L133" s="31" t="n">
         <v>60</v>
@@ -10317,26 +14795,26 @@
       </c>
       <c r="F134" s="31" t="inlineStr">
         <is>
-          <t>Basic Competency</t>
+          <t>Progressing Candidates</t>
         </is>
       </c>
       <c r="G134" s="31" t="n">
-        <v>69.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H134" s="31" t="n">
-        <v>69.7</v>
+        <v>70.5</v>
       </c>
       <c r="I134" s="31" t="n">
-        <v>77.2</v>
+        <v>78.5</v>
       </c>
       <c r="J134" s="31" t="n">
         <v>58</v>
       </c>
       <c r="K134" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="L134" s="31" t="n">
-        <v>45</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="135">
@@ -11321,22 +15799,22 @@
         </is>
       </c>
       <c r="G154" s="31" t="n">
-        <v>54.1</v>
+        <v>55.9</v>
       </c>
       <c r="H154" s="31" t="n">
-        <v>57.5</v>
+        <v>59.1</v>
       </c>
       <c r="I154" s="31" t="n">
-        <v>54.1</v>
+        <v>57.2</v>
       </c>
       <c r="J154" s="31" t="n">
         <v>54</v>
       </c>
       <c r="K154" s="31" t="n">
-        <v>88.7</v>
+        <v>89.5</v>
       </c>
       <c r="L154" s="31" t="n">
-        <v>53.4</v>
+        <v>52.40000000000001</v>
       </c>
     </row>
     <row r="155">
@@ -11771,13 +16249,13 @@
         </is>
       </c>
       <c r="G163" s="31" t="n">
-        <v>73.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H163" s="31" t="n">
-        <v>75.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I163" s="31" t="n">
-        <v>82.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="J163" s="31" t="n">
         <v>59</v>
@@ -11786,7 +16264,7 @@
         <v>100</v>
       </c>
       <c r="L163" s="31" t="n">
-        <v>71.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="164">
@@ -12171,22 +16649,22 @@
         </is>
       </c>
       <c r="G171" s="31" t="n">
-        <v>54.8</v>
+        <v>56.9</v>
       </c>
       <c r="H171" s="31" t="n">
-        <v>59.3</v>
+        <v>61.1</v>
       </c>
       <c r="I171" s="31" t="n">
-        <v>55.3</v>
+        <v>58.9</v>
       </c>
       <c r="J171" s="31" t="n">
         <v>54</v>
       </c>
       <c r="K171" s="31" t="n">
-        <v>95.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="L171" s="31" t="n">
-        <v>63.4</v>
+        <v>63</v>
       </c>
     </row>
     <row r="172">
@@ -12564,7 +17042,7 @@
         <v>76.59999999999999</v>
       </c>
       <c r="M2" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N2" s="31" t="n">
         <v>95.09999999999999</v>
@@ -12650,7 +17128,7 @@
         </is>
       </c>
       <c r="H3" s="31" t="n">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="I3" s="31" t="inlineStr">
         <is>
@@ -12658,7 +17136,7 @@
         </is>
       </c>
       <c r="J3" s="31" t="n">
-        <v>65</v>
+        <v>66.2</v>
       </c>
       <c r="K3" s="31" t="inlineStr">
         <is>
@@ -12666,19 +17144,19 @@
         </is>
       </c>
       <c r="L3" s="31" t="n">
-        <v>73.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="M3" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N3" s="31" t="n">
-        <v>81.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="O3" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>77.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="Q3" s="31" t="inlineStr">
         <is>
@@ -12697,7 +17175,7 @@
         </is>
       </c>
       <c r="U3" s="31" t="n">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="V3" s="31" t="inlineStr">
         <is>
@@ -12705,7 +17183,7 @@
         </is>
       </c>
       <c r="W3" s="31" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="X3" s="31" t="inlineStr">
         <is>
@@ -12755,15 +17233,15 @@
         </is>
       </c>
       <c r="H4" s="31" t="n">
-        <v>90.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="I4" s="31" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J4" s="31" t="n">
-        <v>65</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K4" s="31" t="inlineStr">
         <is>
@@ -12771,19 +17249,19 @@
         </is>
       </c>
       <c r="L4" s="31" t="n">
-        <v>73</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M4" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N4" s="31" t="n">
-        <v>73.5</v>
+        <v>78.7</v>
       </c>
       <c r="O4" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>73.2</v>
+        <v>75.7</v>
       </c>
       <c r="Q4" s="31" t="inlineStr">
         <is>
@@ -12802,7 +17280,7 @@
         </is>
       </c>
       <c r="U4" s="31" t="n">
-        <v>66.5</v>
+        <v>68</v>
       </c>
       <c r="V4" s="31" t="inlineStr">
         <is>
@@ -12810,11 +17288,11 @@
         </is>
       </c>
       <c r="W4" s="31" t="n">
-        <v>68.8</v>
+        <v>70</v>
       </c>
       <c r="X4" s="31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y4" s="31" t="inlineStr">
@@ -12860,7 +17338,7 @@
         </is>
       </c>
       <c r="H5" s="31" t="n">
-        <v>70.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I5" s="31" t="inlineStr">
         <is>
@@ -12868,7 +17346,7 @@
         </is>
       </c>
       <c r="J5" s="31" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="K5" s="31" t="inlineStr">
         <is>
@@ -12876,23 +17354,23 @@
         </is>
       </c>
       <c r="L5" s="31" t="n">
-        <v>73.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M5" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N5" s="31" t="n">
-        <v>91.8</v>
+        <v>45.5</v>
       </c>
       <c r="O5" s="31" t="n">
         <v>4</v>
       </c>
       <c r="P5" s="31" t="n">
-        <v>82.8</v>
+        <v>59.5</v>
       </c>
       <c r="Q5" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="R5" s="31" t="n">
@@ -12907,24 +17385,24 @@
         </is>
       </c>
       <c r="U5" s="31" t="n">
-        <v>75.5</v>
+        <v>61.8</v>
       </c>
       <c r="V5" s="31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W5" s="31" t="n">
-        <v>73.5</v>
+        <v>61.9</v>
       </c>
       <c r="X5" s="31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y5" s="31" t="inlineStr">
         <is>
-          <t>Progressing Candidates</t>
+          <t>Basic Competency</t>
         </is>
       </c>
     </row>
@@ -12984,7 +17462,7 @@
         <v>82.2</v>
       </c>
       <c r="M6" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N6" s="31" t="n">
         <v>98.7</v>
@@ -13089,7 +17567,7 @@
         <v>81</v>
       </c>
       <c r="M7" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N7" s="31" t="n">
         <v>95</v>
@@ -13194,7 +17672,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="M8" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N8" s="31" t="n">
         <v>71.59999999999999</v>
@@ -13299,7 +17777,7 @@
         <v>76.8</v>
       </c>
       <c r="M9" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N9" s="31" t="n">
         <v>94.59999999999999</v>
@@ -13404,7 +17882,7 @@
         <v>82.7</v>
       </c>
       <c r="M10" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N10" s="31" t="n">
         <v>93.8</v>
@@ -13509,7 +17987,7 @@
         <v>81.3</v>
       </c>
       <c r="M11" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N11" s="31" t="n">
         <v>94.09999999999999</v>
@@ -13614,7 +18092,7 @@
         <v>77.2</v>
       </c>
       <c r="M12" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N12" s="31" t="n">
         <v>96</v>
@@ -13719,7 +18197,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="M13" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N13" s="31" t="n">
         <v>94.59999999999999</v>
@@ -13824,7 +18302,7 @@
         <v>81.7</v>
       </c>
       <c r="M14" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N14" s="31" t="n">
         <v>95.5</v>
@@ -13929,7 +18407,7 @@
         <v>70.59999999999999</v>
       </c>
       <c r="M15" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N15" s="31" t="n">
         <v>96.7</v>
@@ -14034,7 +18512,7 @@
         <v>57.7</v>
       </c>
       <c r="M16" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N16" s="31" t="n">
         <v>91.09999999999999</v>
@@ -14139,7 +18617,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="M17" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N17" s="31" t="n">
         <v>96.3</v>
@@ -14244,7 +18722,7 @@
         <v>71.8</v>
       </c>
       <c r="M18" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N18" s="31" t="n">
         <v>96</v>
@@ -14349,7 +18827,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="M19" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N19" s="31" t="n">
         <v>98.7</v>
@@ -14454,7 +18932,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="M20" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N20" s="31" t="n">
         <v>95.8</v>
@@ -14559,7 +19037,7 @@
         <v>76.40000000000001</v>
       </c>
       <c r="M21" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N21" s="31" t="n">
         <v>99.3</v>
@@ -14664,7 +19142,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="M22" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N22" s="31" t="n">
         <v>93.8</v>
@@ -14769,7 +19247,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="M23" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N23" s="31" t="n">
         <v>98.7</v>
@@ -14874,7 +19352,7 @@
         <v>74.2</v>
       </c>
       <c r="M24" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N24" s="31" t="n">
         <v>98.59999999999999</v>
@@ -14979,7 +19457,7 @@
         <v>77</v>
       </c>
       <c r="M25" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N25" s="31" t="n">
         <v>99</v>
@@ -15084,7 +19562,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="M26" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N26" s="31" t="n">
         <v>95.90000000000001</v>
@@ -15189,7 +19667,7 @@
         <v>81.3</v>
       </c>
       <c r="M27" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N27" s="31" t="n">
         <v>98.09999999999999</v>
@@ -15294,7 +19772,7 @@
         <v>75.8</v>
       </c>
       <c r="M28" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N28" s="31" t="n">
         <v>97.5</v>
@@ -15399,7 +19877,7 @@
         <v>77.40000000000001</v>
       </c>
       <c r="M29" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N29" s="31" t="n">
         <v>92.90000000000001</v>
@@ -15504,7 +19982,7 @@
         <v>80.3</v>
       </c>
       <c r="M30" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N30" s="31" t="n">
         <v>98.7</v>
@@ -15609,7 +20087,7 @@
         <v>80.3</v>
       </c>
       <c r="M31" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N31" s="31" t="n">
         <v>97.90000000000001</v>
@@ -15714,7 +20192,7 @@
         <v>81.2</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N32" s="31" t="n">
         <v>96.2</v>
@@ -15819,7 +20297,7 @@
         <v>80</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N33" s="31" t="n">
         <v>97.59999999999999</v>
@@ -15924,7 +20402,7 @@
         <v>80.7</v>
       </c>
       <c r="M34" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N34" s="31" t="n">
         <v>95.90000000000001</v>
@@ -16029,7 +20507,7 @@
         <v>58.6</v>
       </c>
       <c r="M35" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N35" s="31" t="n">
         <v>93.40000000000001</v>
@@ -16134,7 +20612,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="M36" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N36" s="31" t="n">
         <v>96.3</v>
@@ -16239,7 +20717,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="M37" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N37" s="31" t="n">
         <v>88.59999999999999</v>
@@ -16344,7 +20822,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="M38" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N38" s="31" t="n">
         <v>95</v>
@@ -16449,7 +20927,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="M39" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N39" s="31" t="n">
         <v>95.8</v>
@@ -16554,7 +21032,7 @@
         <v>76.8</v>
       </c>
       <c r="M40" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N40" s="31" t="n">
         <v>97.5</v>
@@ -16659,7 +21137,7 @@
         <v>76.40000000000001</v>
       </c>
       <c r="M41" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N41" s="31" t="n">
         <v>96.3</v>
@@ -16764,7 +21242,7 @@
         <v>81.5</v>
       </c>
       <c r="M42" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N42" s="31" t="n">
         <v>97.59999999999999</v>
@@ -16869,7 +21347,7 @@
         <v>74.8</v>
       </c>
       <c r="M43" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N43" s="31" t="n">
         <v>96.59999999999999</v>
@@ -16974,7 +21452,7 @@
         <v>76.8</v>
       </c>
       <c r="M44" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N44" s="31" t="n">
         <v>97.90000000000001</v>
@@ -17079,7 +21557,7 @@
         <v>81</v>
       </c>
       <c r="M45" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N45" s="31" t="n">
         <v>93.59999999999999</v>
@@ -17184,7 +21662,7 @@
         <v>80.7</v>
       </c>
       <c r="M46" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N46" s="31" t="n">
         <v>98.2</v>
@@ -17289,7 +21767,7 @@
         <v>80.5</v>
       </c>
       <c r="M47" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N47" s="31" t="n">
         <v>95.5</v>
@@ -17394,7 +21872,7 @@
         <v>76</v>
       </c>
       <c r="M48" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N48" s="31" t="n">
         <v>97.90000000000001</v>
@@ -17499,7 +21977,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="M49" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N49" s="31" t="n">
         <v>99.40000000000001</v>
@@ -17604,7 +22082,7 @@
         <v>74.59999999999999</v>
       </c>
       <c r="M50" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N50" s="31" t="n">
         <v>97.90000000000001</v>
@@ -17709,7 +22187,7 @@
         <v>74</v>
       </c>
       <c r="M51" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N51" s="31" t="n">
         <v>97.59999999999999</v>
@@ -17814,7 +22292,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="M52" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N52" s="31" t="n">
         <v>97.59999999999999</v>
@@ -17919,7 +22397,7 @@
         <v>73.40000000000001</v>
       </c>
       <c r="M53" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N53" s="31" t="n">
         <v>95</v>
@@ -18024,7 +22502,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="M54" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N54" s="31" t="n">
         <v>98.3</v>
@@ -18129,7 +22607,7 @@
         <v>76</v>
       </c>
       <c r="M55" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N55" s="31" t="n">
         <v>97.2</v>
@@ -18234,7 +22712,7 @@
         <v>81.2</v>
       </c>
       <c r="M56" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N56" s="31" t="n">
         <v>97.90000000000001</v>
@@ -18339,7 +22817,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="M57" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N57" s="31" t="n">
         <v>98</v>
@@ -18444,7 +22922,7 @@
         <v>74.59999999999999</v>
       </c>
       <c r="M58" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N58" s="31" t="n">
         <v>97.3</v>
@@ -18549,7 +23027,7 @@
         <v>76.8</v>
       </c>
       <c r="M59" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N59" s="31" t="n">
         <v>98.59999999999999</v>
@@ -18654,7 +23132,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="M60" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N60" s="31" t="n">
         <v>98.8</v>
@@ -18759,7 +23237,7 @@
         <v>81</v>
       </c>
       <c r="M61" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N61" s="31" t="n">
         <v>92.90000000000001</v>
@@ -18864,7 +23342,7 @@
         <v>81.5</v>
       </c>
       <c r="M62" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N62" s="31" t="n">
         <v>92</v>
@@ -18969,7 +23447,7 @@
         <v>76.40000000000001</v>
       </c>
       <c r="M63" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N63" s="31" t="n">
         <v>95.90000000000001</v>
@@ -19074,7 +23552,7 @@
         <v>77</v>
       </c>
       <c r="M64" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N64" s="31" t="n">
         <v>95.8</v>
@@ -19179,7 +23657,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="M65" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N65" s="31" t="n">
         <v>98.5</v>
@@ -19284,7 +23762,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="M66" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N66" s="31" t="n">
         <v>97.3</v>
@@ -19389,7 +23867,7 @@
         <v>81.8</v>
       </c>
       <c r="M67" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N67" s="31" t="n">
         <v>98.5</v>
@@ -19494,7 +23972,7 @@
         <v>81.2</v>
       </c>
       <c r="M68" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N68" s="31" t="n">
         <v>98.09999999999999</v>
@@ -19599,7 +24077,7 @@
         <v>58.7</v>
       </c>
       <c r="M69" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N69" s="31" t="n">
         <v>93.8</v>
@@ -19704,7 +24182,7 @@
         <v>74.40000000000001</v>
       </c>
       <c r="M70" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N70" s="31" t="n">
         <v>95.5</v>
@@ -19809,7 +24287,7 @@
         <v>72.8</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N71" s="31" t="n">
         <v>98.7</v>
@@ -19914,7 +24392,7 @@
         <v>77</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N72" s="31" t="n">
         <v>95.40000000000001</v>
@@ -20019,7 +24497,7 @@
         <v>65.3</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N73" s="31" t="n">
         <v>96.2</v>
@@ -20124,7 +24602,7 @@
         <v>80.7</v>
       </c>
       <c r="M74" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N74" s="31" t="n">
         <v>86.5</v>
@@ -20229,7 +24707,7 @@
         <v>79.7</v>
       </c>
       <c r="M75" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N75" s="31" t="n">
         <v>95.59999999999999</v>
@@ -20334,7 +24812,7 @@
         <v>77</v>
       </c>
       <c r="M76" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N76" s="31" t="n">
         <v>97.40000000000001</v>
@@ -20439,7 +24917,7 @@
         <v>76.8</v>
       </c>
       <c r="M77" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N77" s="31" t="n">
         <v>94.59999999999999</v>
@@ -20544,7 +25022,7 @@
         <v>81</v>
       </c>
       <c r="M78" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N78" s="31" t="n">
         <v>92.8</v>
@@ -20649,7 +25127,7 @@
         <v>58.9</v>
       </c>
       <c r="M79" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N79" s="31" t="n">
         <v>86.40000000000001</v>
@@ -20754,7 +25232,7 @@
         <v>76.59999999999999</v>
       </c>
       <c r="M80" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N80" s="31" t="n">
         <v>93.8</v>
@@ -20859,7 +25337,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="M81" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N81" s="31" t="n">
         <v>96.3</v>
@@ -20964,7 +25442,7 @@
         <v>70</v>
       </c>
       <c r="M82" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N82" s="31" t="n">
         <v>94.7</v>
@@ -21069,7 +25547,7 @@
         <v>74</v>
       </c>
       <c r="M83" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N83" s="31" t="n">
         <v>99.3</v>
@@ -21174,7 +25652,7 @@
         <v>73.8</v>
       </c>
       <c r="M84" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N84" s="31" t="n">
         <v>99.3</v>
@@ -21279,7 +25757,7 @@
         <v>77</v>
       </c>
       <c r="M85" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N85" s="31" t="n">
         <v>95.2</v>
@@ -21384,7 +25862,7 @@
         <v>80.5</v>
       </c>
       <c r="M86" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N86" s="31" t="n">
         <v>99.40000000000001</v>
@@ -21489,7 +25967,7 @@
         <v>72.8</v>
       </c>
       <c r="M87" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N87" s="31" t="n">
         <v>96</v>
@@ -21594,7 +26072,7 @@
         <v>71.8</v>
       </c>
       <c r="M88" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N88" s="31" t="n">
         <v>98.7</v>
@@ -21699,7 +26177,7 @@
         <v>74</v>
       </c>
       <c r="M89" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N89" s="31" t="n">
         <v>94.8</v>
@@ -21804,7 +26282,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="M90" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N90" s="31" t="n">
         <v>98.09999999999999</v>
@@ -21909,7 +26387,7 @@
         <v>75.40000000000001</v>
       </c>
       <c r="M91" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N91" s="31" t="n">
         <v>97.2</v>
@@ -22014,7 +26492,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="M92" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N92" s="31" t="n">
         <v>98.3</v>
@@ -22119,7 +26597,7 @@
         <v>82.7</v>
       </c>
       <c r="M93" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N93" s="31" t="n">
         <v>100</v>
@@ -22224,7 +26702,7 @@
         <v>81.3</v>
       </c>
       <c r="M94" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N94" s="31" t="n">
         <v>96.3</v>
@@ -22329,7 +26807,7 @@
         <v>71</v>
       </c>
       <c r="M95" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N95" s="31" t="n">
         <v>91.8</v>
@@ -22434,7 +26912,7 @@
         <v>76.40000000000001</v>
       </c>
       <c r="M96" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N96" s="31" t="n">
         <v>97.5</v>
@@ -22539,7 +27017,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="M97" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N97" s="31" t="n">
         <v>97.09999999999999</v>
@@ -22644,7 +27122,7 @@
         <v>70.7</v>
       </c>
       <c r="M98" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N98" s="31" t="n">
         <v>93.2</v>
@@ -22749,7 +27227,7 @@
         <v>46.9</v>
       </c>
       <c r="M99" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N99" s="31" t="n">
         <v>96.8</v>
@@ -22854,7 +27332,7 @@
         <v>73.8</v>
       </c>
       <c r="M100" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N100" s="31" t="n">
         <v>95.90000000000001</v>
@@ -22959,7 +27437,7 @@
         <v>76.2</v>
       </c>
       <c r="M101" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N101" s="31" t="n">
         <v>96.59999999999999</v>
@@ -23064,7 +27542,7 @@
         <v>70.09999999999999</v>
       </c>
       <c r="M102" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N102" s="31" t="n">
         <v>94.3</v>
@@ -23169,7 +27647,7 @@
         <v>82</v>
       </c>
       <c r="M103" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N103" s="31" t="n">
         <v>98.09999999999999</v>
@@ -23274,7 +27752,7 @@
         <v>75.59999999999999</v>
       </c>
       <c r="M104" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N104" s="31" t="n">
         <v>96.8</v>
@@ -23379,7 +27857,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="M105" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N105" s="31" t="n">
         <v>97.40000000000001</v>
@@ -23484,7 +27962,7 @@
         <v>77.2</v>
       </c>
       <c r="M106" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N106" s="31" t="n">
         <v>95.2</v>
@@ -23589,7 +28067,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="M107" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N107" s="31" t="n">
         <v>92</v>
@@ -23675,7 +28153,7 @@
         </is>
       </c>
       <c r="H108" s="31" t="n">
-        <v>84.5</v>
+        <v>85.5</v>
       </c>
       <c r="I108" s="31" t="inlineStr">
         <is>
@@ -23691,19 +28169,19 @@
         </is>
       </c>
       <c r="L108" s="31" t="n">
-        <v>73.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="M108" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N108" s="31" t="n">
-        <v>26.4</v>
+        <v>36.6</v>
       </c>
       <c r="O108" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P108" s="31" t="n">
-        <v>49.8</v>
+        <v>54.2</v>
       </c>
       <c r="Q108" s="31" t="inlineStr">
         <is>
@@ -23722,7 +28200,7 @@
         </is>
       </c>
       <c r="U108" s="31" t="n">
-        <v>52.8</v>
+        <v>55.4</v>
       </c>
       <c r="V108" s="31" t="inlineStr">
         <is>
@@ -23730,7 +28208,7 @@
         </is>
       </c>
       <c r="W108" s="31" t="n">
-        <v>56.3</v>
+        <v>58.6</v>
       </c>
       <c r="X108" s="31" t="inlineStr">
         <is>
@@ -23780,7 +28258,7 @@
         </is>
       </c>
       <c r="H109" s="31" t="n">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="I109" s="31" t="inlineStr">
         <is>
@@ -23796,19 +28274,19 @@
         </is>
       </c>
       <c r="L109" s="31" t="n">
-        <v>72.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="M109" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N109" s="31" t="n">
-        <v>88.5</v>
+        <v>90.7</v>
       </c>
       <c r="O109" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P109" s="31" t="n">
-        <v>80.7</v>
+        <v>81.2</v>
       </c>
       <c r="Q109" s="31" t="inlineStr">
         <is>
@@ -23827,7 +28305,7 @@
         </is>
       </c>
       <c r="U109" s="31" t="n">
-        <v>70.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V109" s="31" t="inlineStr">
         <is>
@@ -23835,7 +28313,7 @@
         </is>
       </c>
       <c r="W109" s="31" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="X109" s="31" t="inlineStr">
         <is>
@@ -23885,7 +28363,7 @@
         </is>
       </c>
       <c r="H110" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="I110" s="31" t="inlineStr">
         <is>
@@ -23893,7 +28371,7 @@
         </is>
       </c>
       <c r="J110" s="31" t="n">
-        <v>68.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K110" s="31" t="inlineStr">
         <is>
@@ -23901,19 +28379,19 @@
         </is>
       </c>
       <c r="L110" s="31" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="M110" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N110" s="31" t="n">
-        <v>90.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O110" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P110" s="31" t="n">
-        <v>80.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="Q110" s="31" t="inlineStr">
         <is>
@@ -23932,7 +28410,7 @@
         </is>
       </c>
       <c r="U110" s="31" t="n">
-        <v>71.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="V110" s="31" t="inlineStr">
         <is>
@@ -23940,7 +28418,7 @@
         </is>
       </c>
       <c r="W110" s="31" t="n">
-        <v>72.8</v>
+        <v>73.2</v>
       </c>
       <c r="X110" s="31" t="inlineStr">
         <is>
@@ -23990,7 +28468,7 @@
         </is>
       </c>
       <c r="H111" s="31" t="n">
-        <v>91.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I111" s="31" t="inlineStr">
         <is>
@@ -23998,7 +28476,7 @@
         </is>
       </c>
       <c r="J111" s="31" t="n">
-        <v>56.6</v>
+        <v>57</v>
       </c>
       <c r="K111" s="31" t="inlineStr">
         <is>
@@ -24006,19 +28484,19 @@
         </is>
       </c>
       <c r="L111" s="31" t="n">
-        <v>72</v>
+        <v>71.5</v>
       </c>
       <c r="M111" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N111" s="31" t="n">
-        <v>92.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="O111" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P111" s="31" t="n">
-        <v>82.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="Q111" s="31" t="inlineStr">
         <is>
@@ -24037,7 +28515,7 @@
         </is>
       </c>
       <c r="U111" s="31" t="n">
-        <v>72.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="V111" s="31" t="inlineStr">
         <is>
@@ -24045,7 +28523,7 @@
         </is>
       </c>
       <c r="W111" s="31" t="n">
-        <v>73.5</v>
+        <v>73.8</v>
       </c>
       <c r="X111" s="31" t="inlineStr">
         <is>
@@ -24095,7 +28573,7 @@
         </is>
       </c>
       <c r="H112" s="31" t="n">
-        <v>50.7</v>
+        <v>53.9</v>
       </c>
       <c r="I112" s="31" t="inlineStr">
         <is>
@@ -24103,7 +28581,7 @@
         </is>
       </c>
       <c r="J112" s="31" t="n">
-        <v>28.4</v>
+        <v>26.2</v>
       </c>
       <c r="K112" s="31" t="inlineStr">
         <is>
@@ -24111,19 +28589,19 @@
         </is>
       </c>
       <c r="L112" s="31" t="n">
-        <v>73.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="M112" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N112" s="31" t="n">
-        <v>78.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="O112" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P112" s="31" t="n">
-        <v>75.8</v>
+        <v>77</v>
       </c>
       <c r="Q112" s="31" t="inlineStr">
         <is>
@@ -24142,7 +28620,7 @@
         </is>
       </c>
       <c r="U112" s="31" t="n">
-        <v>73</v>
+        <v>73.7</v>
       </c>
       <c r="V112" s="31" t="inlineStr">
         <is>
@@ -24150,7 +28628,7 @@
         </is>
       </c>
       <c r="W112" s="31" t="n">
-        <v>68.5</v>
+        <v>69.3</v>
       </c>
       <c r="X112" s="31" t="inlineStr">
         <is>
@@ -24200,7 +28678,7 @@
         </is>
       </c>
       <c r="H113" s="31" t="n">
-        <v>90.09999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="I113" s="31" t="inlineStr">
         <is>
@@ -24208,7 +28686,7 @@
         </is>
       </c>
       <c r="J113" s="31" t="n">
-        <v>63.4</v>
+        <v>63</v>
       </c>
       <c r="K113" s="31" t="inlineStr">
         <is>
@@ -24216,19 +28694,19 @@
         </is>
       </c>
       <c r="L113" s="31" t="n">
-        <v>72.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="M113" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N113" s="31" t="n">
-        <v>90.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O113" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P113" s="31" t="n">
-        <v>81.7</v>
+        <v>82.5</v>
       </c>
       <c r="Q113" s="31" t="inlineStr">
         <is>
@@ -24247,7 +28725,7 @@
         </is>
       </c>
       <c r="U113" s="31" t="n">
-        <v>72.8</v>
+        <v>73.2</v>
       </c>
       <c r="V113" s="31" t="inlineStr">
         <is>
@@ -24255,7 +28733,7 @@
         </is>
       </c>
       <c r="W113" s="31" t="n">
-        <v>74</v>
+        <v>74.5</v>
       </c>
       <c r="X113" s="31" t="inlineStr">
         <is>
@@ -24305,7 +28783,7 @@
         </is>
       </c>
       <c r="H114" s="31" t="n">
-        <v>73.2</v>
+        <v>73.7</v>
       </c>
       <c r="I114" s="31" t="inlineStr">
         <is>
@@ -24313,7 +28791,7 @@
         </is>
       </c>
       <c r="J114" s="31" t="n">
-        <v>46.6</v>
+        <v>43</v>
       </c>
       <c r="K114" s="31" t="inlineStr">
         <is>
@@ -24321,19 +28799,19 @@
         </is>
       </c>
       <c r="L114" s="31" t="n">
-        <v>73</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="M114" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N114" s="31" t="n">
-        <v>91.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="O114" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P114" s="31" t="n">
-        <v>82.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="Q114" s="31" t="inlineStr">
         <is>
@@ -24352,7 +28830,7 @@
         </is>
       </c>
       <c r="U114" s="31" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="V114" s="31" t="inlineStr">
         <is>
@@ -24360,7 +28838,7 @@
         </is>
       </c>
       <c r="W114" s="31" t="n">
-        <v>74</v>
+        <v>73.7</v>
       </c>
       <c r="X114" s="31" t="inlineStr">
         <is>
@@ -24410,7 +28888,7 @@
         </is>
       </c>
       <c r="H115" s="31" t="n">
-        <v>93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I115" s="31" t="inlineStr">
         <is>
@@ -24418,27 +28896,27 @@
         </is>
       </c>
       <c r="J115" s="31" t="n">
-        <v>70</v>
+        <v>69.2</v>
       </c>
       <c r="K115" s="31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L115" s="31" t="n">
         <v>72.90000000000001</v>
       </c>
       <c r="M115" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N115" s="31" t="n">
-        <v>94.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O115" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P115" s="31" t="n">
-        <v>83.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q115" s="31" t="inlineStr">
         <is>
@@ -24457,7 +28935,7 @@
         </is>
       </c>
       <c r="U115" s="31" t="n">
-        <v>73.2</v>
+        <v>73.5</v>
       </c>
       <c r="V115" s="31" t="inlineStr">
         <is>
@@ -24465,7 +28943,7 @@
         </is>
       </c>
       <c r="W115" s="31" t="n">
-        <v>75</v>
+        <v>75.3</v>
       </c>
       <c r="X115" s="31" t="inlineStr">
         <is>
@@ -24515,7 +28993,7 @@
         </is>
       </c>
       <c r="H116" s="31" t="n">
-        <v>81.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I116" s="31" t="inlineStr">
         <is>
@@ -24523,7 +29001,7 @@
         </is>
       </c>
       <c r="J116" s="31" t="n">
-        <v>55</v>
+        <v>55.4</v>
       </c>
       <c r="K116" s="31" t="inlineStr">
         <is>
@@ -24534,16 +29012,16 @@
         <v>73.40000000000001</v>
       </c>
       <c r="M116" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N116" s="31" t="n">
-        <v>89.8</v>
+        <v>91.8</v>
       </c>
       <c r="O116" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P116" s="31" t="n">
-        <v>81.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="Q116" s="31" t="inlineStr">
         <is>
@@ -24562,7 +29040,7 @@
         </is>
       </c>
       <c r="U116" s="31" t="n">
-        <v>71.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="V116" s="31" t="inlineStr">
         <is>
@@ -24570,7 +29048,7 @@
         </is>
       </c>
       <c r="W116" s="31" t="n">
-        <v>71.7</v>
+        <v>72.3</v>
       </c>
       <c r="X116" s="31" t="inlineStr">
         <is>
@@ -24620,7 +29098,7 @@
         </is>
       </c>
       <c r="H117" s="31" t="n">
-        <v>84.5</v>
+        <v>85.5</v>
       </c>
       <c r="I117" s="31" t="inlineStr">
         <is>
@@ -24628,7 +29106,7 @@
         </is>
       </c>
       <c r="J117" s="31" t="n">
-        <v>51.6</v>
+        <v>52.40000000000001</v>
       </c>
       <c r="K117" s="31" t="inlineStr">
         <is>
@@ -24636,19 +29114,19 @@
         </is>
       </c>
       <c r="L117" s="31" t="n">
-        <v>63</v>
+        <v>64.5</v>
       </c>
       <c r="M117" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N117" s="31" t="n">
-        <v>93.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="O117" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P117" s="31" t="n">
-        <v>78.5</v>
+        <v>79.8</v>
       </c>
       <c r="Q117" s="31" t="inlineStr">
         <is>
@@ -24667,15 +29145,15 @@
         </is>
       </c>
       <c r="U117" s="31" t="n">
-        <v>69.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V117" s="31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="W117" s="31" t="n">
-        <v>70.2</v>
+        <v>71</v>
       </c>
       <c r="X117" s="31" t="inlineStr">
         <is>
@@ -24684,7 +29162,7 @@
       </c>
       <c r="Y117" s="31" t="inlineStr">
         <is>
-          <t>Basic Competency</t>
+          <t>Progressing Candidates</t>
         </is>
       </c>
     </row>
@@ -24725,7 +29203,7 @@
         </is>
       </c>
       <c r="H118" s="31" t="n">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="I118" s="31" t="inlineStr">
         <is>
@@ -24733,7 +29211,7 @@
         </is>
       </c>
       <c r="J118" s="31" t="n">
-        <v>75</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K118" s="31" t="inlineStr">
         <is>
@@ -24741,19 +29219,19 @@
         </is>
       </c>
       <c r="L118" s="31" t="n">
-        <v>70</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M118" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N118" s="31" t="n">
-        <v>86.7</v>
+        <v>89.3</v>
       </c>
       <c r="O118" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P118" s="31" t="n">
-        <v>78.3</v>
+        <v>79.8</v>
       </c>
       <c r="Q118" s="31" t="inlineStr">
         <is>
@@ -24772,7 +29250,7 @@
         </is>
       </c>
       <c r="U118" s="31" t="n">
-        <v>67.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="V118" s="31" t="inlineStr">
         <is>
@@ -24780,7 +29258,7 @@
         </is>
       </c>
       <c r="W118" s="31" t="n">
-        <v>70.5</v>
+        <v>71.3</v>
       </c>
       <c r="X118" s="31" t="inlineStr">
         <is>
@@ -24830,7 +29308,7 @@
         </is>
       </c>
       <c r="H119" s="31" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I119" s="31" t="inlineStr">
         <is>
@@ -24838,7 +29316,7 @@
         </is>
       </c>
       <c r="J119" s="31" t="n">
-        <v>48.4</v>
+        <v>47.59999999999999</v>
       </c>
       <c r="K119" s="31" t="inlineStr">
         <is>
@@ -24846,19 +29324,19 @@
         </is>
       </c>
       <c r="L119" s="31" t="n">
-        <v>74.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="M119" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N119" s="31" t="n">
-        <v>89.8</v>
+        <v>91.8</v>
       </c>
       <c r="O119" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P119" s="31" t="n">
-        <v>82.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="Q119" s="31" t="inlineStr">
         <is>
@@ -24877,7 +29355,7 @@
         </is>
       </c>
       <c r="U119" s="31" t="n">
-        <v>72.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="V119" s="31" t="inlineStr">
         <is>
@@ -24885,7 +29363,7 @@
         </is>
       </c>
       <c r="W119" s="31" t="n">
-        <v>73.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="X119" s="31" t="inlineStr">
         <is>
@@ -24935,7 +29413,7 @@
         </is>
       </c>
       <c r="H120" s="31" t="n">
-        <v>63.4</v>
+        <v>65.8</v>
       </c>
       <c r="I120" s="31" t="inlineStr">
         <is>
@@ -24943,7 +29421,7 @@
         </is>
       </c>
       <c r="J120" s="31" t="n">
-        <v>25</v>
+        <v>27.6</v>
       </c>
       <c r="K120" s="31" t="inlineStr">
         <is>
@@ -24951,16 +29429,16 @@
         </is>
       </c>
       <c r="L120" s="31" t="n">
-        <v>73.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="M120" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N120" s="31" t="n">
-        <v>90.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O120" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P120" s="31" t="n">
         <v>81.90000000000001</v>
@@ -24990,7 +29468,7 @@
         </is>
       </c>
       <c r="W120" s="31" t="n">
-        <v>72</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="X120" s="31" t="inlineStr">
         <is>
@@ -25040,7 +29518,7 @@
         </is>
       </c>
       <c r="H121" s="31" t="n">
-        <v>95.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I121" s="31" t="inlineStr">
         <is>
@@ -25048,7 +29526,7 @@
         </is>
       </c>
       <c r="J121" s="31" t="n">
-        <v>65</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K121" s="31" t="inlineStr">
         <is>
@@ -25056,19 +29534,19 @@
         </is>
       </c>
       <c r="L121" s="31" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="M121" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N121" s="31" t="n">
-        <v>92.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="O121" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P121" s="31" t="n">
-        <v>83</v>
+        <v>83.8</v>
       </c>
       <c r="Q121" s="31" t="inlineStr">
         <is>
@@ -25087,7 +29565,7 @@
         </is>
       </c>
       <c r="U121" s="31" t="n">
-        <v>71.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="V121" s="31" t="inlineStr">
         <is>
@@ -25095,7 +29573,7 @@
         </is>
       </c>
       <c r="W121" s="31" t="n">
-        <v>73.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="X121" s="31" t="inlineStr">
         <is>
@@ -25145,7 +29623,7 @@
         </is>
       </c>
       <c r="H122" s="31" t="n">
-        <v>91.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I122" s="31" t="inlineStr">
         <is>
@@ -25153,7 +29631,7 @@
         </is>
       </c>
       <c r="J122" s="31" t="n">
-        <v>55</v>
+        <v>55.4</v>
       </c>
       <c r="K122" s="31" t="inlineStr">
         <is>
@@ -25161,19 +29639,19 @@
         </is>
       </c>
       <c r="L122" s="31" t="n">
-        <v>72.09999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="M122" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N122" s="31" t="n">
-        <v>90.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O122" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P122" s="31" t="n">
-        <v>81.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="Q122" s="31" t="inlineStr">
         <is>
@@ -25192,7 +29670,7 @@
         </is>
       </c>
       <c r="U122" s="31" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="V122" s="31" t="inlineStr">
         <is>
@@ -25200,7 +29678,7 @@
         </is>
       </c>
       <c r="W122" s="31" t="n">
-        <v>72.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="X122" s="31" t="inlineStr">
         <is>
@@ -25250,7 +29728,7 @@
         </is>
       </c>
       <c r="H123" s="31" t="n">
-        <v>87.3</v>
+        <v>88.2</v>
       </c>
       <c r="I123" s="31" t="inlineStr">
         <is>
@@ -25258,7 +29736,7 @@
         </is>
       </c>
       <c r="J123" s="31" t="n">
-        <v>36.6</v>
+        <v>38.4</v>
       </c>
       <c r="K123" s="31" t="inlineStr">
         <is>
@@ -25266,19 +29744,19 @@
         </is>
       </c>
       <c r="L123" s="31" t="n">
-        <v>68.09999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="M123" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N123" s="31" t="n">
-        <v>93.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="O123" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P123" s="31" t="n">
-        <v>81</v>
+        <v>81.8</v>
       </c>
       <c r="Q123" s="31" t="inlineStr">
         <is>
@@ -25297,7 +29775,7 @@
         </is>
       </c>
       <c r="U123" s="31" t="n">
-        <v>71.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V123" s="31" t="inlineStr">
         <is>
@@ -25305,7 +29783,7 @@
         </is>
       </c>
       <c r="W123" s="31" t="n">
-        <v>71</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="X123" s="31" t="inlineStr">
         <is>
@@ -25355,7 +29833,7 @@
         </is>
       </c>
       <c r="H124" s="31" t="n">
-        <v>95.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I124" s="31" t="inlineStr">
         <is>
@@ -25363,7 +29841,7 @@
         </is>
       </c>
       <c r="J124" s="31" t="n">
-        <v>56.6</v>
+        <v>57</v>
       </c>
       <c r="K124" s="31" t="inlineStr">
         <is>
@@ -25371,19 +29849,19 @@
         </is>
       </c>
       <c r="L124" s="31" t="n">
-        <v>72.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M124" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N124" s="31" t="n">
-        <v>89.8</v>
+        <v>91.8</v>
       </c>
       <c r="O124" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P124" s="31" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Q124" s="31" t="inlineStr">
         <is>
@@ -25402,7 +29880,7 @@
         </is>
       </c>
       <c r="U124" s="31" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V124" s="31" t="inlineStr">
         <is>
@@ -25410,7 +29888,7 @@
         </is>
       </c>
       <c r="W124" s="31" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="X124" s="31" t="inlineStr">
         <is>
@@ -25460,15 +29938,15 @@
         </is>
       </c>
       <c r="H125" s="31" t="n">
-        <v>69</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I125" s="31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J125" s="31" t="n">
-        <v>36.6</v>
+        <v>37</v>
       </c>
       <c r="K125" s="31" t="inlineStr">
         <is>
@@ -25476,19 +29954,19 @@
         </is>
       </c>
       <c r="L125" s="31" t="n">
-        <v>20.4</v>
+        <v>27.4</v>
       </c>
       <c r="M125" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N125" s="31" t="n">
-        <v>82.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="O125" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P125" s="31" t="n">
-        <v>51.5</v>
+        <v>56.8</v>
       </c>
       <c r="Q125" s="31" t="inlineStr">
         <is>
@@ -25507,7 +29985,7 @@
         </is>
       </c>
       <c r="U125" s="31" t="n">
-        <v>30.3</v>
+        <v>33.4</v>
       </c>
       <c r="V125" s="31" t="inlineStr">
         <is>
@@ -25515,7 +29993,7 @@
         </is>
       </c>
       <c r="W125" s="31" t="n">
-        <v>34.5</v>
+        <v>37.4</v>
       </c>
       <c r="X125" s="31" t="inlineStr">
         <is>
@@ -25565,7 +30043,7 @@
         </is>
       </c>
       <c r="H126" s="31" t="n">
-        <v>91.5</v>
+        <v>90.8</v>
       </c>
       <c r="I126" s="31" t="inlineStr">
         <is>
@@ -25581,23 +30059,23 @@
         </is>
       </c>
       <c r="L126" s="31" t="n">
-        <v>73.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="M126" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N126" s="31" t="n">
-        <v>42.2</v>
+        <v>49</v>
       </c>
       <c r="O126" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P126" s="31" t="n">
-        <v>58.1</v>
+        <v>61.5</v>
       </c>
       <c r="Q126" s="31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="R126" s="31" t="n">
@@ -25612,15 +30090,15 @@
         </is>
       </c>
       <c r="U126" s="31" t="n">
-        <v>58.9</v>
+        <v>60.9</v>
       </c>
       <c r="V126" s="31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W126" s="31" t="n">
-        <v>62.2</v>
+        <v>63.8</v>
       </c>
       <c r="X126" s="31" t="inlineStr">
         <is>
@@ -25629,7 +30107,7 @@
       </c>
       <c r="Y126" s="31" t="inlineStr">
         <is>
-          <t>Critical Intervention</t>
+          <t>Basic Competency</t>
         </is>
       </c>
     </row>
@@ -25686,23 +30164,23 @@
         </is>
       </c>
       <c r="L127" s="31" t="n">
-        <v>74</v>
+        <v>74.2</v>
       </c>
       <c r="M127" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N127" s="31" t="n">
-        <v>90.8</v>
+        <v>44.9</v>
       </c>
       <c r="O127" s="31" t="n">
         <v>4</v>
       </c>
       <c r="P127" s="31" t="n">
-        <v>82.40000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="Q127" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="R127" s="31" t="n">
@@ -25717,24 +30195,24 @@
         </is>
       </c>
       <c r="U127" s="31" t="n">
-        <v>72.8</v>
+        <v>59.3</v>
       </c>
       <c r="V127" s="31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="W127" s="31" t="n">
-        <v>75.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="X127" s="31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y127" s="31" t="inlineStr">
         <is>
-          <t>Progressing Candidates</t>
+          <t>Critical Intervention</t>
         </is>
       </c>
     </row>
@@ -25775,7 +30253,7 @@
         </is>
       </c>
       <c r="H128" s="31" t="n">
-        <v>87.3</v>
+        <v>86.8</v>
       </c>
       <c r="I128" s="31" t="inlineStr">
         <is>
@@ -25783,7 +30261,7 @@
         </is>
       </c>
       <c r="J128" s="31" t="n">
-        <v>65</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K128" s="31" t="inlineStr">
         <is>
@@ -25791,19 +30269,19 @@
         </is>
       </c>
       <c r="L128" s="31" t="n">
-        <v>72.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="M128" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N128" s="31" t="n">
-        <v>92.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="O128" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P128" s="31" t="n">
-        <v>82.8</v>
+        <v>83.7</v>
       </c>
       <c r="Q128" s="31" t="inlineStr">
         <is>
@@ -25822,7 +30300,7 @@
         </is>
       </c>
       <c r="U128" s="31" t="n">
-        <v>72.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="V128" s="31" t="inlineStr">
         <is>
@@ -25830,7 +30308,7 @@
         </is>
       </c>
       <c r="W128" s="31" t="n">
-        <v>73.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="X128" s="31" t="inlineStr">
         <is>
@@ -25880,7 +30358,7 @@
         </is>
       </c>
       <c r="H129" s="31" t="n">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="I129" s="31" t="inlineStr">
         <is>
@@ -25888,7 +30366,7 @@
         </is>
       </c>
       <c r="J129" s="31" t="n">
-        <v>75</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K129" s="31" t="inlineStr">
         <is>
@@ -25896,19 +30374,19 @@
         </is>
       </c>
       <c r="L129" s="31" t="n">
-        <v>74.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M129" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N129" s="31" t="n">
-        <v>93.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="O129" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P129" s="31" t="n">
-        <v>84.2</v>
+        <v>84.8</v>
       </c>
       <c r="Q129" s="31" t="inlineStr">
         <is>
@@ -25927,7 +30405,7 @@
         </is>
       </c>
       <c r="U129" s="31" t="n">
-        <v>74.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="V129" s="31" t="inlineStr">
         <is>
@@ -25935,7 +30413,7 @@
         </is>
       </c>
       <c r="W129" s="31" t="n">
-        <v>76.7</v>
+        <v>77</v>
       </c>
       <c r="X129" s="31" t="inlineStr">
         <is>
@@ -25985,7 +30463,7 @@
         </is>
       </c>
       <c r="H130" s="31" t="n">
-        <v>93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I130" s="31" t="inlineStr">
         <is>
@@ -25993,7 +30471,7 @@
         </is>
       </c>
       <c r="J130" s="31" t="n">
-        <v>45</v>
+        <v>44.6</v>
       </c>
       <c r="K130" s="31" t="inlineStr">
         <is>
@@ -26001,19 +30479,19 @@
         </is>
       </c>
       <c r="L130" s="31" t="n">
-        <v>73.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="M130" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N130" s="31" t="n">
-        <v>92.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="O130" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P130" s="31" t="n">
-        <v>83</v>
+        <v>83.2</v>
       </c>
       <c r="Q130" s="31" t="inlineStr">
         <is>
@@ -26032,7 +30510,7 @@
         </is>
       </c>
       <c r="U130" s="31" t="n">
-        <v>71.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="V130" s="31" t="inlineStr">
         <is>
@@ -26040,7 +30518,7 @@
         </is>
       </c>
       <c r="W130" s="31" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="X130" s="31" t="inlineStr">
         <is>
@@ -26090,7 +30568,7 @@
         </is>
       </c>
       <c r="H131" s="31" t="n">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="I131" s="31" t="inlineStr">
         <is>
@@ -26106,19 +30584,19 @@
         </is>
       </c>
       <c r="L131" s="31" t="n">
-        <v>74.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M131" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N131" s="31" t="n">
-        <v>94.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O131" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P131" s="31" t="n">
-        <v>84.5</v>
+        <v>85.2</v>
       </c>
       <c r="Q131" s="31" t="inlineStr">
         <is>
@@ -26137,7 +30615,7 @@
         </is>
       </c>
       <c r="U131" s="31" t="n">
-        <v>74.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="V131" s="31" t="inlineStr">
         <is>
@@ -26145,7 +30623,7 @@
         </is>
       </c>
       <c r="W131" s="31" t="n">
-        <v>75.8</v>
+        <v>76.2</v>
       </c>
       <c r="X131" s="31" t="inlineStr">
         <is>
@@ -26195,7 +30673,7 @@
         </is>
       </c>
       <c r="H132" s="31" t="n">
-        <v>73.2</v>
+        <v>75</v>
       </c>
       <c r="I132" s="31" t="inlineStr">
         <is>
@@ -26211,19 +30689,19 @@
         </is>
       </c>
       <c r="L132" s="31" t="n">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="M132" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N132" s="31" t="n">
-        <v>81.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="O132" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P132" s="31" t="n">
-        <v>76.5</v>
+        <v>78.3</v>
       </c>
       <c r="Q132" s="31" t="inlineStr">
         <is>
@@ -26242,7 +30720,7 @@
         </is>
       </c>
       <c r="U132" s="31" t="n">
-        <v>68.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="V132" s="31" t="inlineStr">
         <is>
@@ -26250,7 +30728,7 @@
         </is>
       </c>
       <c r="W132" s="31" t="n">
-        <v>68.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="X132" s="31" t="inlineStr">
         <is>
@@ -26300,7 +30778,7 @@
         </is>
       </c>
       <c r="H133" s="31" t="n">
-        <v>95.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I133" s="31" t="inlineStr">
         <is>
@@ -26316,19 +30794,19 @@
         </is>
       </c>
       <c r="L133" s="31" t="n">
-        <v>72.7</v>
+        <v>72.8</v>
       </c>
       <c r="M133" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N133" s="31" t="n">
-        <v>93.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="O133" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P133" s="31" t="n">
-        <v>83.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Q133" s="31" t="inlineStr">
         <is>
@@ -26347,7 +30825,7 @@
         </is>
       </c>
       <c r="U133" s="31" t="n">
-        <v>72.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="V133" s="31" t="inlineStr">
         <is>
@@ -26355,7 +30833,7 @@
         </is>
       </c>
       <c r="W133" s="31" t="n">
-        <v>73.8</v>
+        <v>74.2</v>
       </c>
       <c r="X133" s="31" t="inlineStr">
         <is>
@@ -26405,7 +30883,7 @@
         </is>
       </c>
       <c r="H134" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="I134" s="31" t="inlineStr">
         <is>
@@ -26413,7 +30891,7 @@
         </is>
       </c>
       <c r="J134" s="31" t="n">
-        <v>45</v>
+        <v>46.2</v>
       </c>
       <c r="K134" s="31" t="inlineStr">
         <is>
@@ -26421,19 +30899,19 @@
         </is>
       </c>
       <c r="L134" s="31" t="n">
-        <v>71.7</v>
+        <v>71</v>
       </c>
       <c r="M134" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N134" s="31" t="n">
-        <v>82.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="O134" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P134" s="31" t="n">
-        <v>77.2</v>
+        <v>78.5</v>
       </c>
       <c r="Q134" s="31" t="inlineStr">
         <is>
@@ -26452,24 +30930,24 @@
         </is>
       </c>
       <c r="U134" s="31" t="n">
-        <v>69.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="V134" s="31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="W134" s="31" t="n">
-        <v>69.7</v>
+        <v>70.5</v>
       </c>
       <c r="X134" s="31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y134" s="31" t="inlineStr">
         <is>
-          <t>Basic Competency</t>
+          <t>Progressing Candidates</t>
         </is>
       </c>
     </row>
@@ -26529,7 +31007,7 @@
         <v>58.1</v>
       </c>
       <c r="M135" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N135" s="31" t="n">
         <v>95.90000000000001</v>
@@ -26634,7 +31112,7 @@
         <v>81.3</v>
       </c>
       <c r="M136" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N136" s="31" t="n">
         <v>96</v>
@@ -26739,7 +31217,7 @@
         <v>80.8</v>
       </c>
       <c r="M137" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N137" s="31" t="n">
         <v>92.40000000000001</v>
@@ -26844,7 +31322,7 @@
         <v>77.2</v>
       </c>
       <c r="M138" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N138" s="31" t="n">
         <v>98.59999999999999</v>
@@ -26949,7 +31427,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="M139" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N139" s="31" t="n">
         <v>99.3</v>
@@ -27054,7 +31532,7 @@
         <v>80.5</v>
       </c>
       <c r="M140" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N140" s="31" t="n">
         <v>97.5</v>
@@ -27159,7 +31637,7 @@
         <v>77</v>
       </c>
       <c r="M141" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N141" s="31" t="n">
         <v>96</v>
@@ -27264,7 +31742,7 @@
         <v>70.7</v>
       </c>
       <c r="M142" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N142" s="31" t="n">
         <v>94.59999999999999</v>
@@ -27369,7 +31847,7 @@
         <v>74.59999999999999</v>
       </c>
       <c r="M143" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N143" s="31" t="n">
         <v>95.90000000000001</v>
@@ -27474,7 +31952,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="M144" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N144" s="31" t="n">
         <v>99.09999999999999</v>
@@ -27579,7 +32057,7 @@
         <v>81.2</v>
       </c>
       <c r="M145" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N145" s="31" t="n">
         <v>98.2</v>
@@ -27684,7 +32162,7 @@
         <v>82.3</v>
       </c>
       <c r="M146" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N146" s="31" t="n">
         <v>96.3</v>
@@ -27789,7 +32267,7 @@
         <v>79.8</v>
       </c>
       <c r="M147" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N147" s="31" t="n">
         <v>99.40000000000001</v>
@@ -27894,7 +32372,7 @@
         <v>80.3</v>
       </c>
       <c r="M148" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N148" s="31" t="n">
         <v>99.09999999999999</v>
@@ -27999,7 +32477,7 @@
         <v>76</v>
       </c>
       <c r="M149" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N149" s="31" t="n">
         <v>96.7</v>
@@ -28104,7 +32582,7 @@
         <v>75.40000000000001</v>
       </c>
       <c r="M150" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N150" s="31" t="n">
         <v>93.40000000000001</v>
@@ -28209,7 +32687,7 @@
         <v>80.7</v>
       </c>
       <c r="M151" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N151" s="31" t="n">
         <v>95.59999999999999</v>
@@ -28314,7 +32792,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="M152" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N152" s="31" t="n">
         <v>97.90000000000001</v>
@@ -28419,7 +32897,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="M153" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N153" s="31" t="n">
         <v>97.5</v>
@@ -28505,7 +32983,7 @@
         </is>
       </c>
       <c r="H154" s="31" t="n">
-        <v>88.7</v>
+        <v>89.5</v>
       </c>
       <c r="I154" s="31" t="inlineStr">
         <is>
@@ -28513,7 +32991,7 @@
         </is>
       </c>
       <c r="J154" s="31" t="n">
-        <v>53.4</v>
+        <v>52.40000000000001</v>
       </c>
       <c r="K154" s="31" t="inlineStr">
         <is>
@@ -28521,19 +32999,19 @@
         </is>
       </c>
       <c r="L154" s="31" t="n">
-        <v>73.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="M154" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N154" s="31" t="n">
-        <v>35</v>
+        <v>42.6</v>
       </c>
       <c r="O154" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P154" s="31" t="n">
-        <v>54.1</v>
+        <v>57.2</v>
       </c>
       <c r="Q154" s="31" t="inlineStr">
         <is>
@@ -28552,7 +33030,7 @@
         </is>
       </c>
       <c r="U154" s="31" t="n">
-        <v>54.1</v>
+        <v>55.9</v>
       </c>
       <c r="V154" s="31" t="inlineStr">
         <is>
@@ -28560,7 +33038,7 @@
         </is>
       </c>
       <c r="W154" s="31" t="n">
-        <v>57.5</v>
+        <v>59.1</v>
       </c>
       <c r="X154" s="31" t="inlineStr">
         <is>
@@ -28629,7 +33107,7 @@
         <v>69.7</v>
       </c>
       <c r="M155" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N155" s="31" t="n">
         <v>95.7</v>
@@ -28734,7 +33212,7 @@
         <v>82.3</v>
       </c>
       <c r="M156" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N156" s="31" t="n">
         <v>96.7</v>
@@ -28839,7 +33317,7 @@
         <v>81.7</v>
       </c>
       <c r="M157" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N157" s="31" t="n">
         <v>95.5</v>
@@ -28944,7 +33422,7 @@
         <v>81.5</v>
       </c>
       <c r="M158" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N158" s="31" t="n">
         <v>95.40000000000001</v>
@@ -29049,7 +33527,7 @@
         <v>76.2</v>
       </c>
       <c r="M159" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N159" s="31" t="n">
         <v>97.09999999999999</v>
@@ -29154,7 +33632,7 @@
         <v>77.8</v>
       </c>
       <c r="M160" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N160" s="31" t="n">
         <v>98.3</v>
@@ -29259,7 +33737,7 @@
         <v>80.8</v>
       </c>
       <c r="M161" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N161" s="31" t="n">
         <v>96.2</v>
@@ -29364,7 +33842,7 @@
         <v>80.7</v>
       </c>
       <c r="M162" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N162" s="31" t="n">
         <v>95.5</v>
@@ -29458,7 +33936,7 @@
         </is>
       </c>
       <c r="J163" s="31" t="n">
-        <v>71.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K163" s="31" t="inlineStr">
         <is>
@@ -29466,19 +33944,19 @@
         </is>
       </c>
       <c r="L163" s="31" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M163" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N163" s="31" t="n">
-        <v>91.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="O163" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P163" s="31" t="n">
-        <v>82.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="Q163" s="31" t="inlineStr">
         <is>
@@ -29497,7 +33975,7 @@
         </is>
       </c>
       <c r="U163" s="31" t="n">
-        <v>73.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="V163" s="31" t="inlineStr">
         <is>
@@ -29505,7 +33983,7 @@
         </is>
       </c>
       <c r="W163" s="31" t="n">
-        <v>75.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="X163" s="31" t="inlineStr">
         <is>
@@ -29574,7 +34052,7 @@
         <v>81</v>
       </c>
       <c r="M164" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N164" s="31" t="n">
         <v>95.40000000000001</v>
@@ -29679,7 +34157,7 @@
         <v>81.5</v>
       </c>
       <c r="M165" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N165" s="31" t="n">
         <v>98.7</v>
@@ -29784,7 +34262,7 @@
         <v>81.7</v>
       </c>
       <c r="M166" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N166" s="31" t="n">
         <v>98.7</v>
@@ -29889,7 +34367,7 @@
         <v>71.2</v>
       </c>
       <c r="M167" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N167" s="31" t="n">
         <v>94.7</v>
@@ -29994,7 +34472,7 @@
         <v>73.8</v>
       </c>
       <c r="M168" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N168" s="31" t="n">
         <v>98.59999999999999</v>
@@ -30099,7 +34577,7 @@
         <v>82</v>
       </c>
       <c r="M169" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N169" s="31" t="n">
         <v>95</v>
@@ -30204,7 +34682,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="M170" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N170" s="31" t="n">
         <v>95</v>
@@ -30290,7 +34768,7 @@
         </is>
       </c>
       <c r="H171" s="31" t="n">
-        <v>95.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I171" s="31" t="inlineStr">
         <is>
@@ -30298,7 +34776,7 @@
         </is>
       </c>
       <c r="J171" s="31" t="n">
-        <v>63.4</v>
+        <v>63</v>
       </c>
       <c r="K171" s="31" t="inlineStr">
         <is>
@@ -30306,19 +34784,19 @@
         </is>
       </c>
       <c r="L171" s="31" t="n">
-        <v>71.3</v>
+        <v>71.2</v>
       </c>
       <c r="M171" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N171" s="31" t="n">
-        <v>39.3</v>
+        <v>46.5</v>
       </c>
       <c r="O171" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P171" s="31" t="n">
-        <v>55.3</v>
+        <v>58.9</v>
       </c>
       <c r="Q171" s="31" t="inlineStr">
         <is>
@@ -30337,7 +34815,7 @@
         </is>
       </c>
       <c r="U171" s="31" t="n">
-        <v>54.8</v>
+        <v>56.9</v>
       </c>
       <c r="V171" s="31" t="inlineStr">
         <is>
@@ -30345,11 +34823,11 @@
         </is>
       </c>
       <c r="W171" s="31" t="n">
-        <v>59.3</v>
+        <v>61.1</v>
       </c>
       <c r="X171" s="31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y171" s="31" t="inlineStr">
@@ -30414,7 +34892,7 @@
         <v>77</v>
       </c>
       <c r="M172" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N172" s="31" t="n">
         <v>89.90000000000001</v>
@@ -30519,7 +34997,7 @@
         <v>75.8</v>
       </c>
       <c r="M173" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N173" s="31" t="n">
         <v>91.3</v>
@@ -30624,7 +35102,7 @@
         <v>67.2</v>
       </c>
       <c r="M174" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N174" s="31" t="n">
         <v>71.90000000000001</v>
@@ -30685,13 +35163,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
+    <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30715,6 +35208,26 @@
           <t>Average Overall Performance Score</t>
         </is>
       </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Deployable Candidates</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Progressing Candidates</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Basic Competency</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Critical Intervention</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="31" t="inlineStr">
@@ -30731,6 +35244,48 @@
       <c r="D2" s="31" t="n">
         <v>85</v>
       </c>
+      <c r="E2" s="31" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Attendance Week</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Batch 1 - JAVA Batch</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Batch 2 - Pytest Batch</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Batch 3 - Robot Python</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Batch 4 - Playwright</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Batch 5 - Dotnet</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="31" t="inlineStr">
@@ -30747,6 +35302,38 @@
       <c r="D3" s="31" t="n">
         <v>78.09999999999999</v>
       </c>
+      <c r="E3" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="31" t="n">
+        <v>23</v>
+      </c>
+      <c r="G3" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>100</v>
+      </c>
+      <c r="V3" t="n">
+        <v>100</v>
+      </c>
+      <c r="W3" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -30763,6 +35350,38 @@
       <c r="D4" s="31" t="n">
         <v>79.8</v>
       </c>
+      <c r="E4" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="31" t="n">
+        <v>34</v>
+      </c>
+      <c r="G4" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Week 10</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="V4" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="W4" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="X4" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>81.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
@@ -30779,6 +35398,38 @@
       <c r="D5" s="31" t="n">
         <v>86.59999999999999</v>
       </c>
+      <c r="E5" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="F5" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Week 11</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="V5" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>100</v>
+      </c>
+      <c r="X5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
@@ -30794,6 +35445,514 @@
       </c>
       <c r="D6" s="31" t="n">
         <v>82.59999999999999</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>100</v>
+      </c>
+      <c r="W7" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="X7" t="n">
+        <v>99</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>97.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Week 14</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>87</v>
+      </c>
+      <c r="V8" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="W8" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="X8" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Week 16</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="V9" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="W9" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="X9" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Week 18</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="V10" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="W10" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Week 19</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>99</v>
+      </c>
+      <c r="W11" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>96.90000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>100</v>
+      </c>
+      <c r="V12" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="X12" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>98.59999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Week 20</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="V13" t="n">
+        <v>100</v>
+      </c>
+      <c r="W13" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Week 21</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>100</v>
+      </c>
+      <c r="V14" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Week 22</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="V15" t="n">
+        <v>99</v>
+      </c>
+      <c r="W15" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="X15" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Week 23</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="V16" t="n">
+        <v>99</v>
+      </c>
+      <c r="W16" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="X16" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>96.90000000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Week 25</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="V17" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="X17" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>93.09999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Week 26</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="V18" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="X18" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>94.40000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="X19" t="n">
+        <v>98</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="V20" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="W20" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="X20" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>90.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>100</v>
+      </c>
+      <c r="V21" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="X21" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>100</v>
+      </c>
+      <c r="W22" t="n">
+        <v>100</v>
+      </c>
+      <c r="X22" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="V23" t="n">
+        <v>95</v>
+      </c>
+      <c r="W23" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="X23" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Assessment Week</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="W24" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="X24" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>97.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="V25" t="n">
+        <v>100</v>
+      </c>
+      <c r="W25" t="n">
+        <v>100</v>
+      </c>
+      <c r="X25" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>77.09999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
+        <v>79.09999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>75.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>72.90000000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>66.59999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/test/published_reports/pmq_client_dashboard.xlsx
+++ b/test/published_reports/pmq_client_dashboard.xlsx
@@ -17,10 +17,6 @@
     <sheet name="executive_roster" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="jecrc_batch_performance" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="galgotias_batch_performance" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="college_batch_weekly_performance" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="college_track_weekly_performance" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="college_weekly_signal_counts" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="college_batch_weekly_attendance" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -620,9 +616,6 @@
             </numRef>
           </val>
         </ser>
-        <dLbls>
-          <showVal val="1"/>
-        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -642,204 +635,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Batch</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-          <max val="100"/>
-          <min val="0"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Average Attendance Percentage</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>JECRC Batch-wise Performance Bucket Mix</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="stacked"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'jecrc_batch_performance'!E1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="10B981"/>
-            </a:solidFill>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'jecrc_batch_performance'!$A$2:$A$6</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'jecrc_batch_performance'!$E$2:$E$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'jecrc_batch_performance'!F1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="7C3AED"/>
-            </a:solidFill>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'jecrc_batch_performance'!$A$2:$A$6</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'jecrc_batch_performance'!$F$2:$F$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'jecrc_batch_performance'!G1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="0EA5E9"/>
-            </a:solidFill>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'jecrc_batch_performance'!$A$2:$A$6</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'jecrc_batch_performance'!$G$2:$G$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'jecrc_batch_performance'!H1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="EF4444"/>
-            </a:solidFill>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'jecrc_batch_performance'!$A$2:$A$6</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'jecrc_batch_performance'!$H$2:$H$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="100"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Student Count</a:t>
+                  <a:t>JECRC Batches</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -866,7 +662,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Batch</a:t>
+                  <a:t>Attendance %</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -878,7 +674,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="b"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -886,8 +682,9 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -898,21 +695,23 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>JECRC Week-on-Week Attendance Progress</a:t>
+              <a:t>JECRC Batch-wise Average Overall Performance</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'jecrc_batch_performance'!U2</f>
+              <f>'jecrc_batch_performance'!D1</f>
             </strRef>
           </tx>
           <spPr>
@@ -920,156 +719,76 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
+          <dPt>
+            <idx val="0"/>
             <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1D4ED8"/>
+              </a:solidFill>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
-          </marker>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="7C3AED"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="0EA5E9"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="10B981"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="F59E0B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'jecrc_batch_performance'!$T$3:$T$25</f>
+              <f>'jecrc_batch_performance'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'jecrc_batch_performance'!$U$3:$U$25</f>
+              <f>'jecrc_batch_performance'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'jecrc_batch_performance'!V2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'jecrc_batch_performance'!$T$3:$T$25</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'jecrc_batch_performance'!$V$3:$V$25</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'jecrc_batch_performance'!W2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'jecrc_batch_performance'!$T$3:$T$25</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'jecrc_batch_performance'!$W$3:$W$25</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'jecrc_batch_performance'!X2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'jecrc_batch_performance'!$T$3:$T$25</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'jecrc_batch_performance'!$X$3:$X$25</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'jecrc_batch_performance'!Y2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'jecrc_batch_performance'!$T$3:$T$25</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'jecrc_batch_performance'!$Y$3:$Y$25</f>
-            </numRef>
-          </val>
-        </ser>
+        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
-      </lineChart>
+      </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -1085,7 +804,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Week</a:t>
+                  <a:t>JECRC Batches</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1100,8 +819,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="100"/>
-          <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -1114,7 +831,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Average Attendance Percentage</a:t>
+                  <a:t>Overall Performance Score</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1126,7 +843,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="b"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1134,127 +851,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>JECRC Week-on-Week Performance Progress</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'jecrc_batch_performance'!U24</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'jecrc_batch_performance'!$T$25:$T$31</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'jecrc_batch_performance'!$U$25:$U$31</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Week</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-          <max val="100"/>
-          <min val="0"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Average Score</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
@@ -1347,8 +944,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="100"/>
-          <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -1381,7 +976,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="11"/>
   <chart>
@@ -1474,8 +1069,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="100"/>
-          <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -1539,12 +1132,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3060000"/>
+    <ext cx="3960000" cy="2700000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1561,12 +1154,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3420000"/>
+    <ext cx="3960000" cy="2700000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1576,50 +1169,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5040000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>55</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5040000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3282,4033 +2831,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000EA5E9"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>College</t>
-        </is>
-      </c>
-      <c r="B1" s="28" t="inlineStr">
-        <is>
-          <t>Assigned Batch</t>
-        </is>
-      </c>
-      <c r="C1" s="28" t="inlineStr">
-        <is>
-          <t>Assessment Week</t>
-        </is>
-      </c>
-      <c r="D1" s="28" t="inlineStr">
-        <is>
-          <t>Average Score</t>
-        </is>
-      </c>
-      <c r="E1" s="28" t="inlineStr">
-        <is>
-          <t>Submission Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B2" s="31" t="inlineStr"/>
-      <c r="C2" s="31" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="D2" s="31" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="E2" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B3" s="31" t="inlineStr"/>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="D3" s="31" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="E3" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="inlineStr"/>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="E4" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr"/>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="E5" s="31" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="inlineStr"/>
-      <c r="C6" s="31" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="E6" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="inlineStr"/>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="D7" s="31" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="E7" s="31" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="inlineStr"/>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="D8" s="31" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="E8" s="31" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr"/>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="D9" s="31" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="E9" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr"/>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="E10" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="inlineStr"/>
-      <c r="C11" s="31" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="D11" s="31" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="E11" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B12" s="31" t="inlineStr"/>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="D12" s="31" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="E12" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B13" s="31" t="inlineStr"/>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="E13" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B14" s="31" t="inlineStr"/>
-      <c r="C14" s="31" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="D14" s="31" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="E14" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="inlineStr"/>
-      <c r="C15" s="31" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="E15" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr"/>
-      <c r="C16" s="31" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="D16" s="31" t="n">
-        <v>69</v>
-      </c>
-      <c r="E16" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="007C3AED"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>College</t>
-        </is>
-      </c>
-      <c r="B1" s="28" t="inlineStr">
-        <is>
-          <t>Track</t>
-        </is>
-      </c>
-      <c r="C1" s="28" t="inlineStr">
-        <is>
-          <t>Assessment Week</t>
-        </is>
-      </c>
-      <c r="D1" s="28" t="inlineStr">
-        <is>
-          <t>Average Score</t>
-        </is>
-      </c>
-      <c r="E1" s="28" t="inlineStr">
-        <is>
-          <t>Submission Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B2" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C2" s="31" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="D2" s="31" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="E2" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B3" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="D3" s="31" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="E3" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="E4" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="E5" s="31" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C6" s="31" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="E6" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="D7" s="31" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="E7" s="31" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="D8" s="31" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="E8" s="31" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>Assignment</t>
-        </is>
-      </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="D9" s="31" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="E9" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>Assignment</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Second</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="E10" s="31" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C11" s="31" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="D11" s="31" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="E11" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="D12" s="31" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="E12" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B13" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="E13" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C14" s="31" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="D14" s="31" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="E14" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C15" s="31" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="E15" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="D16" s="31" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="E16" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C17" s="31" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="E17" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-      <c r="C18" s="31" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="D18" s="31" t="n">
-        <v>69</v>
-      </c>
-      <c r="E18" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B19" s="31" t="inlineStr">
-        <is>
-          <t>Assignment</t>
-        </is>
-      </c>
-      <c r="C19" s="31" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="D19" s="31" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="E19" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>College</t>
-        </is>
-      </c>
-      <c r="B1" s="28" t="inlineStr">
-        <is>
-          <t>Assessment Week</t>
-        </is>
-      </c>
-      <c r="C1" s="28" t="inlineStr">
-        <is>
-          <t>Assessments Done</t>
-        </is>
-      </c>
-      <c r="D1" s="28" t="inlineStr">
-        <is>
-          <t>Assignments Done</t>
-        </is>
-      </c>
-      <c r="E1" s="28" t="inlineStr">
-        <is>
-          <t>Trainer Feedback Provided</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B2" s="31" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="C2" s="31" t="n">
-        <v>140</v>
-      </c>
-      <c r="D2" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B3" s="31" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="C3" s="31" t="n">
-        <v>140</v>
-      </c>
-      <c r="D3" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="n">
-        <v>140</v>
-      </c>
-      <c r="D4" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="n">
-        <v>139</v>
-      </c>
-      <c r="D5" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="31" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C6" s="31" t="n">
-        <v>140</v>
-      </c>
-      <c r="D6" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="n">
-        <v>81</v>
-      </c>
-      <c r="D7" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="31" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="C8" s="31" t="n">
-        <v>47</v>
-      </c>
-      <c r="D8" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="31" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="C9" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="31" t="n">
-        <v>140</v>
-      </c>
-      <c r="E9" s="31" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>Second</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="31" t="n">
-        <v>23</v>
-      </c>
-      <c r="E10" s="31" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="C11" s="31" t="n">
-        <v>33</v>
-      </c>
-      <c r="D11" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="C12" s="31" t="n">
-        <v>33</v>
-      </c>
-      <c r="D12" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B13" s="31" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="n">
-        <v>33</v>
-      </c>
-      <c r="D13" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C14" s="31" t="n">
-        <v>33</v>
-      </c>
-      <c r="D14" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C15" s="31" t="n">
-        <v>33</v>
-      </c>
-      <c r="D15" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="n">
-        <v>33</v>
-      </c>
-      <c r="D16" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="C17" s="31" t="n">
-        <v>33</v>
-      </c>
-      <c r="D17" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="C18" s="31" t="n">
-        <v>33</v>
-      </c>
-      <c r="D18" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B19" s="31" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="C19" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="31" t="n">
-        <v>33</v>
-      </c>
-      <c r="E19" s="31" t="n">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0010B981"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D139"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>College</t>
-        </is>
-      </c>
-      <c r="B1" s="28" t="inlineStr">
-        <is>
-          <t>Assigned Batch</t>
-        </is>
-      </c>
-      <c r="C1" s="28" t="inlineStr">
-        <is>
-          <t>Attendance Week</t>
-        </is>
-      </c>
-      <c r="D1" s="28" t="inlineStr">
-        <is>
-          <t>Average Attendance %</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B2" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C2" s="31" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="D2" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B3" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="D3" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="n">
-        <v>99.3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="n">
-        <v>97.40000000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C6" s="31" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="D7" s="31" t="n">
-        <v>91.3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="D8" s="31" t="n">
-        <v>99.09999999999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="D9" s="31" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Week 9</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="n">
-        <v>82.59999999999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C11" s="31" t="inlineStr">
-        <is>
-          <t>Week 10</t>
-        </is>
-      </c>
-      <c r="D11" s="31" t="n">
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="D12" s="31" t="n">
-        <v>99.09999999999999</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B13" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="n">
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C14" s="31" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="D14" s="31" t="n">
-        <v>94.2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C15" s="31" t="inlineStr">
-        <is>
-          <t>Week 14</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="inlineStr">
-        <is>
-          <t>Week 16</t>
-        </is>
-      </c>
-      <c r="D16" s="31" t="n">
-        <v>84.09999999999999</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C17" s="31" t="inlineStr">
-        <is>
-          <t>Week 18</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="n">
-        <v>98.90000000000001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C18" s="31" t="inlineStr">
-        <is>
-          <t>Week 19</t>
-        </is>
-      </c>
-      <c r="D18" s="31" t="n">
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B19" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C19" s="31" t="inlineStr">
-        <is>
-          <t>Week 20</t>
-        </is>
-      </c>
-      <c r="D19" s="31" t="n">
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C20" s="31" t="inlineStr">
-        <is>
-          <t>Week 21</t>
-        </is>
-      </c>
-      <c r="D20" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>Week 22</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="n">
-        <v>98.90000000000001</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B22" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>Week 23</t>
-        </is>
-      </c>
-      <c r="D22" s="31" t="n">
-        <v>94.59999999999999</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B23" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C23" s="31" t="inlineStr">
-        <is>
-          <t>Week 25</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="n">
-        <v>89.90000000000001</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B24" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="C24" s="31" t="inlineStr">
-        <is>
-          <t>Week 26</t>
-        </is>
-      </c>
-      <c r="D24" s="31" t="n">
-        <v>98.59999999999999</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B25" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C25" s="31" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B26" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C26" s="31" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="D26" s="31" t="n">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B27" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C27" s="31" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="D27" s="31" t="n">
-        <v>97.2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B28" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C28" s="31" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="D28" s="31" t="n">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B29" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C29" s="31" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="D29" s="31" t="n">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B30" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C30" s="31" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="D30" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B31" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C31" s="31" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="D31" s="31" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B32" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C32" s="31" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="D32" s="31" t="n">
-        <v>98.59999999999999</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C33" s="31" t="inlineStr">
-        <is>
-          <t>Week 9</t>
-        </is>
-      </c>
-      <c r="D33" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B34" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C34" s="31" t="inlineStr">
-        <is>
-          <t>Week 10</t>
-        </is>
-      </c>
-      <c r="D34" s="31" t="n">
-        <v>93.8</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B35" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C35" s="31" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="D35" s="31" t="n">
-        <v>99.2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B36" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C36" s="31" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="D36" s="31" t="n">
-        <v>99.2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B37" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C37" s="31" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="D37" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B38" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C38" s="31" t="inlineStr">
-        <is>
-          <t>Week 14</t>
-        </is>
-      </c>
-      <c r="D38" s="31" t="n">
-        <v>70.8</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B39" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C39" s="31" t="inlineStr">
-        <is>
-          <t>Week 16</t>
-        </is>
-      </c>
-      <c r="D39" s="31" t="n">
-        <v>93.09999999999999</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B40" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C40" s="31" t="inlineStr">
-        <is>
-          <t>Week 18</t>
-        </is>
-      </c>
-      <c r="D40" s="31" t="n">
-        <v>97.90000000000001</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B41" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C41" s="31" t="inlineStr">
-        <is>
-          <t>Week 19</t>
-        </is>
-      </c>
-      <c r="D41" s="31" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B42" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C42" s="31" t="inlineStr">
-        <is>
-          <t>Week 20</t>
-        </is>
-      </c>
-      <c r="D42" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B43" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C43" s="31" t="inlineStr">
-        <is>
-          <t>Week 21</t>
-        </is>
-      </c>
-      <c r="D43" s="31" t="n">
-        <v>87.5</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B44" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C44" s="31" t="inlineStr">
-        <is>
-          <t>Week 22</t>
-        </is>
-      </c>
-      <c r="D44" s="31" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B45" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C45" s="31" t="inlineStr">
-        <is>
-          <t>Week 23</t>
-        </is>
-      </c>
-      <c r="D45" s="31" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B46" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C46" s="31" t="inlineStr">
-        <is>
-          <t>Week 25</t>
-        </is>
-      </c>
-      <c r="D46" s="31" t="n">
-        <v>97.2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B47" s="31" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="C47" s="31" t="inlineStr">
-        <is>
-          <t>Week 26</t>
-        </is>
-      </c>
-      <c r="D47" s="31" t="n">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B48" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C48" s="31" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="D48" s="31" t="n">
-        <v>94.3</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B49" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C49" s="31" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="D49" s="31" t="n">
-        <v>98.09999999999999</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B50" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C50" s="31" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="D50" s="31" t="n">
-        <v>98.09999999999999</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B51" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C51" s="31" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="D51" s="31" t="n">
-        <v>95.40000000000001</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B52" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C52" s="31" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="D52" s="31" t="n">
-        <v>94.3</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B53" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C53" s="31" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="D53" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B54" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C54" s="31" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="D54" s="31" t="n">
-        <v>99.40000000000001</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B55" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C55" s="31" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="D55" s="31" t="n">
-        <v>93.8</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B56" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C56" s="31" t="inlineStr">
-        <is>
-          <t>Week 9</t>
-        </is>
-      </c>
-      <c r="D56" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B57" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C57" s="31" t="inlineStr">
-        <is>
-          <t>Week 10</t>
-        </is>
-      </c>
-      <c r="D57" s="31" t="n">
-        <v>91.40000000000001</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B58" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C58" s="31" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="D58" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B59" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C59" s="31" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="D59" s="31" t="n">
-        <v>98.3</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B60" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C60" s="31" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="D60" s="31" t="n">
-        <v>97.09999999999999</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B61" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C61" s="31" t="inlineStr">
-        <is>
-          <t>Week 14</t>
-        </is>
-      </c>
-      <c r="D61" s="31" t="n">
-        <v>85.7</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B62" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C62" s="31" t="inlineStr">
-        <is>
-          <t>Week 16</t>
-        </is>
-      </c>
-      <c r="D62" s="31" t="n">
-        <v>88.59999999999999</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B63" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C63" s="31" t="inlineStr">
-        <is>
-          <t>Week 18</t>
-        </is>
-      </c>
-      <c r="D63" s="31" t="n">
-        <v>94.3</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B64" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C64" s="31" t="inlineStr">
-        <is>
-          <t>Week 19</t>
-        </is>
-      </c>
-      <c r="D64" s="31" t="n">
-        <v>94.3</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B65" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C65" s="31" t="inlineStr">
-        <is>
-          <t>Week 20</t>
-        </is>
-      </c>
-      <c r="D65" s="31" t="n">
-        <v>94.3</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B66" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C66" s="31" t="inlineStr">
-        <is>
-          <t>Week 21</t>
-        </is>
-      </c>
-      <c r="D66" s="31" t="n">
-        <v>94.3</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B67" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C67" s="31" t="inlineStr">
-        <is>
-          <t>Week 22</t>
-        </is>
-      </c>
-      <c r="D67" s="31" t="n">
-        <v>92.90000000000001</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B68" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C68" s="31" t="inlineStr">
-        <is>
-          <t>Week 23</t>
-        </is>
-      </c>
-      <c r="D68" s="31" t="n">
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C69" s="31" t="inlineStr">
-        <is>
-          <t>Week 25</t>
-        </is>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>97.09999999999999</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="C70" s="31" t="inlineStr">
-        <is>
-          <t>Week 26</t>
-        </is>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>97.09999999999999</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B71" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C71" s="31" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B72" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C72" s="31" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="D72" s="31" t="n">
-        <v>97.09999999999999</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B73" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C73" s="31" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="D73" s="31" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C74" s="31" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="D74" s="31" t="n">
-        <v>98.8</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C75" s="31" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>76.5</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B76" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C76" s="31" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="D76" s="31" t="n">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C77" s="31" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>99.40000000000001</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C78" s="31" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>97.09999999999999</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B79" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C79" s="31" t="inlineStr">
-        <is>
-          <t>Week 9</t>
-        </is>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B80" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C80" s="31" t="inlineStr">
-        <is>
-          <t>Week 10</t>
-        </is>
-      </c>
-      <c r="D80" s="31" t="n">
-        <v>91.2</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B81" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C81" s="31" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="D81" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C82" s="31" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="D82" s="31" t="n">
-        <v>98.8</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C83" s="31" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B84" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C84" s="31" t="inlineStr">
-        <is>
-          <t>Week 14</t>
-        </is>
-      </c>
-      <c r="D84" s="31" t="n">
-        <v>70.59999999999999</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B85" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C85" s="31" t="inlineStr">
-        <is>
-          <t>Week 16</t>
-        </is>
-      </c>
-      <c r="D85" s="31" t="n">
-        <v>94.09999999999999</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B86" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C86" s="31" t="inlineStr">
-        <is>
-          <t>Week 18</t>
-        </is>
-      </c>
-      <c r="D86" s="31" t="n">
-        <v>96.3</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B87" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C87" s="31" t="inlineStr">
-        <is>
-          <t>Week 19</t>
-        </is>
-      </c>
-      <c r="D87" s="31" t="n">
-        <v>97.8</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B88" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C88" s="31" t="inlineStr">
-        <is>
-          <t>Week 20</t>
-        </is>
-      </c>
-      <c r="D88" s="31" t="n">
-        <v>97.09999999999999</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B89" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C89" s="31" t="inlineStr">
-        <is>
-          <t>Week 21</t>
-        </is>
-      </c>
-      <c r="D89" s="31" t="n">
-        <v>88.2</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B90" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C90" s="31" t="inlineStr">
-        <is>
-          <t>Week 22</t>
-        </is>
-      </c>
-      <c r="D90" s="31" t="n">
-        <v>92.59999999999999</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B91" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C91" s="31" t="inlineStr">
-        <is>
-          <t>Week 23</t>
-        </is>
-      </c>
-      <c r="D91" s="31" t="n">
-        <v>94.90000000000001</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B92" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C92" s="31" t="inlineStr">
-        <is>
-          <t>Week 25</t>
-        </is>
-      </c>
-      <c r="D92" s="31" t="n">
-        <v>93.09999999999999</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B93" s="31" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="C93" s="31" t="inlineStr">
-        <is>
-          <t>Week 26</t>
-        </is>
-      </c>
-      <c r="D93" s="31" t="n">
-        <v>96.09999999999999</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B94" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C94" s="31" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="D94" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B95" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C95" s="31" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="D95" s="31" t="n">
-        <v>98.59999999999999</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B96" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C96" s="31" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="D96" s="31" t="n">
-        <v>97.90000000000001</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B97" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C97" s="31" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="D97" s="31" t="n">
-        <v>90.8</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B98" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C98" s="31" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="D98" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B99" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C99" s="31" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="D99" s="31" t="n">
-        <v>97.90000000000001</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B100" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C100" s="31" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="D100" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B101" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C101" s="31" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="D101" s="31" t="n">
-        <v>97.2</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B102" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C102" s="31" t="inlineStr">
-        <is>
-          <t>Week 9</t>
-        </is>
-      </c>
-      <c r="D102" s="31" t="n">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B103" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C103" s="31" t="inlineStr">
-        <is>
-          <t>Week 10</t>
-        </is>
-      </c>
-      <c r="D103" s="31" t="n">
-        <v>81.2</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B104" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C104" s="31" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="D104" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B105" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C105" s="31" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="D105" s="31" t="n">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B106" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C106" s="31" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="D106" s="31" t="n">
-        <v>97.2</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B107" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C107" s="31" t="inlineStr">
-        <is>
-          <t>Week 14</t>
-        </is>
-      </c>
-      <c r="D107" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B108" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C108" s="31" t="inlineStr">
-        <is>
-          <t>Week 16</t>
-        </is>
-      </c>
-      <c r="D108" s="31" t="n">
-        <v>93.09999999999999</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B109" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C109" s="31" t="inlineStr">
-        <is>
-          <t>Week 18</t>
-        </is>
-      </c>
-      <c r="D109" s="31" t="n">
-        <v>97.90000000000001</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B110" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C110" s="31" t="inlineStr">
-        <is>
-          <t>Week 19</t>
-        </is>
-      </c>
-      <c r="D110" s="31" t="n">
-        <v>96.90000000000001</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B111" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C111" s="31" t="inlineStr">
-        <is>
-          <t>Week 20</t>
-        </is>
-      </c>
-      <c r="D111" s="31" t="n">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B112" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C112" s="31" t="inlineStr">
-        <is>
-          <t>Week 21</t>
-        </is>
-      </c>
-      <c r="D112" s="31" t="n">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B113" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C113" s="31" t="inlineStr">
-        <is>
-          <t>Week 22</t>
-        </is>
-      </c>
-      <c r="D113" s="31" t="n">
-        <v>97.90000000000001</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B114" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C114" s="31" t="inlineStr">
-        <is>
-          <t>Week 23</t>
-        </is>
-      </c>
-      <c r="D114" s="31" t="n">
-        <v>96.90000000000001</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B115" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C115" s="31" t="inlineStr">
-        <is>
-          <t>Week 25</t>
-        </is>
-      </c>
-      <c r="D115" s="31" t="n">
-        <v>93.09999999999999</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="31" t="inlineStr">
-        <is>
-          <t>JECRC</t>
-        </is>
-      </c>
-      <c r="B116" s="31" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
-      <c r="C116" s="31" t="inlineStr">
-        <is>
-          <t>Week 26</t>
-        </is>
-      </c>
-      <c r="D116" s="31" t="n">
-        <v>94.40000000000001</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B117" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C117" s="31" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="D117" s="31" t="n">
-        <v>87.90000000000001</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B118" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C118" s="31" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="D118" s="31" t="n">
-        <v>92.40000000000001</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B119" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C119" s="31" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="D119" s="31" t="n">
-        <v>93.90000000000001</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B120" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C120" s="31" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="D120" s="31" t="n">
-        <v>84.09999999999999</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B121" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C121" s="31" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="D121" s="31" t="n">
-        <v>84.8</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B122" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C122" s="31" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="D122" s="31" t="n">
-        <v>87.90000000000001</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B123" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C123" s="31" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="D123" s="31" t="n">
-        <v>84.3</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B124" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C124" s="31" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="D124" s="31" t="n">
-        <v>85.90000000000001</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B125" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C125" s="31" t="inlineStr">
-        <is>
-          <t>Week 9</t>
-        </is>
-      </c>
-      <c r="D125" s="31" t="n">
-        <v>92.40000000000001</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B126" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C126" s="31" t="inlineStr">
-        <is>
-          <t>Week 10</t>
-        </is>
-      </c>
-      <c r="D126" s="31" t="n">
-        <v>86.40000000000001</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B127" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C127" s="31" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="D127" s="31" t="n">
-        <v>88.5</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B128" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C128" s="31" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="D128" s="31" t="n">
-        <v>84.8</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B129" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C129" s="31" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="D129" s="31" t="n">
-        <v>84.8</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B130" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C130" s="31" t="inlineStr">
-        <is>
-          <t>Week 14</t>
-        </is>
-      </c>
-      <c r="D130" s="31" t="n">
-        <v>93.3</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B131" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C131" s="31" t="inlineStr">
-        <is>
-          <t>Week 15</t>
-        </is>
-      </c>
-      <c r="D131" s="31" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B132" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C132" s="31" t="inlineStr">
-        <is>
-          <t>Week 16</t>
-        </is>
-      </c>
-      <c r="D132" s="31" t="n">
-        <v>93.90000000000001</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B133" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C133" s="31" t="inlineStr">
-        <is>
-          <t>Week 18</t>
-        </is>
-      </c>
-      <c r="D133" s="31" t="n">
-        <v>87.90000000000001</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B134" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C134" s="31" t="inlineStr">
-        <is>
-          <t>Week 19</t>
-        </is>
-      </c>
-      <c r="D134" s="31" t="n">
-        <v>84.8</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B135" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C135" s="31" t="inlineStr">
-        <is>
-          <t>Week 21</t>
-        </is>
-      </c>
-      <c r="D135" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B136" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C136" s="31" t="inlineStr">
-        <is>
-          <t>Week 22</t>
-        </is>
-      </c>
-      <c r="D136" s="31" t="n">
-        <v>89.90000000000001</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B137" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C137" s="31" t="inlineStr">
-        <is>
-          <t>Week 23</t>
-        </is>
-      </c>
-      <c r="D137" s="31" t="n">
-        <v>82.8</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B138" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C138" s="31" t="inlineStr">
-        <is>
-          <t>Week 25</t>
-        </is>
-      </c>
-      <c r="D138" s="31" t="n">
-        <v>85.90000000000001</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="31" t="inlineStr">
-        <is>
-          <t>Galgotias University</t>
-        </is>
-      </c>
-      <c r="B139" s="31" t="inlineStr">
-        <is>
-          <t>Batch 1</t>
-        </is>
-      </c>
-      <c r="C139" s="31" t="inlineStr">
-        <is>
-          <t>Week 26</t>
-        </is>
-      </c>
-      <c r="D139" s="31" t="n">
-        <v>84.8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -35163,28 +30685,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
-    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
-    <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
-    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
-    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
-    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
-    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
-    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
-    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
-    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
-    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35208,26 +30715,6 @@
           <t>Average Overall Performance Score</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
-        <is>
-          <t>Deployable Candidates</t>
-        </is>
-      </c>
-      <c r="F1" s="28" t="inlineStr">
-        <is>
-          <t>Progressing Candidates</t>
-        </is>
-      </c>
-      <c r="G1" s="28" t="inlineStr">
-        <is>
-          <t>Basic Competency</t>
-        </is>
-      </c>
-      <c r="H1" s="28" t="inlineStr">
-        <is>
-          <t>Critical Intervention</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="31" t="inlineStr">
@@ -35244,48 +30731,6 @@
       <c r="D2" s="31" t="n">
         <v>85</v>
       </c>
-      <c r="E2" s="31" t="n">
-        <v>23</v>
-      </c>
-      <c r="F2" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Attendance Week</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Batch 1 - JAVA Batch</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Batch 2 - Pytest Batch</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Batch 3 - Robot Python</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Batch 4 - Playwright</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Batch 5 - Dotnet</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="31" t="inlineStr">
@@ -35302,38 +30747,6 @@
       <c r="D3" s="31" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="E3" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="31" t="n">
-        <v>23</v>
-      </c>
-      <c r="G3" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>100</v>
-      </c>
-      <c r="V3" t="n">
-        <v>100</v>
-      </c>
-      <c r="W3" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="X3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -35350,38 +30763,6 @@
       <c r="D4" s="31" t="n">
         <v>79.8</v>
       </c>
-      <c r="E4" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="31" t="n">
-        <v>34</v>
-      </c>
-      <c r="G4" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Week 10</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="V4" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="X4" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>81.2</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
@@ -35398,38 +30779,6 @@
       <c r="D5" s="31" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="E5" s="31" t="n">
-        <v>33</v>
-      </c>
-      <c r="F5" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="V5" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="W5" t="n">
-        <v>100</v>
-      </c>
-      <c r="X5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
@@ -35445,514 +30794,6 @@
       </c>
       <c r="D6" s="31" t="n">
         <v>82.59999999999999</v>
-      </c>
-      <c r="E6" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="F6" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="W6" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>100</v>
-      </c>
-      <c r="W7" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="X7" t="n">
-        <v>99</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>97.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Week 14</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
-        <v>87</v>
-      </c>
-      <c r="V8" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="W8" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="X8" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Week 16</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="V9" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="W9" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="X9" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>93.09999999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Week 18</t>
-        </is>
-      </c>
-      <c r="U10" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="V10" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="W10" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="X10" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>97.90000000000001</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Week 19</t>
-        </is>
-      </c>
-      <c r="U11" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="V11" t="n">
-        <v>99</v>
-      </c>
-      <c r="W11" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>96.90000000000001</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="U12" t="n">
-        <v>100</v>
-      </c>
-      <c r="V12" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="X12" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>98.59999999999999</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Week 20</t>
-        </is>
-      </c>
-      <c r="U13" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="V13" t="n">
-        <v>100</v>
-      </c>
-      <c r="W13" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Week 21</t>
-        </is>
-      </c>
-      <c r="U14" t="n">
-        <v>100</v>
-      </c>
-      <c r="V14" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Week 22</t>
-        </is>
-      </c>
-      <c r="U15" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="V15" t="n">
-        <v>99</v>
-      </c>
-      <c r="W15" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="X15" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>97.90000000000001</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Week 23</t>
-        </is>
-      </c>
-      <c r="U16" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="V16" t="n">
-        <v>99</v>
-      </c>
-      <c r="W16" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="X16" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>96.90000000000001</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Week 25</t>
-        </is>
-      </c>
-      <c r="U17" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="V17" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="W17" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="X17" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>93.09999999999999</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Week 26</t>
-        </is>
-      </c>
-      <c r="U18" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="V18" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="W18" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="X18" t="n">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>94.40000000000001</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="U19" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="V19" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="W19" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="X19" t="n">
-        <v>98</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>97.90000000000001</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="U20" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="V20" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="W20" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="X20" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>90.8</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>100</v>
-      </c>
-      <c r="V21" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="X21" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="U22" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="V22" t="n">
-        <v>100</v>
-      </c>
-      <c r="W22" t="n">
-        <v>100</v>
-      </c>
-      <c r="X22" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>97.90000000000001</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="U23" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="V23" t="n">
-        <v>95</v>
-      </c>
-      <c r="W23" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="X23" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Assessment Week</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="W24" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="X24" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>97.2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="U25" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="V25" t="n">
-        <v>100</v>
-      </c>
-      <c r="W25" t="n">
-        <v>100</v>
-      </c>
-      <c r="X25" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="U26" t="n">
-        <v>77.09999999999999</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="U27" t="n">
-        <v>79.09999999999999</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="U28" t="n">
-        <v>81.3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="U29" t="n">
-        <v>75.3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="U30" t="n">
-        <v>72.90000000000001</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="U31" t="n">
-        <v>66.59999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/test/published_reports/pmq_client_dashboard.xlsx
+++ b/test/published_reports/pmq_client_dashboard.xlsx
@@ -1706,7 +1706,7 @@
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>Average overall performance score is 82.6, which is currently stable.</t>
+          <t>Average overall performance score is 82.5, which is currently stable.</t>
         </is>
       </c>
       <c r="B31" s="23" t="n"/>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="B9" s="31" t="n">
-        <v>86.7</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="10">
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="B13" s="31" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="14">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="B14" s="31" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
     </row>
   </sheetData>
@@ -2995,7 +2995,7 @@
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
         <is>
-          <t>Average overall performance score is 82.6, which is currently stable.</t>
+          <t>Average overall performance score is 82.5, which is currently stable.</t>
         </is>
       </c>
       <c r="B5" s="31" t="inlineStr">
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="G2" s="31" t="n">
-        <v>78.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H2" s="31" t="n">
-        <v>80</v>
+        <v>79.5</v>
       </c>
       <c r="I2" s="31" t="n">
-        <v>85.8</v>
+        <v>84.8</v>
       </c>
       <c r="J2" s="31" t="n">
         <v>68</v>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="G3" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="H3" s="31" t="n">
-        <v>88.3</v>
+        <v>88.2</v>
       </c>
       <c r="I3" s="31" t="n">
-        <v>90.7</v>
+        <v>90.5</v>
       </c>
       <c r="J3" s="31" t="n">
         <v>82</v>
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="G4" s="31" t="n">
-        <v>87.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H4" s="31" t="n">
-        <v>87.7</v>
+        <v>87.5</v>
       </c>
       <c r="I4" s="31" t="n">
-        <v>88.7</v>
+        <v>88.2</v>
       </c>
       <c r="J4" s="31" t="n">
         <v>85</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="G5" s="31" t="n">
-        <v>78.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="H5" s="31" t="n">
-        <v>80.7</v>
+        <v>79.8</v>
       </c>
       <c r="I5" s="31" t="n">
-        <v>83</v>
+        <v>81.2</v>
       </c>
       <c r="J5" s="31" t="n">
         <v>71</v>
@@ -3557,13 +3557,13 @@
         </is>
       </c>
       <c r="G6" s="31" t="n">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H6" s="31" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I6" s="31" t="n">
-        <v>86</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J6" s="31" t="n">
         <v>65</v>
@@ -3607,13 +3607,13 @@
         </is>
       </c>
       <c r="G7" s="31" t="n">
-        <v>83.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="H7" s="31" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I7" s="31" t="n">
-        <v>88.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="J7" s="31" t="n">
         <v>76</v>
@@ -3657,13 +3657,13 @@
         </is>
       </c>
       <c r="G8" s="31" t="n">
-        <v>85.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H8" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I8" s="31" t="n">
-        <v>88.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="J8" s="31" t="n">
         <v>82</v>
@@ -3707,13 +3707,13 @@
         </is>
       </c>
       <c r="G9" s="31" t="n">
-        <v>81.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="H9" s="31" t="n">
-        <v>82.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I9" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="J9" s="31" t="n">
         <v>72</v>
@@ -3763,7 +3763,7 @@
         <v>83.5</v>
       </c>
       <c r="I10" s="31" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="J10" s="31" t="n">
         <v>73</v>
@@ -3807,13 +3807,13 @@
         </is>
       </c>
       <c r="G11" s="31" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="H11" s="31" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I11" s="31" t="n">
-        <v>88.8</v>
+        <v>89</v>
       </c>
       <c r="J11" s="31" t="n">
         <v>80.5</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="G12" s="31" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H12" s="31" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I12" s="31" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="J12" s="31" t="n">
         <v>75</v>
@@ -3907,13 +3907,13 @@
         </is>
       </c>
       <c r="G13" s="31" t="n">
-        <v>77</v>
+        <v>76.7</v>
       </c>
       <c r="H13" s="31" t="n">
-        <v>78</v>
+        <v>77.8</v>
       </c>
       <c r="I13" s="31" t="n">
-        <v>74.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J13" s="31" t="n">
         <v>80</v>
@@ -3957,13 +3957,13 @@
         </is>
       </c>
       <c r="G14" s="31" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="H14" s="31" t="n">
-        <v>84.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="I14" s="31" t="n">
-        <v>89</v>
+        <v>89.2</v>
       </c>
       <c r="J14" s="31" t="n">
         <v>73</v>
@@ -4007,13 +4007,13 @@
         </is>
       </c>
       <c r="G15" s="31" t="n">
-        <v>77.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H15" s="31" t="n">
-        <v>79.7</v>
+        <v>79.8</v>
       </c>
       <c r="I15" s="31" t="n">
-        <v>83.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="J15" s="31" t="n">
         <v>69</v>
@@ -4057,13 +4057,13 @@
         </is>
       </c>
       <c r="G16" s="31" t="n">
-        <v>75.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="H16" s="31" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="I16" s="31" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="J16" s="31" t="n">
         <v>60</v>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="G17" s="31" t="n">
-        <v>75.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H17" s="31" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="I17" s="31" t="n">
-        <v>85.5</v>
+        <v>85.8</v>
       </c>
       <c r="J17" s="31" t="n">
         <v>61</v>
@@ -4213,7 +4213,7 @@
         <v>84.90000000000001</v>
       </c>
       <c r="I19" s="31" t="n">
-        <v>88.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="J19" s="31" t="n">
         <v>81</v>
@@ -4257,13 +4257,13 @@
         </is>
       </c>
       <c r="G20" s="31" t="n">
-        <v>75.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H20" s="31" t="n">
-        <v>77.7</v>
+        <v>77.8</v>
       </c>
       <c r="I20" s="31" t="n">
-        <v>86</v>
+        <v>86.2</v>
       </c>
       <c r="J20" s="31" t="n">
         <v>60</v>
@@ -4310,10 +4310,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="H21" s="31" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="I21" s="31" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="J21" s="31" t="n">
         <v>60</v>
@@ -4363,7 +4363,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="I22" s="31" t="n">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="J22" s="31" t="n">
         <v>68</v>
@@ -4407,13 +4407,13 @@
         </is>
       </c>
       <c r="G23" s="31" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="H23" s="31" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="I23" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="J23" s="31" t="n">
         <v>63</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="G24" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="H24" s="31" t="n">
         <v>87.5</v>
       </c>
       <c r="I24" s="31" t="n">
-        <v>89.8</v>
+        <v>89.7</v>
       </c>
       <c r="J24" s="31" t="n">
         <v>82</v>
@@ -4507,13 +4507,13 @@
         </is>
       </c>
       <c r="G25" s="31" t="n">
-        <v>76.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H25" s="31" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="I25" s="31" t="n">
-        <v>86.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="J25" s="31" t="n">
         <v>63</v>
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="G26" s="31" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H26" s="31" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I26" s="31" t="n">
-        <v>86.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="J26" s="31" t="n">
         <v>68</v>
@@ -4607,13 +4607,13 @@
         </is>
       </c>
       <c r="G27" s="31" t="n">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H27" s="31" t="n">
         <v>87.5</v>
       </c>
       <c r="I27" s="31" t="n">
-        <v>89.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="J27" s="31" t="n">
         <v>82</v>
@@ -4707,13 +4707,13 @@
         </is>
       </c>
       <c r="G29" s="31" t="n">
-        <v>87.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H29" s="31" t="n">
-        <v>87.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="I29" s="31" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="J29" s="31" t="n">
         <v>85</v>
@@ -4757,13 +4757,13 @@
         </is>
       </c>
       <c r="G30" s="31" t="n">
-        <v>83.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H30" s="31" t="n">
-        <v>84.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I30" s="31" t="n">
-        <v>89.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="J30" s="31" t="n">
         <v>74.5</v>
@@ -4810,10 +4810,10 @@
         <v>82.90000000000001</v>
       </c>
       <c r="H31" s="31" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I31" s="31" t="n">
-        <v>88.8</v>
+        <v>88.7</v>
       </c>
       <c r="J31" s="31" t="n">
         <v>74.5</v>
@@ -4857,13 +4857,13 @@
         </is>
       </c>
       <c r="G32" s="31" t="n">
-        <v>78.7</v>
+        <v>77.8</v>
       </c>
       <c r="H32" s="31" t="n">
-        <v>79.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I32" s="31" t="n">
-        <v>76.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="J32" s="31" t="n">
         <v>82</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="G33" s="31" t="n">
-        <v>83.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="H33" s="31" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I33" s="31" t="n">
-        <v>89.5</v>
+        <v>89.8</v>
       </c>
       <c r="J33" s="31" t="n">
         <v>74</v>
@@ -4957,13 +4957,13 @@
         </is>
       </c>
       <c r="G34" s="31" t="n">
-        <v>77.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H34" s="31" t="n">
-        <v>79.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I34" s="31" t="n">
-        <v>83.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="J34" s="31" t="n">
         <v>68</v>
@@ -5007,13 +5007,13 @@
         </is>
       </c>
       <c r="G35" s="31" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H35" s="31" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="I35" s="31" t="n">
-        <v>88.7</v>
+        <v>88.8</v>
       </c>
       <c r="J35" s="31" t="n">
         <v>81</v>
@@ -5057,13 +5057,13 @@
         </is>
       </c>
       <c r="G36" s="31" t="n">
-        <v>86.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H36" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I36" s="31" t="n">
-        <v>89.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J36" s="31" t="n">
         <v>82</v>
@@ -5107,13 +5107,13 @@
         </is>
       </c>
       <c r="G37" s="31" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H37" s="31" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="I37" s="31" t="n">
-        <v>87.3</v>
+        <v>87.5</v>
       </c>
       <c r="J37" s="31" t="n">
         <v>69</v>
@@ -5157,13 +5157,13 @@
         </is>
       </c>
       <c r="G38" s="31" t="n">
-        <v>78.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H38" s="31" t="n">
-        <v>80.2</v>
+        <v>79.5</v>
       </c>
       <c r="I38" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="J38" s="31" t="n">
         <v>66</v>
@@ -5207,13 +5207,13 @@
         </is>
       </c>
       <c r="G39" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="H39" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="I39" s="31" t="n">
-        <v>90</v>
+        <v>89.8</v>
       </c>
       <c r="J39" s="31" t="n">
         <v>80</v>
@@ -5257,13 +5257,13 @@
         </is>
       </c>
       <c r="G40" s="31" t="n">
-        <v>75.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H40" s="31" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I40" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="J40" s="31" t="n">
         <v>60</v>
@@ -5307,13 +5307,13 @@
         </is>
       </c>
       <c r="G41" s="31" t="n">
-        <v>78.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H41" s="31" t="n">
-        <v>80.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="I41" s="31" t="n">
-        <v>87.2</v>
+        <v>86</v>
       </c>
       <c r="J41" s="31" t="n">
         <v>65</v>
@@ -5357,13 +5357,13 @@
         </is>
       </c>
       <c r="G42" s="31" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H42" s="31" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I42" s="31" t="n">
-        <v>88.2</v>
+        <v>88.3</v>
       </c>
       <c r="J42" s="31" t="n">
         <v>80</v>
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="G43" s="31" t="n">
-        <v>86.5</v>
+        <v>86.3</v>
       </c>
       <c r="H43" s="31" t="n">
-        <v>88.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I43" s="31" t="n">
-        <v>89.7</v>
+        <v>89.3</v>
       </c>
       <c r="J43" s="31" t="n">
         <v>82</v>
@@ -5457,13 +5457,13 @@
         </is>
       </c>
       <c r="G44" s="31" t="n">
-        <v>85.8</v>
+        <v>85.7</v>
       </c>
       <c r="H44" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="I44" s="31" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="J44" s="31" t="n">
         <v>82</v>
@@ -5507,13 +5507,13 @@
         </is>
       </c>
       <c r="G45" s="31" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H45" s="31" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="I45" s="31" t="n">
-        <v>86.8</v>
+        <v>87</v>
       </c>
       <c r="J45" s="31" t="n">
         <v>65</v>
@@ -5607,13 +5607,13 @@
         </is>
       </c>
       <c r="G47" s="31" t="n">
-        <v>78.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H47" s="31" t="n">
-        <v>80.7</v>
+        <v>80</v>
       </c>
       <c r="I47" s="31" t="n">
-        <v>86.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="J47" s="31" t="n">
         <v>68</v>
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="G48" s="31" t="n">
-        <v>76.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H48" s="31" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I48" s="31" t="n">
-        <v>85.5</v>
+        <v>85.8</v>
       </c>
       <c r="J48" s="31" t="n">
         <v>63</v>
@@ -5710,10 +5710,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="H49" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="I49" s="31" t="n">
-        <v>89.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="J49" s="31" t="n">
         <v>81</v>
@@ -5757,13 +5757,13 @@
         </is>
       </c>
       <c r="G50" s="31" t="n">
-        <v>74.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H50" s="31" t="n">
-        <v>77.3</v>
+        <v>77.5</v>
       </c>
       <c r="I50" s="31" t="n">
-        <v>84.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="J50" s="31" t="n">
         <v>60</v>
@@ -5807,13 +5807,13 @@
         </is>
       </c>
       <c r="G51" s="31" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H51" s="31" t="n">
         <v>85.8</v>
       </c>
       <c r="I51" s="31" t="n">
-        <v>89.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="J51" s="31" t="n">
         <v>79.5</v>
@@ -5857,13 +5857,13 @@
         </is>
       </c>
       <c r="G52" s="31" t="n">
-        <v>77.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="H52" s="31" t="n">
-        <v>80</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I52" s="31" t="n">
-        <v>86.8</v>
+        <v>84</v>
       </c>
       <c r="J52" s="31" t="n">
         <v>64</v>
@@ -5907,13 +5907,13 @@
         </is>
       </c>
       <c r="G53" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H53" s="31" t="n">
-        <v>88.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I53" s="31" t="n">
-        <v>89.8</v>
+        <v>89.3</v>
       </c>
       <c r="J53" s="31" t="n">
         <v>84</v>
@@ -5957,13 +5957,13 @@
         </is>
       </c>
       <c r="G54" s="31" t="n">
-        <v>74.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="H54" s="31" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="I54" s="31" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="J54" s="31" t="n">
         <v>59</v>
@@ -6007,13 +6007,13 @@
         </is>
       </c>
       <c r="G55" s="31" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="H55" s="31" t="n">
-        <v>77.7</v>
+        <v>77.8</v>
       </c>
       <c r="I55" s="31" t="n">
-        <v>85.8</v>
+        <v>86</v>
       </c>
       <c r="J55" s="31" t="n">
         <v>60</v>
@@ -6057,13 +6057,13 @@
         </is>
       </c>
       <c r="G56" s="31" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H56" s="31" t="n">
-        <v>80.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="I56" s="31" t="n">
-        <v>87.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="J56" s="31" t="n">
         <v>65</v>
@@ -6107,13 +6107,13 @@
         </is>
       </c>
       <c r="G57" s="31" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H57" s="31" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="I57" s="31" t="n">
-        <v>90.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="J57" s="31" t="n">
         <v>80.5</v>
@@ -6157,13 +6157,13 @@
         </is>
       </c>
       <c r="G58" s="31" t="n">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="H58" s="31" t="n">
-        <v>84.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="I58" s="31" t="n">
-        <v>88</v>
+        <v>88.2</v>
       </c>
       <c r="J58" s="31" t="n">
         <v>81</v>
@@ -6207,13 +6207,13 @@
         </is>
       </c>
       <c r="G59" s="31" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="H59" s="31" t="n">
         <v>84.2</v>
       </c>
-      <c r="H59" s="31" t="n">
-        <v>84</v>
-      </c>
       <c r="I59" s="31" t="n">
-        <v>87.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="J59" s="31" t="n">
         <v>79.5</v>
@@ -6257,13 +6257,13 @@
         </is>
       </c>
       <c r="G60" s="31" t="n">
-        <v>75.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H60" s="31" t="n">
-        <v>78.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="I60" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J60" s="31" t="n">
         <v>61</v>
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="G61" s="31" t="n">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="H61" s="31" t="n">
-        <v>80.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I61" s="31" t="n">
-        <v>86.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="J61" s="31" t="n">
         <v>67</v>
@@ -6357,13 +6357,13 @@
         </is>
       </c>
       <c r="G62" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="H62" s="31" t="n">
-        <v>87</v>
+        <v>86.8</v>
       </c>
       <c r="I62" s="31" t="n">
-        <v>89.7</v>
+        <v>89.5</v>
       </c>
       <c r="J62" s="31" t="n">
         <v>81</v>
@@ -6407,13 +6407,13 @@
         </is>
       </c>
       <c r="G63" s="31" t="n">
-        <v>78.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="H63" s="31" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="I63" s="31" t="n">
-        <v>84.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="J63" s="31" t="n">
         <v>70</v>
@@ -6460,10 +6460,10 @@
         <v>87.8</v>
       </c>
       <c r="H64" s="31" t="n">
-        <v>88.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I64" s="31" t="n">
-        <v>89.8</v>
+        <v>89.7</v>
       </c>
       <c r="J64" s="31" t="n">
         <v>85</v>
@@ -6507,13 +6507,13 @@
         </is>
       </c>
       <c r="G65" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="H65" s="31" t="n">
-        <v>88.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="I65" s="31" t="n">
-        <v>90</v>
+        <v>89.5</v>
       </c>
       <c r="J65" s="31" t="n">
         <v>83</v>
@@ -6557,13 +6557,13 @@
         </is>
       </c>
       <c r="G66" s="31" t="n">
-        <v>75.7</v>
+        <v>75.8</v>
       </c>
       <c r="H66" s="31" t="n">
-        <v>77.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="I66" s="31" t="n">
-        <v>76.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="J66" s="31" t="n">
         <v>75</v>
@@ -6607,13 +6607,13 @@
         </is>
       </c>
       <c r="G67" s="31" t="n">
-        <v>74.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H67" s="31" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I67" s="31" t="n">
-        <v>85.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="J67" s="31" t="n">
         <v>60</v>
@@ -6657,13 +6657,13 @@
         </is>
       </c>
       <c r="G68" s="31" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="H68" s="31" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="I68" s="31" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="J68" s="31" t="n">
         <v>70</v>
@@ -6707,13 +6707,13 @@
         </is>
       </c>
       <c r="G69" s="31" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="H69" s="31" t="n">
         <v>78.3</v>
       </c>
-      <c r="H69" s="31" t="n">
-        <v>80</v>
-      </c>
       <c r="I69" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="J69" s="31" t="n">
         <v>66</v>
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="G70" s="31" t="n">
-        <v>81.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="H70" s="31" t="n">
-        <v>82.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I70" s="31" t="n">
-        <v>81.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="J70" s="31" t="n">
         <v>81</v>
@@ -6807,13 +6807,13 @@
         </is>
       </c>
       <c r="G71" s="31" t="n">
-        <v>83.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H71" s="31" t="n">
-        <v>83.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I71" s="31" t="n">
-        <v>84.7</v>
+        <v>83.8</v>
       </c>
       <c r="J71" s="31" t="n">
         <v>81</v>
@@ -6857,13 +6857,13 @@
         </is>
       </c>
       <c r="G72" s="31" t="n">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H72" s="31" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="I72" s="31" t="n">
-        <v>86.2</v>
+        <v>86.5</v>
       </c>
       <c r="J72" s="31" t="n">
         <v>82</v>
@@ -6907,13 +6907,13 @@
         </is>
       </c>
       <c r="G73" s="31" t="n">
-        <v>78.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H73" s="31" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I73" s="31" t="n">
-        <v>87.5</v>
+        <v>87.7</v>
       </c>
       <c r="J73" s="31" t="n">
         <v>65</v>
@@ -6957,13 +6957,13 @@
         </is>
       </c>
       <c r="G74" s="31" t="n">
-        <v>77.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H74" s="31" t="n">
-        <v>80.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="I74" s="31" t="n">
-        <v>85.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="J74" s="31" t="n">
         <v>67</v>
@@ -7013,7 +7013,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="I75" s="31" t="n">
-        <v>87.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="J75" s="31" t="n">
         <v>83</v>
@@ -7057,13 +7057,13 @@
         </is>
       </c>
       <c r="G76" s="31" t="n">
-        <v>76.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H76" s="31" t="n">
-        <v>78.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="I76" s="31" t="n">
-        <v>73.8</v>
+        <v>74.3</v>
       </c>
       <c r="J76" s="31" t="n">
         <v>81</v>
@@ -7107,13 +7107,13 @@
         </is>
       </c>
       <c r="G77" s="31" t="n">
-        <v>78.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H77" s="31" t="n">
-        <v>79.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I77" s="31" t="n">
-        <v>85.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J77" s="31" t="n">
         <v>68</v>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="G78" s="31" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="H78" s="31" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="I78" s="31" t="n">
-        <v>89.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="J78" s="31" t="n">
         <v>73</v>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="G79" s="31" t="n">
-        <v>68.8</v>
+        <v>69</v>
       </c>
       <c r="H79" s="31" t="n">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I79" s="31" t="n">
-        <v>82.7</v>
+        <v>83</v>
       </c>
       <c r="J79" s="31" t="n">
         <v>49</v>
@@ -7257,13 +7257,13 @@
         </is>
       </c>
       <c r="G80" s="31" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="H80" s="31" t="n">
         <v>80.2</v>
       </c>
       <c r="I80" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="J80" s="31" t="n">
         <v>66</v>
@@ -7357,13 +7357,13 @@
         </is>
       </c>
       <c r="G82" s="31" t="n">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="H82" s="31" t="n">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I82" s="31" t="n">
-        <v>85.8</v>
+        <v>86.2</v>
       </c>
       <c r="J82" s="31" t="n">
         <v>68</v>
@@ -7407,13 +7407,13 @@
         </is>
       </c>
       <c r="G83" s="31" t="n">
-        <v>87.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H83" s="31" t="n">
-        <v>87.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I83" s="31" t="n">
-        <v>90</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="J83" s="31" t="n">
         <v>84</v>
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="G84" s="31" t="n">
-        <v>74.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H84" s="31" t="n">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="I84" s="31" t="n">
-        <v>84.5</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="J84" s="31" t="n">
         <v>60</v>
@@ -7513,7 +7513,7 @@
         <v>77</v>
       </c>
       <c r="I85" s="31" t="n">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="J85" s="31" t="n">
         <v>59</v>
@@ -7557,13 +7557,13 @@
         </is>
       </c>
       <c r="G86" s="31" t="n">
-        <v>77.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="H86" s="31" t="n">
-        <v>80.5</v>
+        <v>80.7</v>
       </c>
       <c r="I86" s="31" t="n">
-        <v>84.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="J86" s="31" t="n">
         <v>69</v>
@@ -7657,13 +7657,13 @@
         </is>
       </c>
       <c r="G88" s="31" t="n">
-        <v>79.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="H88" s="31" t="n">
-        <v>81.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I88" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="J88" s="31" t="n">
         <v>69</v>
@@ -7707,13 +7707,13 @@
         </is>
       </c>
       <c r="G89" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="H89" s="31" t="n">
         <v>86.2</v>
       </c>
       <c r="I89" s="31" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="J89" s="31" t="n">
         <v>80</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="G91" s="31" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="H91" s="31" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I91" s="31" t="n">
-        <v>89.2</v>
+        <v>89.3</v>
       </c>
       <c r="J91" s="31" t="n">
         <v>82</v>
@@ -7857,13 +7857,13 @@
         </is>
       </c>
       <c r="G92" s="31" t="n">
-        <v>81.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H92" s="31" t="n">
-        <v>82.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I92" s="31" t="n">
-        <v>81.7</v>
+        <v>81.2</v>
       </c>
       <c r="J92" s="31" t="n">
         <v>81</v>
@@ -7907,13 +7907,13 @@
         </is>
       </c>
       <c r="G93" s="31" t="n">
-        <v>77</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H93" s="31" t="n">
-        <v>79.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I93" s="31" t="n">
-        <v>86.8</v>
+        <v>85.7</v>
       </c>
       <c r="J93" s="31" t="n">
         <v>63</v>
@@ -7957,13 +7957,13 @@
         </is>
       </c>
       <c r="G94" s="31" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="H94" s="31" t="n">
         <v>86.5</v>
       </c>
       <c r="I94" s="31" t="n">
-        <v>89.8</v>
+        <v>89.7</v>
       </c>
       <c r="J94" s="31" t="n">
         <v>81.5</v>
@@ -8007,13 +8007,13 @@
         </is>
       </c>
       <c r="G95" s="31" t="n">
-        <v>79.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H95" s="31" t="n">
-        <v>79.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I95" s="31" t="n">
-        <v>83.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="J95" s="31" t="n">
         <v>73</v>
@@ -8057,13 +8057,13 @@
         </is>
       </c>
       <c r="G96" s="31" t="n">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="H96" s="31" t="n">
-        <v>77.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I96" s="31" t="n">
-        <v>71.7</v>
+        <v>71.3</v>
       </c>
       <c r="J96" s="31" t="n">
         <v>82</v>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="G97" s="31" t="n">
-        <v>75.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="H97" s="31" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I97" s="31" t="n">
-        <v>84.7</v>
+        <v>85</v>
       </c>
       <c r="J97" s="31" t="n">
         <v>62</v>
@@ -8157,13 +8157,13 @@
         </is>
       </c>
       <c r="G98" s="31" t="n">
-        <v>76.2</v>
+        <v>74.5</v>
       </c>
       <c r="H98" s="31" t="n">
-        <v>79.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I98" s="31" t="n">
-        <v>86.8</v>
+        <v>84</v>
       </c>
       <c r="J98" s="31" t="n">
         <v>61</v>
@@ -8207,13 +8207,13 @@
         </is>
       </c>
       <c r="G99" s="31" t="n">
-        <v>81.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H99" s="31" t="n">
-        <v>81.7</v>
+        <v>82</v>
       </c>
       <c r="I99" s="31" t="n">
-        <v>82.3</v>
+        <v>82.8</v>
       </c>
       <c r="J99" s="31" t="n">
         <v>80</v>
@@ -8257,13 +8257,13 @@
         </is>
       </c>
       <c r="G100" s="31" t="n">
-        <v>86.8</v>
+        <v>86.7</v>
       </c>
       <c r="H100" s="31" t="n">
-        <v>88.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I100" s="31" t="n">
-        <v>90.2</v>
+        <v>90</v>
       </c>
       <c r="J100" s="31" t="n">
         <v>82</v>
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="G102" s="31" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="H102" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="I102" s="31" t="n">
-        <v>89.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="J102" s="31" t="n">
         <v>80</v>
@@ -8407,13 +8407,13 @@
         </is>
       </c>
       <c r="G103" s="31" t="n">
-        <v>77.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H103" s="31" t="n">
-        <v>79.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I103" s="31" t="n">
-        <v>86</v>
+        <v>86.5</v>
       </c>
       <c r="J103" s="31" t="n">
         <v>66</v>
@@ -8457,13 +8457,13 @@
         </is>
       </c>
       <c r="G104" s="31" t="n">
-        <v>84</v>
+        <v>84.3</v>
       </c>
       <c r="H104" s="31" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I104" s="31" t="n">
-        <v>87.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="J104" s="31" t="n">
         <v>79.5</v>
@@ -8507,13 +8507,13 @@
         </is>
       </c>
       <c r="G105" s="31" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H105" s="31" t="n">
         <v>79</v>
       </c>
       <c r="I105" s="31" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="J105" s="31" t="n">
         <v>74</v>
@@ -8557,13 +8557,13 @@
         </is>
       </c>
       <c r="G106" s="31" t="n">
-        <v>85.5</v>
+        <v>85.2</v>
       </c>
       <c r="H106" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I106" s="31" t="n">
-        <v>89.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J106" s="31" t="n">
         <v>80</v>
@@ -8657,13 +8657,13 @@
         </is>
       </c>
       <c r="G108" s="31" t="n">
-        <v>78.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H108" s="31" t="n">
-        <v>80.2</v>
+        <v>79.5</v>
       </c>
       <c r="I108" s="31" t="n">
-        <v>88</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="J108" s="31" t="n">
         <v>66</v>
@@ -8757,13 +8757,13 @@
         </is>
       </c>
       <c r="G110" s="31" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H110" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="I110" s="31" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="J110" s="31" t="n">
         <v>82</v>
@@ -8807,13 +8807,13 @@
         </is>
       </c>
       <c r="G111" s="31" t="n">
-        <v>79</v>
+        <v>78.3</v>
       </c>
       <c r="H111" s="31" t="n">
-        <v>81</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I111" s="31" t="n">
-        <v>86.7</v>
+        <v>85.5</v>
       </c>
       <c r="J111" s="31" t="n">
         <v>68</v>
@@ -8857,13 +8857,13 @@
         </is>
       </c>
       <c r="G112" s="31" t="n">
-        <v>78.3</v>
+        <v>77.3</v>
       </c>
       <c r="H112" s="31" t="n">
-        <v>79.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I112" s="31" t="n">
-        <v>76.8</v>
+        <v>75</v>
       </c>
       <c r="J112" s="31" t="n">
         <v>80.5</v>
@@ -8907,13 +8907,13 @@
         </is>
       </c>
       <c r="G113" s="31" t="n">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="H113" s="31" t="n">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I113" s="31" t="n">
-        <v>85.5</v>
+        <v>85.8</v>
       </c>
       <c r="J113" s="31" t="n">
         <v>68</v>
@@ -8963,7 +8963,7 @@
         <v>86.8</v>
       </c>
       <c r="I114" s="31" t="n">
-        <v>90</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="J114" s="31" t="n">
         <v>79</v>
@@ -9007,13 +9007,13 @@
         </is>
       </c>
       <c r="G115" s="31" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="H115" s="31" t="n">
         <v>86.7</v>
       </c>
-      <c r="H115" s="31" t="n">
-        <v>86.90000000000001</v>
-      </c>
       <c r="I115" s="31" t="n">
-        <v>90</v>
+        <v>89.7</v>
       </c>
       <c r="J115" s="31" t="n">
         <v>82</v>
@@ -9057,13 +9057,13 @@
         </is>
       </c>
       <c r="G116" s="31" t="n">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H116" s="31" t="n">
-        <v>84.3</v>
+        <v>84.5</v>
       </c>
       <c r="I116" s="31" t="n">
-        <v>89.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="J116" s="31" t="n">
         <v>72</v>
@@ -9107,13 +9107,13 @@
         </is>
       </c>
       <c r="G117" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="H117" s="31" t="n">
-        <v>87.8</v>
+        <v>87.7</v>
       </c>
       <c r="I117" s="31" t="n">
-        <v>89.7</v>
+        <v>89.5</v>
       </c>
       <c r="J117" s="31" t="n">
         <v>81</v>
@@ -9157,13 +9157,13 @@
         </is>
       </c>
       <c r="G118" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="H118" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="I118" s="31" t="n">
-        <v>89.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="J118" s="31" t="n">
         <v>84</v>
@@ -9207,13 +9207,13 @@
         </is>
       </c>
       <c r="G119" s="31" t="n">
-        <v>78.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H119" s="31" t="n">
-        <v>79</v>
+        <v>78.3</v>
       </c>
       <c r="I119" s="31" t="n">
-        <v>86.7</v>
+        <v>85.3</v>
       </c>
       <c r="J119" s="31" t="n">
         <v>66</v>
@@ -9257,13 +9257,13 @@
         </is>
       </c>
       <c r="G120" s="31" t="n">
-        <v>77.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="H120" s="31" t="n">
-        <v>78.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I120" s="31" t="n">
-        <v>84.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="J120" s="31" t="n">
         <v>67</v>
@@ -9307,13 +9307,13 @@
         </is>
       </c>
       <c r="G121" s="31" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H121" s="31" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="I121" s="31" t="n">
-        <v>88.2</v>
+        <v>88.3</v>
       </c>
       <c r="J121" s="31" t="n">
         <v>82</v>
@@ -9457,13 +9457,13 @@
         </is>
       </c>
       <c r="G124" s="31" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="H124" s="31" t="n">
         <v>82</v>
       </c>
       <c r="I124" s="31" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="J124" s="31" t="n">
         <v>80</v>
@@ -9507,13 +9507,13 @@
         </is>
       </c>
       <c r="G125" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H125" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="I125" s="31" t="n">
-        <v>89.3</v>
+        <v>89</v>
       </c>
       <c r="J125" s="31" t="n">
         <v>81</v>
@@ -9557,13 +9557,13 @@
         </is>
       </c>
       <c r="G126" s="31" t="n">
-        <v>85.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H126" s="31" t="n">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="I126" s="31" t="n">
-        <v>88.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J126" s="31" t="n">
         <v>80</v>
@@ -9607,13 +9607,13 @@
         </is>
       </c>
       <c r="G127" s="31" t="n">
-        <v>86.7</v>
+        <v>86.8</v>
       </c>
       <c r="H127" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I127" s="31" t="n">
-        <v>89.3</v>
+        <v>89.5</v>
       </c>
       <c r="J127" s="31" t="n">
         <v>83</v>
@@ -9657,13 +9657,13 @@
         </is>
       </c>
       <c r="G128" s="31" t="n">
-        <v>77.5</v>
+        <v>76</v>
       </c>
       <c r="H128" s="31" t="n">
-        <v>78</v>
+        <v>76.8</v>
       </c>
       <c r="I128" s="31" t="n">
-        <v>86.2</v>
+        <v>83.7</v>
       </c>
       <c r="J128" s="31" t="n">
         <v>65</v>
@@ -9713,7 +9713,7 @@
         <v>81.3</v>
       </c>
       <c r="I129" s="31" t="n">
-        <v>88.2</v>
+        <v>88.3</v>
       </c>
       <c r="J129" s="31" t="n">
         <v>68</v>
@@ -9757,13 +9757,13 @@
         </is>
       </c>
       <c r="G130" s="31" t="n">
-        <v>85</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H130" s="31" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I130" s="31" t="n">
-        <v>88.5</v>
+        <v>88.7</v>
       </c>
       <c r="J130" s="31" t="n">
         <v>80</v>
@@ -9807,13 +9807,13 @@
         </is>
       </c>
       <c r="G131" s="31" t="n">
-        <v>84.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="H131" s="31" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="I131" s="31" t="n">
-        <v>87.8</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="J131" s="31" t="n">
         <v>80</v>
@@ -9857,13 +9857,13 @@
         </is>
       </c>
       <c r="G132" s="31" t="n">
-        <v>84.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="H132" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="I132" s="31" t="n">
-        <v>88.3</v>
+        <v>88</v>
       </c>
       <c r="J132" s="31" t="n">
         <v>80</v>
@@ -9907,13 +9907,13 @@
         </is>
       </c>
       <c r="G133" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="H133" s="31" t="n">
-        <v>88</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I133" s="31" t="n">
-        <v>90.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="J133" s="31" t="n">
         <v>82</v>
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="G134" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="H134" s="31" t="n">
-        <v>88.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="I134" s="31" t="n">
-        <v>90.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="J134" s="31" t="n">
         <v>82</v>
@@ -10007,13 +10007,13 @@
         </is>
       </c>
       <c r="G135" s="31" t="n">
-        <v>78.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="H135" s="31" t="n">
-        <v>80.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I135" s="31" t="n">
-        <v>83.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J135" s="31" t="n">
         <v>72</v>
@@ -10057,13 +10057,13 @@
         </is>
       </c>
       <c r="G136" s="31" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H136" s="31" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I136" s="31" t="n">
-        <v>86.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="J136" s="31" t="n">
         <v>69</v>
@@ -10110,10 +10110,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="H137" s="31" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I137" s="31" t="n">
-        <v>89.2</v>
+        <v>89.3</v>
       </c>
       <c r="J137" s="31" t="n">
         <v>75</v>
@@ -10157,13 +10157,13 @@
         </is>
       </c>
       <c r="G138" s="31" t="n">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="H138" s="31" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="I138" s="31" t="n">
-        <v>88.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J138" s="31" t="n">
         <v>80</v>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="G139" s="31" t="n">
-        <v>77.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H139" s="31" t="n">
-        <v>79</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I139" s="31" t="n">
-        <v>84.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="J139" s="31" t="n">
         <v>68</v>
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="G140" s="31" t="n">
-        <v>75.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="H140" s="31" t="n">
-        <v>78.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="I140" s="31" t="n">
-        <v>83.7</v>
+        <v>81.5</v>
       </c>
       <c r="J140" s="31" t="n">
         <v>64</v>
@@ -10307,13 +10307,13 @@
         </is>
       </c>
       <c r="G141" s="31" t="n">
-        <v>79.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="H141" s="31" t="n">
-        <v>80.2</v>
+        <v>79.5</v>
       </c>
       <c r="I141" s="31" t="n">
-        <v>75.7</v>
+        <v>74.2</v>
       </c>
       <c r="J141" s="31" t="n">
         <v>84</v>
@@ -10553,13 +10553,13 @@
         <v>7</v>
       </c>
       <c r="N2" s="31" t="n">
-        <v>95.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O2" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>85.8</v>
+        <v>84.8</v>
       </c>
       <c r="Q2" s="31" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="U2" s="31" t="n">
-        <v>78.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="V2" s="31" t="inlineStr">
         <is>
@@ -10586,11 +10586,11 @@
         </is>
       </c>
       <c r="W2" s="31" t="n">
-        <v>80</v>
+        <v>79.5</v>
       </c>
       <c r="X2" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y2" s="31" t="inlineStr">
@@ -10658,13 +10658,13 @@
         <v>7</v>
       </c>
       <c r="N3" s="31" t="n">
-        <v>99.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="O3" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>90.7</v>
+        <v>90.5</v>
       </c>
       <c r="Q3" s="31" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         </is>
       </c>
       <c r="U3" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="V3" s="31" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         </is>
       </c>
       <c r="W3" s="31" t="n">
-        <v>88.3</v>
+        <v>88.2</v>
       </c>
       <c r="X3" s="31" t="inlineStr">
         <is>
@@ -10763,13 +10763,13 @@
         <v>7</v>
       </c>
       <c r="N4" s="31" t="n">
-        <v>96.40000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O4" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>88.7</v>
+        <v>88.2</v>
       </c>
       <c r="Q4" s="31" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="U4" s="31" t="n">
-        <v>87.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="V4" s="31" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="W4" s="31" t="n">
-        <v>87.7</v>
+        <v>87.5</v>
       </c>
       <c r="X4" s="31" t="inlineStr">
         <is>
@@ -10868,13 +10868,13 @@
         <v>7</v>
       </c>
       <c r="N5" s="31" t="n">
-        <v>84.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="O5" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P5" s="31" t="n">
-        <v>83</v>
+        <v>81.2</v>
       </c>
       <c r="Q5" s="31" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         </is>
       </c>
       <c r="U5" s="31" t="n">
-        <v>78.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="V5" s="31" t="inlineStr">
         <is>
@@ -10901,11 +10901,11 @@
         </is>
       </c>
       <c r="W5" s="31" t="n">
-        <v>80.7</v>
+        <v>79.8</v>
       </c>
       <c r="X5" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y5" s="31" t="inlineStr">
@@ -10973,13 +10973,13 @@
         <v>7</v>
       </c>
       <c r="N6" s="31" t="n">
-        <v>95.3</v>
+        <v>96</v>
       </c>
       <c r="O6" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>86</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q6" s="31" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="U6" s="31" t="n">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="V6" s="31" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         </is>
       </c>
       <c r="W6" s="31" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="X6" s="31" t="inlineStr">
         <is>
@@ -11078,13 +11078,13 @@
         <v>7</v>
       </c>
       <c r="N7" s="31" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="O7" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P7" s="31" t="n">
-        <v>88.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="Q7" s="31" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="U7" s="31" t="n">
-        <v>83.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="V7" s="31" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         </is>
       </c>
       <c r="W7" s="31" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="X7" s="31" t="inlineStr">
         <is>
@@ -11183,13 +11183,13 @@
         <v>7</v>
       </c>
       <c r="N8" s="31" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="O8" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>88.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Q8" s="31" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         </is>
       </c>
       <c r="U8" s="31" t="n">
-        <v>85.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="V8" s="31" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="W8" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="X8" s="31" t="inlineStr">
         <is>
@@ -11288,13 +11288,13 @@
         <v>7</v>
       </c>
       <c r="N9" s="31" t="n">
-        <v>97.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="O9" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="Q9" s="31" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="U9" s="31" t="n">
-        <v>81.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="V9" s="31" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="W9" s="31" t="n">
-        <v>82.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="X9" s="31" t="inlineStr">
         <is>
@@ -11393,13 +11393,13 @@
         <v>7</v>
       </c>
       <c r="N10" s="31" t="n">
-        <v>94.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="O10" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="Q10" s="31" t="inlineStr">
         <is>
@@ -11498,13 +11498,13 @@
         <v>7</v>
       </c>
       <c r="N11" s="31" t="n">
-        <v>95.8</v>
+        <v>96.2</v>
       </c>
       <c r="O11" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>88.8</v>
+        <v>89</v>
       </c>
       <c r="Q11" s="31" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         </is>
       </c>
       <c r="U11" s="31" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="V11" s="31" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         </is>
       </c>
       <c r="W11" s="31" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="X11" s="31" t="inlineStr">
         <is>
@@ -11603,13 +11603,13 @@
         <v>7</v>
       </c>
       <c r="N12" s="31" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="O12" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="Q12" s="31" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="U12" s="31" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="V12" s="31" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         </is>
       </c>
       <c r="W12" s="31" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="X12" s="31" t="inlineStr">
         <is>
@@ -11708,13 +11708,13 @@
         <v>7</v>
       </c>
       <c r="N13" s="31" t="n">
-        <v>92.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O13" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>74.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="Q13" s="31" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         </is>
       </c>
       <c r="U13" s="31" t="n">
-        <v>77</v>
+        <v>76.7</v>
       </c>
       <c r="V13" s="31" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         </is>
       </c>
       <c r="W13" s="31" t="n">
-        <v>78</v>
+        <v>77.8</v>
       </c>
       <c r="X13" s="31" t="inlineStr">
         <is>
@@ -11813,13 +11813,13 @@
         <v>7</v>
       </c>
       <c r="N14" s="31" t="n">
-        <v>97</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O14" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>89</v>
+        <v>89.2</v>
       </c>
       <c r="Q14" s="31" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="U14" s="31" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="V14" s="31" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         </is>
       </c>
       <c r="W14" s="31" t="n">
-        <v>84.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="X14" s="31" t="inlineStr">
         <is>
@@ -11918,13 +11918,13 @@
         <v>7</v>
       </c>
       <c r="N15" s="31" t="n">
-        <v>95.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O15" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>83.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Q15" s="31" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         </is>
       </c>
       <c r="U15" s="31" t="n">
-        <v>77.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="V15" s="31" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         </is>
       </c>
       <c r="W15" s="31" t="n">
-        <v>79.7</v>
+        <v>79.8</v>
       </c>
       <c r="X15" s="31" t="inlineStr">
         <is>
@@ -12023,13 +12023,13 @@
         <v>7</v>
       </c>
       <c r="N16" s="31" t="n">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="O16" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P16" s="31" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="Q16" s="31" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         </is>
       </c>
       <c r="U16" s="31" t="n">
-        <v>75.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="V16" s="31" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         </is>
       </c>
       <c r="W16" s="31" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="X16" s="31" t="inlineStr">
         <is>
@@ -12128,13 +12128,13 @@
         <v>7</v>
       </c>
       <c r="N17" s="31" t="n">
-        <v>97.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O17" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P17" s="31" t="n">
-        <v>85.5</v>
+        <v>85.8</v>
       </c>
       <c r="Q17" s="31" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="U17" s="31" t="n">
-        <v>75.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="V17" s="31" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="W17" s="31" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="X17" s="31" t="inlineStr">
         <is>
@@ -12233,10 +12233,10 @@
         <v>7</v>
       </c>
       <c r="N18" s="31" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="O18" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P18" s="31" t="n">
         <v>87.8</v>
@@ -12338,13 +12338,13 @@
         <v>7</v>
       </c>
       <c r="N19" s="31" t="n">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="O19" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P19" s="31" t="n">
-        <v>88.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Q19" s="31" t="inlineStr">
         <is>
@@ -12443,13 +12443,13 @@
         <v>7</v>
       </c>
       <c r="N20" s="31" t="n">
-        <v>98.5</v>
+        <v>98.8</v>
       </c>
       <c r="O20" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P20" s="31" t="n">
-        <v>86</v>
+        <v>86.2</v>
       </c>
       <c r="Q20" s="31" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="U20" s="31" t="n">
-        <v>75.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="V20" s="31" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="W20" s="31" t="n">
-        <v>77.7</v>
+        <v>77.8</v>
       </c>
       <c r="X20" s="31" t="inlineStr">
         <is>
@@ -12548,13 +12548,13 @@
         <v>7</v>
       </c>
       <c r="N21" s="31" t="n">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="O21" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P21" s="31" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Q21" s="31" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="W21" s="31" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="X21" s="31" t="inlineStr">
         <is>
@@ -12653,13 +12653,13 @@
         <v>7</v>
       </c>
       <c r="N22" s="31" t="n">
-        <v>98.3</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O22" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P22" s="31" t="n">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="Q22" s="31" t="inlineStr">
         <is>
@@ -12758,13 +12758,13 @@
         <v>7</v>
       </c>
       <c r="N23" s="31" t="n">
-        <v>96.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O23" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P23" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="Q23" s="31" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         </is>
       </c>
       <c r="U23" s="31" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="V23" s="31" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         </is>
       </c>
       <c r="W23" s="31" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="X23" s="31" t="inlineStr">
         <is>
@@ -12863,13 +12863,13 @@
         <v>7</v>
       </c>
       <c r="N24" s="31" t="n">
-        <v>98.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O24" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P24" s="31" t="n">
-        <v>89.8</v>
+        <v>89.7</v>
       </c>
       <c r="Q24" s="31" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         </is>
       </c>
       <c r="U24" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="V24" s="31" t="inlineStr">
         <is>
@@ -12968,13 +12968,13 @@
         <v>7</v>
       </c>
       <c r="N25" s="31" t="n">
-        <v>97.5</v>
+        <v>98</v>
       </c>
       <c r="O25" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P25" s="31" t="n">
-        <v>86.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Q25" s="31" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="U25" s="31" t="n">
-        <v>76.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="V25" s="31" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         </is>
       </c>
       <c r="W25" s="31" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="X25" s="31" t="inlineStr">
         <is>
@@ -13073,13 +13073,13 @@
         <v>7</v>
       </c>
       <c r="N26" s="31" t="n">
-        <v>95.09999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="O26" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P26" s="31" t="n">
-        <v>86.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Q26" s="31" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         </is>
       </c>
       <c r="U26" s="31" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="V26" s="31" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         </is>
       </c>
       <c r="W26" s="31" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="X26" s="31" t="inlineStr">
         <is>
@@ -13178,13 +13178,13 @@
         <v>7</v>
       </c>
       <c r="N27" s="31" t="n">
-        <v>98.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="O27" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P27" s="31" t="n">
-        <v>89.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="Q27" s="31" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="U27" s="31" t="n">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="V27" s="31" t="inlineStr">
         <is>
@@ -13283,10 +13283,10 @@
         <v>7</v>
       </c>
       <c r="N28" s="31" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="O28" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P28" s="31" t="n">
         <v>89.40000000000001</v>
@@ -13388,13 +13388,13 @@
         <v>7</v>
       </c>
       <c r="N29" s="31" t="n">
-        <v>97.2</v>
+        <v>96.8</v>
       </c>
       <c r="O29" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P29" s="31" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="Q29" s="31" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         </is>
       </c>
       <c r="U29" s="31" t="n">
-        <v>87.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="V29" s="31" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="W29" s="31" t="n">
-        <v>87.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="X29" s="31" t="inlineStr">
         <is>
@@ -13493,13 +13493,13 @@
         <v>7</v>
       </c>
       <c r="N30" s="31" t="n">
-        <v>98.2</v>
+        <v>97.7</v>
       </c>
       <c r="O30" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P30" s="31" t="n">
-        <v>89.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="Q30" s="31" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         </is>
       </c>
       <c r="U30" s="31" t="n">
-        <v>83.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="V30" s="31" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="W30" s="31" t="n">
-        <v>84.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="X30" s="31" t="inlineStr">
         <is>
@@ -13598,13 +13598,13 @@
         <v>7</v>
       </c>
       <c r="N31" s="31" t="n">
-        <v>97</v>
+        <v>96.7</v>
       </c>
       <c r="O31" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P31" s="31" t="n">
-        <v>88.8</v>
+        <v>88.7</v>
       </c>
       <c r="Q31" s="31" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="W31" s="31" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X31" s="31" t="inlineStr">
         <is>
@@ -13703,13 +13703,13 @@
         <v>7</v>
       </c>
       <c r="N32" s="31" t="n">
-        <v>94.2</v>
+        <v>91.2</v>
       </c>
       <c r="O32" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P32" s="31" t="n">
-        <v>76.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Q32" s="31" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="U32" s="31" t="n">
-        <v>78.7</v>
+        <v>77.8</v>
       </c>
       <c r="V32" s="31" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         </is>
       </c>
       <c r="W32" s="31" t="n">
-        <v>79.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="X32" s="31" t="inlineStr">
         <is>
@@ -13808,13 +13808,13 @@
         <v>7</v>
       </c>
       <c r="N33" s="31" t="n">
-        <v>96.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O33" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P33" s="31" t="n">
-        <v>89.5</v>
+        <v>89.8</v>
       </c>
       <c r="Q33" s="31" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         </is>
       </c>
       <c r="U33" s="31" t="n">
-        <v>83.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="V33" s="31" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         </is>
       </c>
       <c r="W33" s="31" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="X33" s="31" t="inlineStr">
         <is>
@@ -13913,13 +13913,13 @@
         <v>7</v>
       </c>
       <c r="N34" s="31" t="n">
-        <v>89.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O34" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P34" s="31" t="n">
-        <v>83.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="Q34" s="31" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         </is>
       </c>
       <c r="U34" s="31" t="n">
-        <v>77.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="V34" s="31" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         </is>
       </c>
       <c r="W34" s="31" t="n">
-        <v>79.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="X34" s="31" t="inlineStr">
         <is>
@@ -14018,13 +14018,13 @@
         <v>7</v>
       </c>
       <c r="N35" s="31" t="n">
-        <v>95.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O35" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P35" s="31" t="n">
-        <v>88.7</v>
+        <v>88.8</v>
       </c>
       <c r="Q35" s="31" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         </is>
       </c>
       <c r="U35" s="31" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="V35" s="31" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         </is>
       </c>
       <c r="W35" s="31" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="X35" s="31" t="inlineStr">
         <is>
@@ -14123,13 +14123,13 @@
         <v>7</v>
       </c>
       <c r="N36" s="31" t="n">
-        <v>95.5</v>
+        <v>94.2</v>
       </c>
       <c r="O36" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P36" s="31" t="n">
-        <v>89.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q36" s="31" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         </is>
       </c>
       <c r="U36" s="31" t="n">
-        <v>86.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="V36" s="31" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         </is>
       </c>
       <c r="W36" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="X36" s="31" t="inlineStr">
         <is>
@@ -14228,13 +14228,13 @@
         <v>7</v>
       </c>
       <c r="N37" s="31" t="n">
-        <v>97.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="O37" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P37" s="31" t="n">
-        <v>87.3</v>
+        <v>87.5</v>
       </c>
       <c r="Q37" s="31" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="U37" s="31" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="V37" s="31" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         </is>
       </c>
       <c r="W37" s="31" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="X37" s="31" t="inlineStr">
         <is>
@@ -14333,13 +14333,13 @@
         <v>7</v>
       </c>
       <c r="N38" s="31" t="n">
-        <v>97.8</v>
+        <v>95</v>
       </c>
       <c r="O38" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P38" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="Q38" s="31" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         </is>
       </c>
       <c r="U38" s="31" t="n">
-        <v>78.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="V38" s="31" t="inlineStr">
         <is>
@@ -14366,11 +14366,11 @@
         </is>
       </c>
       <c r="W38" s="31" t="n">
-        <v>80.2</v>
+        <v>79.5</v>
       </c>
       <c r="X38" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y38" s="31" t="inlineStr">
@@ -14438,17 +14438,17 @@
         <v>7</v>
       </c>
       <c r="N39" s="31" t="n">
-        <v>98.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="O39" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P39" s="31" t="n">
-        <v>90</v>
+        <v>89.8</v>
       </c>
       <c r="Q39" s="31" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="R39" s="31" t="n">
@@ -14463,7 +14463,7 @@
         </is>
       </c>
       <c r="U39" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="V39" s="31" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         </is>
       </c>
       <c r="W39" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="X39" s="31" t="inlineStr">
         <is>
@@ -14543,13 +14543,13 @@
         <v>7</v>
       </c>
       <c r="N40" s="31" t="n">
-        <v>97</v>
+        <v>97.5</v>
       </c>
       <c r="O40" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P40" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="Q40" s="31" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         </is>
       </c>
       <c r="U40" s="31" t="n">
-        <v>75.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="V40" s="31" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         </is>
       </c>
       <c r="W40" s="31" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="X40" s="31" t="inlineStr">
         <is>
@@ -14648,13 +14648,13 @@
         <v>7</v>
       </c>
       <c r="N41" s="31" t="n">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="O41" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P41" s="31" t="n">
-        <v>87.2</v>
+        <v>86</v>
       </c>
       <c r="Q41" s="31" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         </is>
       </c>
       <c r="U41" s="31" t="n">
-        <v>78.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V41" s="31" t="inlineStr">
         <is>
@@ -14681,11 +14681,11 @@
         </is>
       </c>
       <c r="W41" s="31" t="n">
-        <v>80.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="X41" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y41" s="31" t="inlineStr">
@@ -14753,13 +14753,13 @@
         <v>7</v>
       </c>
       <c r="N42" s="31" t="n">
-        <v>95.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O42" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P42" s="31" t="n">
-        <v>88.2</v>
+        <v>88.3</v>
       </c>
       <c r="Q42" s="31" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="U42" s="31" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="V42" s="31" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="W42" s="31" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="X42" s="31" t="inlineStr">
         <is>
@@ -14858,13 +14858,13 @@
         <v>7</v>
       </c>
       <c r="N43" s="31" t="n">
-        <v>98.7</v>
+        <v>98</v>
       </c>
       <c r="O43" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P43" s="31" t="n">
-        <v>89.7</v>
+        <v>89.3</v>
       </c>
       <c r="Q43" s="31" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         </is>
       </c>
       <c r="U43" s="31" t="n">
-        <v>86.5</v>
+        <v>86.3</v>
       </c>
       <c r="V43" s="31" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         </is>
       </c>
       <c r="W43" s="31" t="n">
-        <v>88.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X43" s="31" t="inlineStr">
         <is>
@@ -14963,13 +14963,13 @@
         <v>7</v>
       </c>
       <c r="N44" s="31" t="n">
-        <v>96.5</v>
+        <v>96.2</v>
       </c>
       <c r="O44" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P44" s="31" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="Q44" s="31" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         </is>
       </c>
       <c r="U44" s="31" t="n">
-        <v>85.8</v>
+        <v>85.7</v>
       </c>
       <c r="V44" s="31" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         </is>
       </c>
       <c r="W44" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="X44" s="31" t="inlineStr">
         <is>
@@ -15068,13 +15068,13 @@
         <v>7</v>
       </c>
       <c r="N45" s="31" t="n">
-        <v>97.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="O45" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P45" s="31" t="n">
-        <v>86.8</v>
+        <v>87</v>
       </c>
       <c r="Q45" s="31" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         </is>
       </c>
       <c r="U45" s="31" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="V45" s="31" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         </is>
       </c>
       <c r="W45" s="31" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="X45" s="31" t="inlineStr">
         <is>
@@ -15173,10 +15173,10 @@
         <v>7</v>
       </c>
       <c r="N46" s="31" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="O46" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P46" s="31" t="n">
         <v>90.7</v>
@@ -15278,13 +15278,13 @@
         <v>7</v>
       </c>
       <c r="N47" s="31" t="n">
-        <v>98</v>
+        <v>95.3</v>
       </c>
       <c r="O47" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P47" s="31" t="n">
-        <v>86.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Q47" s="31" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="U47" s="31" t="n">
-        <v>78.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="V47" s="31" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         </is>
       </c>
       <c r="W47" s="31" t="n">
-        <v>80.7</v>
+        <v>80</v>
       </c>
       <c r="X47" s="31" t="inlineStr">
         <is>
@@ -15383,13 +15383,13 @@
         <v>7</v>
       </c>
       <c r="N48" s="31" t="n">
-        <v>97.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O48" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P48" s="31" t="n">
-        <v>85.5</v>
+        <v>85.8</v>
       </c>
       <c r="Q48" s="31" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         </is>
       </c>
       <c r="U48" s="31" t="n">
-        <v>76.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="V48" s="31" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         </is>
       </c>
       <c r="W48" s="31" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="X48" s="31" t="inlineStr">
         <is>
@@ -15488,13 +15488,13 @@
         <v>7</v>
       </c>
       <c r="N49" s="31" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="O49" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P49" s="31" t="n">
-        <v>89.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="Q49" s="31" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         </is>
       </c>
       <c r="W49" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="X49" s="31" t="inlineStr">
         <is>
@@ -15593,13 +15593,13 @@
         <v>7</v>
       </c>
       <c r="N50" s="31" t="n">
-        <v>95.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="O50" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P50" s="31" t="n">
-        <v>84.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="Q50" s="31" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         </is>
       </c>
       <c r="U50" s="31" t="n">
-        <v>74.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="V50" s="31" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         </is>
       </c>
       <c r="W50" s="31" t="n">
-        <v>77.3</v>
+        <v>77.5</v>
       </c>
       <c r="X50" s="31" t="inlineStr">
         <is>
@@ -15698,17 +15698,17 @@
         <v>7</v>
       </c>
       <c r="N51" s="31" t="n">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O51" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P51" s="31" t="n">
-        <v>89.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="Q51" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="R51" s="31" t="n">
@@ -15723,7 +15723,7 @@
         </is>
       </c>
       <c r="U51" s="31" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="V51" s="31" t="inlineStr">
         <is>
@@ -15803,13 +15803,13 @@
         <v>7</v>
       </c>
       <c r="N52" s="31" t="n">
-        <v>97.7</v>
+        <v>92</v>
       </c>
       <c r="O52" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P52" s="31" t="n">
-        <v>86.8</v>
+        <v>84</v>
       </c>
       <c r="Q52" s="31" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         </is>
       </c>
       <c r="U52" s="31" t="n">
-        <v>77.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="V52" s="31" t="inlineStr">
         <is>
@@ -15836,11 +15836,11 @@
         </is>
       </c>
       <c r="W52" s="31" t="n">
-        <v>80</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="X52" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y52" s="31" t="inlineStr">
@@ -15908,13 +15908,13 @@
         <v>7</v>
       </c>
       <c r="N53" s="31" t="n">
-        <v>98.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O53" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P53" s="31" t="n">
-        <v>89.8</v>
+        <v>89.3</v>
       </c>
       <c r="Q53" s="31" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         </is>
       </c>
       <c r="U53" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="V53" s="31" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="W53" s="31" t="n">
-        <v>88.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X53" s="31" t="inlineStr">
         <is>
@@ -16013,13 +16013,13 @@
         <v>7</v>
       </c>
       <c r="N54" s="31" t="n">
-        <v>97.7</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O54" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P54" s="31" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="Q54" s="31" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         </is>
       </c>
       <c r="U54" s="31" t="n">
-        <v>74.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="V54" s="31" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="W54" s="31" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="X54" s="31" t="inlineStr">
         <is>
@@ -16118,13 +16118,13 @@
         <v>7</v>
       </c>
       <c r="N55" s="31" t="n">
-        <v>96.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O55" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P55" s="31" t="n">
-        <v>85.8</v>
+        <v>86</v>
       </c>
       <c r="Q55" s="31" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         </is>
       </c>
       <c r="U55" s="31" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="V55" s="31" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         </is>
       </c>
       <c r="W55" s="31" t="n">
-        <v>77.7</v>
+        <v>77.8</v>
       </c>
       <c r="X55" s="31" t="inlineStr">
         <is>
@@ -16223,13 +16223,13 @@
         <v>7</v>
       </c>
       <c r="N56" s="31" t="n">
-        <v>98.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="O56" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P56" s="31" t="n">
-        <v>87.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="Q56" s="31" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         </is>
       </c>
       <c r="U56" s="31" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="V56" s="31" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         </is>
       </c>
       <c r="W56" s="31" t="n">
-        <v>80.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="X56" s="31" t="inlineStr">
         <is>
@@ -16328,13 +16328,13 @@
         <v>7</v>
       </c>
       <c r="N57" s="31" t="n">
-        <v>98.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="O57" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P57" s="31" t="n">
-        <v>90.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Q57" s="31" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="U57" s="31" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="V57" s="31" t="inlineStr">
         <is>
@@ -16433,13 +16433,13 @@
         <v>7</v>
       </c>
       <c r="N58" s="31" t="n">
-        <v>95.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O58" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P58" s="31" t="n">
-        <v>88</v>
+        <v>88.2</v>
       </c>
       <c r="Q58" s="31" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         </is>
       </c>
       <c r="U58" s="31" t="n">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="V58" s="31" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         </is>
       </c>
       <c r="W58" s="31" t="n">
-        <v>84.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="X58" s="31" t="inlineStr">
         <is>
@@ -16538,13 +16538,13 @@
         <v>7</v>
       </c>
       <c r="N59" s="31" t="n">
-        <v>93.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="O59" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P59" s="31" t="n">
-        <v>87.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="Q59" s="31" t="inlineStr">
         <is>
@@ -16563,15 +16563,15 @@
         </is>
       </c>
       <c r="U59" s="31" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="V59" s="31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W59" s="31" t="n">
         <v>84.2</v>
-      </c>
-      <c r="V59" s="31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W59" s="31" t="n">
-        <v>84</v>
       </c>
       <c r="X59" s="31" t="inlineStr">
         <is>
@@ -16643,13 +16643,13 @@
         <v>7</v>
       </c>
       <c r="N60" s="31" t="n">
-        <v>95.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O60" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P60" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q60" s="31" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         </is>
       </c>
       <c r="U60" s="31" t="n">
-        <v>75.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="V60" s="31" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         </is>
       </c>
       <c r="W60" s="31" t="n">
-        <v>78.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="X60" s="31" t="inlineStr">
         <is>
@@ -16748,13 +16748,13 @@
         <v>7</v>
       </c>
       <c r="N61" s="31" t="n">
-        <v>96.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="O61" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P61" s="31" t="n">
-        <v>86.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Q61" s="31" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         </is>
       </c>
       <c r="U61" s="31" t="n">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="V61" s="31" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         </is>
       </c>
       <c r="W61" s="31" t="n">
-        <v>80.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="X61" s="31" t="inlineStr">
         <is>
@@ -16853,13 +16853,13 @@
         <v>7</v>
       </c>
       <c r="N62" s="31" t="n">
-        <v>98.7</v>
+        <v>98.5</v>
       </c>
       <c r="O62" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P62" s="31" t="n">
-        <v>89.7</v>
+        <v>89.5</v>
       </c>
       <c r="Q62" s="31" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="U62" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="V62" s="31" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         </is>
       </c>
       <c r="W62" s="31" t="n">
-        <v>87</v>
+        <v>86.8</v>
       </c>
       <c r="X62" s="31" t="inlineStr">
         <is>
@@ -16958,13 +16958,13 @@
         <v>7</v>
       </c>
       <c r="N63" s="31" t="n">
-        <v>96.8</v>
+        <v>97.3</v>
       </c>
       <c r="O63" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P63" s="31" t="n">
-        <v>84.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Q63" s="31" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         </is>
       </c>
       <c r="U63" s="31" t="n">
-        <v>78.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="V63" s="31" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         </is>
       </c>
       <c r="W63" s="31" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="X63" s="31" t="inlineStr">
         <is>
@@ -17063,13 +17063,13 @@
         <v>7</v>
       </c>
       <c r="N64" s="31" t="n">
-        <v>97.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O64" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P64" s="31" t="n">
-        <v>89.8</v>
+        <v>89.7</v>
       </c>
       <c r="Q64" s="31" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         </is>
       </c>
       <c r="W64" s="31" t="n">
-        <v>88.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="X64" s="31" t="inlineStr">
         <is>
@@ -17168,17 +17168,17 @@
         <v>7</v>
       </c>
       <c r="N65" s="31" t="n">
-        <v>98.7</v>
+        <v>97.8</v>
       </c>
       <c r="O65" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P65" s="31" t="n">
-        <v>90</v>
+        <v>89.5</v>
       </c>
       <c r="Q65" s="31" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="R65" s="31" t="n">
@@ -17193,7 +17193,7 @@
         </is>
       </c>
       <c r="U65" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="V65" s="31" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="W65" s="31" t="n">
-        <v>88.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="X65" s="31" t="inlineStr">
         <is>
@@ -17273,13 +17273,13 @@
         <v>7</v>
       </c>
       <c r="N66" s="31" t="n">
-        <v>93.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O66" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P66" s="31" t="n">
-        <v>76.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="Q66" s="31" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="U66" s="31" t="n">
-        <v>75.7</v>
+        <v>75.8</v>
       </c>
       <c r="V66" s="31" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         </is>
       </c>
       <c r="W66" s="31" t="n">
-        <v>77.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="X66" s="31" t="inlineStr">
         <is>
@@ -17378,13 +17378,13 @@
         <v>7</v>
       </c>
       <c r="N67" s="31" t="n">
-        <v>96.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="O67" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P67" s="31" t="n">
-        <v>85.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="Q67" s="31" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="U67" s="31" t="n">
-        <v>74.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="V67" s="31" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="W67" s="31" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="X67" s="31" t="inlineStr">
         <is>
@@ -17483,13 +17483,13 @@
         <v>7</v>
       </c>
       <c r="N68" s="31" t="n">
-        <v>98.5</v>
+        <v>98.8</v>
       </c>
       <c r="O68" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P68" s="31" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="Q68" s="31" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         </is>
       </c>
       <c r="U68" s="31" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="V68" s="31" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         </is>
       </c>
       <c r="W68" s="31" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="X68" s="31" t="inlineStr">
         <is>
@@ -17588,13 +17588,13 @@
         <v>7</v>
       </c>
       <c r="N69" s="31" t="n">
-        <v>96.8</v>
+        <v>90</v>
       </c>
       <c r="O69" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P69" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="Q69" s="31" t="inlineStr">
         <is>
@@ -17613,19 +17613,19 @@
         </is>
       </c>
       <c r="U69" s="31" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="V69" s="31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W69" s="31" t="n">
         <v>78.3</v>
       </c>
-      <c r="V69" s="31" t="inlineStr">
+      <c r="X69" s="31" t="inlineStr">
         <is>
           <t>B</t>
-        </is>
-      </c>
-      <c r="W69" s="31" t="n">
-        <v>80</v>
-      </c>
-      <c r="X69" s="31" t="inlineStr">
-        <is>
-          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="31" t="inlineStr">
@@ -17693,13 +17693,13 @@
         <v>7</v>
       </c>
       <c r="N70" s="31" t="n">
-        <v>96.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="O70" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>81.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="Q70" s="31" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         </is>
       </c>
       <c r="U70" s="31" t="n">
-        <v>81.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="V70" s="31" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="W70" s="31" t="n">
-        <v>82.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="X70" s="31" t="inlineStr">
         <is>
@@ -17798,13 +17798,13 @@
         <v>7</v>
       </c>
       <c r="N71" s="31" t="n">
-        <v>88.7</v>
+        <v>86.8</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>84.7</v>
+        <v>83.8</v>
       </c>
       <c r="Q71" s="31" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         </is>
       </c>
       <c r="U71" s="31" t="n">
-        <v>83.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="V71" s="31" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="W71" s="31" t="n">
-        <v>83.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="X71" s="31" t="inlineStr">
         <is>
@@ -17903,13 +17903,13 @@
         <v>7</v>
       </c>
       <c r="N72" s="31" t="n">
-        <v>92.7</v>
+        <v>93.3</v>
       </c>
       <c r="O72" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>86.2</v>
+        <v>86.5</v>
       </c>
       <c r="Q72" s="31" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="U72" s="31" t="n">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="V72" s="31" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         </is>
       </c>
       <c r="W72" s="31" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="X72" s="31" t="inlineStr">
         <is>
@@ -18008,13 +18008,13 @@
         <v>7</v>
       </c>
       <c r="N73" s="31" t="n">
-        <v>97.90000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>87.5</v>
+        <v>87.7</v>
       </c>
       <c r="Q73" s="31" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         </is>
       </c>
       <c r="U73" s="31" t="n">
-        <v>78.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="V73" s="31" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         </is>
       </c>
       <c r="W73" s="31" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="X73" s="31" t="inlineStr">
         <is>
@@ -18113,13 +18113,13 @@
         <v>7</v>
       </c>
       <c r="N74" s="31" t="n">
-        <v>94.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="O74" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>85.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="Q74" s="31" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         </is>
       </c>
       <c r="U74" s="31" t="n">
-        <v>77.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V74" s="31" t="inlineStr">
         <is>
@@ -18146,11 +18146,11 @@
         </is>
       </c>
       <c r="W74" s="31" t="n">
-        <v>80.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="X74" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y74" s="31" t="inlineStr">
@@ -18218,13 +18218,13 @@
         <v>7</v>
       </c>
       <c r="N75" s="31" t="n">
-        <v>94.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="O75" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>87.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="Q75" s="31" t="inlineStr">
         <is>
@@ -18323,13 +18323,13 @@
         <v>7</v>
       </c>
       <c r="N76" s="31" t="n">
-        <v>88.7</v>
+        <v>89.7</v>
       </c>
       <c r="O76" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P76" s="31" t="n">
-        <v>73.8</v>
+        <v>74.3</v>
       </c>
       <c r="Q76" s="31" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         </is>
       </c>
       <c r="U76" s="31" t="n">
-        <v>76.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="V76" s="31" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         </is>
       </c>
       <c r="W76" s="31" t="n">
-        <v>78.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="X76" s="31" t="inlineStr">
         <is>
@@ -18428,13 +18428,13 @@
         <v>7</v>
       </c>
       <c r="N77" s="31" t="n">
-        <v>94.2</v>
+        <v>92.2</v>
       </c>
       <c r="O77" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P77" s="31" t="n">
-        <v>85.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q77" s="31" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="U77" s="31" t="n">
-        <v>78.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="V77" s="31" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         </is>
       </c>
       <c r="W77" s="31" t="n">
-        <v>79.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="X77" s="31" t="inlineStr">
         <is>
@@ -18533,13 +18533,13 @@
         <v>7</v>
       </c>
       <c r="N78" s="31" t="n">
-        <v>96.7</v>
+        <v>97.3</v>
       </c>
       <c r="O78" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>89.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="Q78" s="31" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         </is>
       </c>
       <c r="U78" s="31" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="V78" s="31" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         </is>
       </c>
       <c r="W78" s="31" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="X78" s="31" t="inlineStr">
         <is>
@@ -18638,13 +18638,13 @@
         <v>7</v>
       </c>
       <c r="N79" s="31" t="n">
-        <v>95.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>82.7</v>
+        <v>83</v>
       </c>
       <c r="Q79" s="31" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         </is>
       </c>
       <c r="U79" s="31" t="n">
-        <v>68.8</v>
+        <v>69</v>
       </c>
       <c r="V79" s="31" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         </is>
       </c>
       <c r="W79" s="31" t="n">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="X79" s="31" t="inlineStr">
         <is>
@@ -18743,13 +18743,13 @@
         <v>7</v>
       </c>
       <c r="N80" s="31" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="O80" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="Q80" s="31" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         </is>
       </c>
       <c r="U80" s="31" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="V80" s="31" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>99.7</v>
       </c>
       <c r="O81" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P81" s="31" t="n">
         <v>86.8</v>
@@ -18953,13 +18953,13 @@
         <v>7</v>
       </c>
       <c r="N82" s="31" t="n">
-        <v>94.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O82" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>85.8</v>
+        <v>86.2</v>
       </c>
       <c r="Q82" s="31" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="U82" s="31" t="n">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="V82" s="31" t="inlineStr">
         <is>
@@ -18986,11 +18986,11 @@
         </is>
       </c>
       <c r="W82" s="31" t="n">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="X82" s="31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y82" s="31" t="inlineStr">
@@ -19058,13 +19058,13 @@
         <v>7</v>
       </c>
       <c r="N83" s="31" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="O83" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P83" s="31" t="n">
-        <v>90</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Q83" s="31" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         </is>
       </c>
       <c r="U83" s="31" t="n">
-        <v>87.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="V83" s="31" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         </is>
       </c>
       <c r="W83" s="31" t="n">
-        <v>87.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="X83" s="31" t="inlineStr">
         <is>
@@ -19163,13 +19163,13 @@
         <v>7</v>
       </c>
       <c r="N84" s="31" t="n">
-        <v>96.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O84" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P84" s="31" t="n">
-        <v>84.5</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Q84" s="31" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         </is>
       </c>
       <c r="U84" s="31" t="n">
-        <v>74.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="V84" s="31" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         </is>
       </c>
       <c r="W84" s="31" t="n">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="X84" s="31" t="inlineStr">
         <is>
@@ -19268,13 +19268,13 @@
         <v>7</v>
       </c>
       <c r="N85" s="31" t="n">
-        <v>98.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="O85" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P85" s="31" t="n">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="Q85" s="31" t="inlineStr">
         <is>
@@ -19373,13 +19373,13 @@
         <v>7</v>
       </c>
       <c r="N86" s="31" t="n">
-        <v>94.2</v>
+        <v>95.2</v>
       </c>
       <c r="O86" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P86" s="31" t="n">
-        <v>84.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="Q86" s="31" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         </is>
       </c>
       <c r="U86" s="31" t="n">
-        <v>77.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="V86" s="31" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         </is>
       </c>
       <c r="W86" s="31" t="n">
-        <v>80.5</v>
+        <v>80.7</v>
       </c>
       <c r="X86" s="31" t="inlineStr">
         <is>
@@ -19478,10 +19478,10 @@
         <v>7</v>
       </c>
       <c r="N87" s="31" t="n">
-        <v>98.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="O87" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P87" s="31" t="n">
         <v>89.8</v>
@@ -19583,13 +19583,13 @@
         <v>7</v>
       </c>
       <c r="N88" s="31" t="n">
-        <v>97.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="O88" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P88" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="Q88" s="31" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="U88" s="31" t="n">
-        <v>79.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="V88" s="31" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         </is>
       </c>
       <c r="W88" s="31" t="n">
-        <v>81.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="X88" s="31" t="inlineStr">
         <is>
@@ -19688,13 +19688,13 @@
         <v>7</v>
       </c>
       <c r="N89" s="31" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="O89" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P89" s="31" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="Q89" s="31" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         </is>
       </c>
       <c r="U89" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="V89" s="31" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>100</v>
       </c>
       <c r="O90" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P90" s="31" t="n">
         <v>91.3</v>
@@ -19898,13 +19898,13 @@
         <v>7</v>
       </c>
       <c r="N91" s="31" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O91" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P91" s="31" t="n">
-        <v>89.2</v>
+        <v>89.3</v>
       </c>
       <c r="Q91" s="31" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         </is>
       </c>
       <c r="U91" s="31" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="V91" s="31" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         </is>
       </c>
       <c r="W91" s="31" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="X91" s="31" t="inlineStr">
         <is>
@@ -20003,13 +20003,13 @@
         <v>7</v>
       </c>
       <c r="N92" s="31" t="n">
-        <v>92.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="O92" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P92" s="31" t="n">
-        <v>81.7</v>
+        <v>81.2</v>
       </c>
       <c r="Q92" s="31" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="U92" s="31" t="n">
-        <v>81.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="V92" s="31" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         </is>
       </c>
       <c r="W92" s="31" t="n">
-        <v>82.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="X92" s="31" t="inlineStr">
         <is>
@@ -20108,13 +20108,13 @@
         <v>7</v>
       </c>
       <c r="N93" s="31" t="n">
-        <v>97.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="O93" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P93" s="31" t="n">
-        <v>86.8</v>
+        <v>85.7</v>
       </c>
       <c r="Q93" s="31" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         </is>
       </c>
       <c r="U93" s="31" t="n">
-        <v>77</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="V93" s="31" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         </is>
       </c>
       <c r="W93" s="31" t="n">
-        <v>79.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="X93" s="31" t="inlineStr">
         <is>
@@ -20213,13 +20213,13 @@
         <v>7</v>
       </c>
       <c r="N94" s="31" t="n">
-        <v>97.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O94" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P94" s="31" t="n">
-        <v>89.8</v>
+        <v>89.7</v>
       </c>
       <c r="Q94" s="31" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         </is>
       </c>
       <c r="U94" s="31" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="V94" s="31" t="inlineStr">
         <is>
@@ -20318,13 +20318,13 @@
         <v>7</v>
       </c>
       <c r="N95" s="31" t="n">
-        <v>95.90000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="O95" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P95" s="31" t="n">
-        <v>83.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="Q95" s="31" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         </is>
       </c>
       <c r="U95" s="31" t="n">
-        <v>79.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="V95" s="31" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         </is>
       </c>
       <c r="W95" s="31" t="n">
-        <v>79.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="X95" s="31" t="inlineStr">
         <is>
@@ -20423,13 +20423,13 @@
         <v>7</v>
       </c>
       <c r="N96" s="31" t="n">
-        <v>96.5</v>
+        <v>95.7</v>
       </c>
       <c r="O96" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P96" s="31" t="n">
-        <v>71.7</v>
+        <v>71.3</v>
       </c>
       <c r="Q96" s="31" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         </is>
       </c>
       <c r="U96" s="31" t="n">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="V96" s="31" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         </is>
       </c>
       <c r="W96" s="31" t="n">
-        <v>77.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="X96" s="31" t="inlineStr">
         <is>
@@ -20528,13 +20528,13 @@
         <v>7</v>
       </c>
       <c r="N97" s="31" t="n">
-        <v>95.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="O97" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P97" s="31" t="n">
-        <v>84.7</v>
+        <v>85</v>
       </c>
       <c r="Q97" s="31" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         </is>
       </c>
       <c r="U97" s="31" t="n">
-        <v>75.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="V97" s="31" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         </is>
       </c>
       <c r="W97" s="31" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="X97" s="31" t="inlineStr">
         <is>
@@ -20633,13 +20633,13 @@
         <v>7</v>
       </c>
       <c r="N98" s="31" t="n">
-        <v>97.3</v>
+        <v>91.7</v>
       </c>
       <c r="O98" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P98" s="31" t="n">
-        <v>86.8</v>
+        <v>84</v>
       </c>
       <c r="Q98" s="31" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         </is>
       </c>
       <c r="U98" s="31" t="n">
-        <v>76.2</v>
+        <v>74.5</v>
       </c>
       <c r="V98" s="31" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         </is>
       </c>
       <c r="W98" s="31" t="n">
-        <v>79.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="X98" s="31" t="inlineStr">
         <is>
@@ -20738,13 +20738,13 @@
         <v>7</v>
       </c>
       <c r="N99" s="31" t="n">
-        <v>94.59999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O99" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P99" s="31" t="n">
-        <v>82.3</v>
+        <v>82.8</v>
       </c>
       <c r="Q99" s="31" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         </is>
       </c>
       <c r="U99" s="31" t="n">
-        <v>81.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="V99" s="31" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         </is>
       </c>
       <c r="W99" s="31" t="n">
-        <v>81.7</v>
+        <v>82</v>
       </c>
       <c r="X99" s="31" t="inlineStr">
         <is>
@@ -20843,13 +20843,13 @@
         <v>7</v>
       </c>
       <c r="N100" s="31" t="n">
-        <v>98.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O100" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P100" s="31" t="n">
-        <v>90.2</v>
+        <v>90</v>
       </c>
       <c r="Q100" s="31" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="U100" s="31" t="n">
-        <v>86.8</v>
+        <v>86.7</v>
       </c>
       <c r="V100" s="31" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         </is>
       </c>
       <c r="W100" s="31" t="n">
-        <v>88.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="X100" s="31" t="inlineStr">
         <is>
@@ -21053,13 +21053,13 @@
         <v>7</v>
       </c>
       <c r="N102" s="31" t="n">
-        <v>96.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O102" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P102" s="31" t="n">
-        <v>89.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="Q102" s="31" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         </is>
       </c>
       <c r="U102" s="31" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="V102" s="31" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="W102" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="X102" s="31" t="inlineStr">
         <is>
@@ -21158,13 +21158,13 @@
         <v>7</v>
       </c>
       <c r="N103" s="31" t="n">
-        <v>94.8</v>
+        <v>95.7</v>
       </c>
       <c r="O103" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P103" s="31" t="n">
-        <v>86</v>
+        <v>86.5</v>
       </c>
       <c r="Q103" s="31" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         </is>
       </c>
       <c r="U103" s="31" t="n">
-        <v>77.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="V103" s="31" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="W103" s="31" t="n">
-        <v>79.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="X103" s="31" t="inlineStr">
         <is>
@@ -21263,13 +21263,13 @@
         <v>7</v>
       </c>
       <c r="N104" s="31" t="n">
-        <v>92.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O104" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P104" s="31" t="n">
-        <v>87.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="Q104" s="31" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         </is>
       </c>
       <c r="U104" s="31" t="n">
-        <v>84</v>
+        <v>84.3</v>
       </c>
       <c r="V104" s="31" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         </is>
       </c>
       <c r="W104" s="31" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="X104" s="31" t="inlineStr">
         <is>
@@ -21368,13 +21368,13 @@
         <v>7</v>
       </c>
       <c r="N105" s="31" t="n">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="O105" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P105" s="31" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="Q105" s="31" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         </is>
       </c>
       <c r="U105" s="31" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="V105" s="31" t="inlineStr">
         <is>
@@ -21473,13 +21473,13 @@
         <v>7</v>
       </c>
       <c r="N106" s="31" t="n">
-        <v>97.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O106" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P106" s="31" t="n">
-        <v>89.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q106" s="31" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         </is>
       </c>
       <c r="U106" s="31" t="n">
-        <v>85.5</v>
+        <v>85.2</v>
       </c>
       <c r="V106" s="31" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         </is>
       </c>
       <c r="W106" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="X106" s="31" t="inlineStr">
         <is>
@@ -21578,10 +21578,10 @@
         <v>7</v>
       </c>
       <c r="N107" s="31" t="n">
-        <v>92.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O107" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P107" s="31" t="n">
         <v>86.7</v>
@@ -21683,13 +21683,13 @@
         <v>7</v>
       </c>
       <c r="N108" s="31" t="n">
-        <v>98.8</v>
+        <v>96</v>
       </c>
       <c r="O108" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P108" s="31" t="n">
-        <v>88</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Q108" s="31" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         </is>
       </c>
       <c r="U108" s="31" t="n">
-        <v>78.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="V108" s="31" t="inlineStr">
         <is>
@@ -21716,11 +21716,11 @@
         </is>
       </c>
       <c r="W108" s="31" t="n">
-        <v>80.2</v>
+        <v>79.5</v>
       </c>
       <c r="X108" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y108" s="31" t="inlineStr">
@@ -21788,10 +21788,10 @@
         <v>7</v>
       </c>
       <c r="N109" s="31" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="O109" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P109" s="31" t="n">
         <v>90.7</v>
@@ -21893,13 +21893,13 @@
         <v>7</v>
       </c>
       <c r="N110" s="31" t="n">
-        <v>98</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O110" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P110" s="31" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="Q110" s="31" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         </is>
       </c>
       <c r="U110" s="31" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="V110" s="31" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         </is>
       </c>
       <c r="W110" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="X110" s="31" t="inlineStr">
         <is>
@@ -21998,13 +21998,13 @@
         <v>7</v>
       </c>
       <c r="N111" s="31" t="n">
-        <v>96.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O111" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P111" s="31" t="n">
-        <v>86.7</v>
+        <v>85.5</v>
       </c>
       <c r="Q111" s="31" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         </is>
       </c>
       <c r="U111" s="31" t="n">
-        <v>79</v>
+        <v>78.3</v>
       </c>
       <c r="V111" s="31" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         </is>
       </c>
       <c r="W111" s="31" t="n">
-        <v>81</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="X111" s="31" t="inlineStr">
         <is>
@@ -22103,13 +22103,13 @@
         <v>7</v>
       </c>
       <c r="N112" s="31" t="n">
-        <v>82.8</v>
+        <v>79.3</v>
       </c>
       <c r="O112" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P112" s="31" t="n">
-        <v>76.8</v>
+        <v>75</v>
       </c>
       <c r="Q112" s="31" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="U112" s="31" t="n">
-        <v>78.3</v>
+        <v>77.3</v>
       </c>
       <c r="V112" s="31" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="W112" s="31" t="n">
-        <v>79.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="X112" s="31" t="inlineStr">
         <is>
@@ -22208,13 +22208,13 @@
         <v>7</v>
       </c>
       <c r="N113" s="31" t="n">
-        <v>96.5</v>
+        <v>97</v>
       </c>
       <c r="O113" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P113" s="31" t="n">
-        <v>85.5</v>
+        <v>85.8</v>
       </c>
       <c r="Q113" s="31" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         </is>
       </c>
       <c r="U113" s="31" t="n">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="V113" s="31" t="inlineStr">
         <is>
@@ -22241,11 +22241,11 @@
         </is>
       </c>
       <c r="W113" s="31" t="n">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="X113" s="31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y113" s="31" t="inlineStr">
@@ -22313,13 +22313,13 @@
         <v>7</v>
       </c>
       <c r="N114" s="31" t="n">
-        <v>98.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O114" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P114" s="31" t="n">
-        <v>90</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Q114" s="31" t="inlineStr">
         <is>
@@ -22418,17 +22418,17 @@
         <v>7</v>
       </c>
       <c r="N115" s="31" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="O115" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P115" s="31" t="n">
-        <v>90</v>
+        <v>89.7</v>
       </c>
       <c r="Q115" s="31" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="R115" s="31" t="n">
@@ -22443,15 +22443,15 @@
         </is>
       </c>
       <c r="U115" s="31" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="V115" s="31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W115" s="31" t="n">
         <v>86.7</v>
-      </c>
-      <c r="V115" s="31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W115" s="31" t="n">
-        <v>86.90000000000001</v>
       </c>
       <c r="X115" s="31" t="inlineStr">
         <is>
@@ -22523,13 +22523,13 @@
         <v>7</v>
       </c>
       <c r="N116" s="31" t="n">
-        <v>96.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O116" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P116" s="31" t="n">
-        <v>89.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="Q116" s="31" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         </is>
       </c>
       <c r="U116" s="31" t="n">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="V116" s="31" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         </is>
       </c>
       <c r="W116" s="31" t="n">
-        <v>84.3</v>
+        <v>84.5</v>
       </c>
       <c r="X116" s="31" t="inlineStr">
         <is>
@@ -22628,13 +22628,13 @@
         <v>7</v>
       </c>
       <c r="N117" s="31" t="n">
-        <v>99.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="O117" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P117" s="31" t="n">
-        <v>89.7</v>
+        <v>89.5</v>
       </c>
       <c r="Q117" s="31" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         </is>
       </c>
       <c r="U117" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="V117" s="31" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         </is>
       </c>
       <c r="W117" s="31" t="n">
-        <v>87.8</v>
+        <v>87.7</v>
       </c>
       <c r="X117" s="31" t="inlineStr">
         <is>
@@ -22733,13 +22733,13 @@
         <v>7</v>
       </c>
       <c r="N118" s="31" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O118" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P118" s="31" t="n">
-        <v>89.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Q118" s="31" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="U118" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="V118" s="31" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         </is>
       </c>
       <c r="W118" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="X118" s="31" t="inlineStr">
         <is>
@@ -22838,13 +22838,13 @@
         <v>7</v>
       </c>
       <c r="N119" s="31" t="n">
-        <v>97.3</v>
+        <v>94.7</v>
       </c>
       <c r="O119" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P119" s="31" t="n">
-        <v>86.7</v>
+        <v>85.3</v>
       </c>
       <c r="Q119" s="31" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         </is>
       </c>
       <c r="U119" s="31" t="n">
-        <v>78.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V119" s="31" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         </is>
       </c>
       <c r="W119" s="31" t="n">
-        <v>79</v>
+        <v>78.3</v>
       </c>
       <c r="X119" s="31" t="inlineStr">
         <is>
@@ -22943,13 +22943,13 @@
         <v>7</v>
       </c>
       <c r="N120" s="31" t="n">
-        <v>93.8</v>
+        <v>92</v>
       </c>
       <c r="O120" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P120" s="31" t="n">
-        <v>84.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="Q120" s="31" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         </is>
       </c>
       <c r="U120" s="31" t="n">
-        <v>77.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="V120" s="31" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         </is>
       </c>
       <c r="W120" s="31" t="n">
-        <v>78.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="X120" s="31" t="inlineStr">
         <is>
@@ -23048,13 +23048,13 @@
         <v>7</v>
       </c>
       <c r="N121" s="31" t="n">
-        <v>95.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O121" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P121" s="31" t="n">
-        <v>88.2</v>
+        <v>88.3</v>
       </c>
       <c r="Q121" s="31" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         </is>
       </c>
       <c r="U121" s="31" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="V121" s="31" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         </is>
       </c>
       <c r="W121" s="31" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="X121" s="31" t="inlineStr">
         <is>
@@ -23258,10 +23258,10 @@
         <v>7</v>
       </c>
       <c r="N123" s="31" t="n">
-        <v>97.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="O123" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P123" s="31" t="n">
         <v>89.8</v>
@@ -23363,13 +23363,13 @@
         <v>7</v>
       </c>
       <c r="N124" s="31" t="n">
-        <v>96.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O124" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P124" s="31" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="Q124" s="31" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="U124" s="31" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="V124" s="31" t="inlineStr">
         <is>
@@ -23468,13 +23468,13 @@
         <v>7</v>
       </c>
       <c r="N125" s="31" t="n">
-        <v>96.3</v>
+        <v>95.7</v>
       </c>
       <c r="O125" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P125" s="31" t="n">
-        <v>89.3</v>
+        <v>89</v>
       </c>
       <c r="Q125" s="31" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         </is>
       </c>
       <c r="U125" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="V125" s="31" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         </is>
       </c>
       <c r="W125" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="X125" s="31" t="inlineStr">
         <is>
@@ -23573,13 +23573,13 @@
         <v>7</v>
       </c>
       <c r="N126" s="31" t="n">
-        <v>96</v>
+        <v>96.5</v>
       </c>
       <c r="O126" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P126" s="31" t="n">
-        <v>88.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q126" s="31" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         </is>
       </c>
       <c r="U126" s="31" t="n">
-        <v>85.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V126" s="31" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         </is>
       </c>
       <c r="W126" s="31" t="n">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="X126" s="31" t="inlineStr">
         <is>
@@ -23678,13 +23678,13 @@
         <v>7</v>
       </c>
       <c r="N127" s="31" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O127" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P127" s="31" t="n">
-        <v>89.3</v>
+        <v>89.5</v>
       </c>
       <c r="Q127" s="31" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         </is>
       </c>
       <c r="U127" s="31" t="n">
-        <v>86.7</v>
+        <v>86.8</v>
       </c>
       <c r="V127" s="31" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         </is>
       </c>
       <c r="W127" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="X127" s="31" t="inlineStr">
         <is>
@@ -23783,13 +23783,13 @@
         <v>7</v>
       </c>
       <c r="N128" s="31" t="n">
-        <v>96.2</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O128" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P128" s="31" t="n">
-        <v>86.2</v>
+        <v>83.7</v>
       </c>
       <c r="Q128" s="31" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         </is>
       </c>
       <c r="U128" s="31" t="n">
-        <v>77.5</v>
+        <v>76</v>
       </c>
       <c r="V128" s="31" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         </is>
       </c>
       <c r="W128" s="31" t="n">
-        <v>78</v>
+        <v>76.8</v>
       </c>
       <c r="X128" s="31" t="inlineStr">
         <is>
@@ -23888,13 +23888,13 @@
         <v>7</v>
       </c>
       <c r="N129" s="31" t="n">
-        <v>98.7</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O129" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P129" s="31" t="n">
-        <v>88.2</v>
+        <v>88.3</v>
       </c>
       <c r="Q129" s="31" t="inlineStr">
         <is>
@@ -23993,13 +23993,13 @@
         <v>7</v>
       </c>
       <c r="N130" s="31" t="n">
-        <v>96.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O130" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P130" s="31" t="n">
-        <v>88.5</v>
+        <v>88.7</v>
       </c>
       <c r="Q130" s="31" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         </is>
       </c>
       <c r="U130" s="31" t="n">
-        <v>85</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="V130" s="31" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         </is>
       </c>
       <c r="W130" s="31" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="X130" s="31" t="inlineStr">
         <is>
@@ -24098,13 +24098,13 @@
         <v>7</v>
       </c>
       <c r="N131" s="31" t="n">
-        <v>95</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O131" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P131" s="31" t="n">
-        <v>87.8</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Q131" s="31" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         </is>
       </c>
       <c r="U131" s="31" t="n">
-        <v>84.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="V131" s="31" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         </is>
       </c>
       <c r="W131" s="31" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="X131" s="31" t="inlineStr">
         <is>
@@ -24203,13 +24203,13 @@
         <v>7</v>
       </c>
       <c r="N132" s="31" t="n">
-        <v>95.59999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="O132" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P132" s="31" t="n">
-        <v>88.3</v>
+        <v>88</v>
       </c>
       <c r="Q132" s="31" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         </is>
       </c>
       <c r="U132" s="31" t="n">
-        <v>84.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="V132" s="31" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         </is>
       </c>
       <c r="W132" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="X132" s="31" t="inlineStr">
         <is>
@@ -24308,13 +24308,13 @@
         <v>7</v>
       </c>
       <c r="N133" s="31" t="n">
-        <v>99.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="O133" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P133" s="31" t="n">
-        <v>90.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Q133" s="31" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         </is>
       </c>
       <c r="U133" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="V133" s="31" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         </is>
       </c>
       <c r="W133" s="31" t="n">
-        <v>88</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X133" s="31" t="inlineStr">
         <is>
@@ -24413,13 +24413,13 @@
         <v>7</v>
       </c>
       <c r="N134" s="31" t="n">
-        <v>99.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="O134" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P134" s="31" t="n">
-        <v>90.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="Q134" s="31" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         </is>
       </c>
       <c r="U134" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="V134" s="31" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         </is>
       </c>
       <c r="W134" s="31" t="n">
-        <v>88.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="X134" s="31" t="inlineStr">
         <is>
@@ -24518,13 +24518,13 @@
         <v>7</v>
       </c>
       <c r="N135" s="31" t="n">
-        <v>95.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O135" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P135" s="31" t="n">
-        <v>83.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Q135" s="31" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         </is>
       </c>
       <c r="U135" s="31" t="n">
-        <v>78.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="V135" s="31" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         </is>
       </c>
       <c r="W135" s="31" t="n">
-        <v>80.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="X135" s="31" t="inlineStr">
         <is>
@@ -24623,13 +24623,13 @@
         <v>7</v>
       </c>
       <c r="N136" s="31" t="n">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O136" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P136" s="31" t="n">
-        <v>86.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Q136" s="31" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         </is>
       </c>
       <c r="U136" s="31" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="V136" s="31" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         </is>
       </c>
       <c r="W136" s="31" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="X136" s="31" t="inlineStr">
         <is>
@@ -24728,13 +24728,13 @@
         <v>7</v>
       </c>
       <c r="N137" s="31" t="n">
-        <v>96.3</v>
+        <v>96.7</v>
       </c>
       <c r="O137" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P137" s="31" t="n">
-        <v>89.2</v>
+        <v>89.3</v>
       </c>
       <c r="Q137" s="31" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         </is>
       </c>
       <c r="W137" s="31" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X137" s="31" t="inlineStr">
         <is>
@@ -24833,13 +24833,13 @@
         <v>7</v>
       </c>
       <c r="N138" s="31" t="n">
-        <v>95.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O138" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P138" s="31" t="n">
-        <v>88.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q138" s="31" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         </is>
       </c>
       <c r="U138" s="31" t="n">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="V138" s="31" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         </is>
       </c>
       <c r="W138" s="31" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="X138" s="31" t="inlineStr">
         <is>
@@ -24938,13 +24938,13 @@
         <v>7</v>
       </c>
       <c r="N139" s="31" t="n">
-        <v>91.2</v>
+        <v>92.7</v>
       </c>
       <c r="O139" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P139" s="31" t="n">
-        <v>84.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="Q139" s="31" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         </is>
       </c>
       <c r="U139" s="31" t="n">
-        <v>77.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="V139" s="31" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         </is>
       </c>
       <c r="W139" s="31" t="n">
-        <v>79</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="X139" s="31" t="inlineStr">
         <is>
@@ -25043,13 +25043,13 @@
         <v>7</v>
       </c>
       <c r="N140" s="31" t="n">
-        <v>91.5</v>
+        <v>87.2</v>
       </c>
       <c r="O140" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P140" s="31" t="n">
-        <v>83.7</v>
+        <v>81.5</v>
       </c>
       <c r="Q140" s="31" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         </is>
       </c>
       <c r="U140" s="31" t="n">
-        <v>75.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="V140" s="31" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="W140" s="31" t="n">
-        <v>78.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="X140" s="31" t="inlineStr">
         <is>
@@ -25148,13 +25148,13 @@
         <v>7</v>
       </c>
       <c r="N141" s="31" t="n">
-        <v>84.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="O141" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P141" s="31" t="n">
-        <v>75.7</v>
+        <v>74.2</v>
       </c>
       <c r="Q141" s="31" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         </is>
       </c>
       <c r="U141" s="31" t="n">
-        <v>79.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="V141" s="31" t="inlineStr">
         <is>
@@ -25181,11 +25181,11 @@
         </is>
       </c>
       <c r="W141" s="31" t="n">
-        <v>80.2</v>
+        <v>79.5</v>
       </c>
       <c r="X141" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y141" s="31" t="inlineStr">
@@ -25266,7 +25266,7 @@
         <v>97.2</v>
       </c>
       <c r="D3" s="31" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="4">
@@ -25282,7 +25282,7 @@
         <v>96</v>
       </c>
       <c r="D4" s="31" t="n">
-        <v>79.90000000000001</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="5">
@@ -25298,7 +25298,7 @@
         <v>96.3</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>86.8</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="6">
@@ -25314,7 +25314,7 @@
         <v>96.5</v>
       </c>
       <c r="D6" s="31" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
     </row>
   </sheetData>

--- a/test/published_reports/pmq_client_dashboard.xlsx
+++ b/test/published_reports/pmq_client_dashboard.xlsx
@@ -1618,7 +1618,7 @@
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>Average overall performance score is 85.9, which is currently stable.</t>
+          <t>Average overall performance score is 85.8, which is currently stable.</t>
         </is>
       </c>
       <c r="B31" s="23" t="n"/>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="B9" s="31" t="n">
-        <v>89</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="10">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="B12" s="31" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="B13" s="31" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="14">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="B14" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
     </row>
   </sheetData>
@@ -2790,7 +2790,7 @@
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
         <is>
-          <t>Average overall performance score is 85.9, which is currently stable.</t>
+          <t>Average overall performance score is 85.8, which is currently stable.</t>
         </is>
       </c>
       <c r="B5" s="31" t="inlineStr">
@@ -3027,22 +3027,22 @@
         </is>
       </c>
       <c r="G2" s="31" t="n">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H2" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="I2" s="31" t="n">
-        <v>89.8</v>
+        <v>90</v>
       </c>
       <c r="J2" s="31" t="n">
         <v>80.5</v>
       </c>
       <c r="K2" s="31" t="n">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="L2" s="31" t="n">
-        <v>64.2</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -3077,22 +3077,22 @@
         </is>
       </c>
       <c r="G3" s="31" t="n">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H3" s="31" t="n">
-        <v>85.8</v>
+        <v>86.2</v>
       </c>
       <c r="I3" s="31" t="n">
-        <v>89</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J3" s="31" t="n">
         <v>81</v>
       </c>
       <c r="K3" s="31" t="n">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="L3" s="31" t="n">
-        <v>74.2</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="4">
@@ -3127,13 +3127,13 @@
         </is>
       </c>
       <c r="G4" s="31" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H4" s="31" t="n">
-        <v>84.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="I4" s="31" t="n">
-        <v>89.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="J4" s="31" t="n">
         <v>74.5</v>
@@ -3142,7 +3142,7 @@
         <v>99</v>
       </c>
       <c r="L4" s="31" t="n">
-        <v>75.8</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -3177,19 +3177,19 @@
         </is>
       </c>
       <c r="G5" s="31" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="H5" s="31" t="n">
         <v>86.7</v>
       </c>
       <c r="I5" s="31" t="n">
-        <v>90</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J5" s="31" t="n">
         <v>81</v>
       </c>
       <c r="K5" s="31" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="L5" s="31" t="n">
         <v>77.59999999999999</v>
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="G6" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="H6" s="31" t="n">
-        <v>87.2</v>
+        <v>87.3</v>
       </c>
       <c r="I6" s="31" t="n">
-        <v>89.7</v>
+        <v>89.8</v>
       </c>
       <c r="J6" s="31" t="n">
         <v>81</v>
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="G7" s="31" t="n">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H7" s="31" t="n">
-        <v>86</v>
+        <v>86.2</v>
       </c>
       <c r="I7" s="31" t="n">
-        <v>90.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="J7" s="31" t="n">
         <v>79.5</v>
       </c>
       <c r="K7" s="31" t="n">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="L7" s="31" t="n">
-        <v>72.40000000000001</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
@@ -3327,22 +3327,22 @@
         </is>
       </c>
       <c r="G8" s="31" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H8" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="I8" s="31" t="n">
-        <v>90.7</v>
+        <v>90.8</v>
       </c>
       <c r="J8" s="31" t="n">
         <v>80.5</v>
       </c>
       <c r="K8" s="31" t="n">
-        <v>93.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="L8" s="31" t="n">
-        <v>73.40000000000001</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="9">
@@ -3380,19 +3380,19 @@
         <v>85.09999999999999</v>
       </c>
       <c r="H9" s="31" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="I9" s="31" t="n">
-        <v>89</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J9" s="31" t="n">
         <v>79.5</v>
       </c>
       <c r="K9" s="31" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="L9" s="31" t="n">
-        <v>67.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -3427,13 +3427,13 @@
         </is>
       </c>
       <c r="G10" s="31" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H10" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="I10" s="31" t="n">
-        <v>89.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="J10" s="31" t="n">
         <v>81</v>
@@ -3442,7 +3442,7 @@
         <v>100</v>
       </c>
       <c r="L10" s="31" t="n">
-        <v>76.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -3477,22 +3477,22 @@
         </is>
       </c>
       <c r="G11" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="H11" s="31" t="n">
-        <v>87.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I11" s="31" t="n">
-        <v>90.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J11" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K11" s="31" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="L11" s="31" t="n">
-        <v>91.59999999999999</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="12">
@@ -3527,22 +3527,22 @@
         </is>
       </c>
       <c r="G12" s="31" t="n">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H12" s="31" t="n">
         <v>86.5</v>
       </c>
       <c r="I12" s="31" t="n">
-        <v>90</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J12" s="31" t="n">
         <v>81.5</v>
       </c>
       <c r="K12" s="31" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L12" s="31" t="n">
-        <v>65.8</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3577,22 +3577,22 @@
         </is>
       </c>
       <c r="G13" s="31" t="n">
-        <v>81.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="H13" s="31" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="I13" s="31" t="n">
-        <v>83.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="J13" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K13" s="31" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="L13" s="31" t="n">
-        <v>69.2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -3627,22 +3627,22 @@
         </is>
       </c>
       <c r="G14" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="H14" s="31" t="n">
-        <v>87.2</v>
+        <v>82.3</v>
       </c>
       <c r="I14" s="31" t="n">
-        <v>90.3</v>
+        <v>82.2</v>
       </c>
       <c r="J14" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K14" s="31" t="n">
-        <v>98</v>
+        <v>93.3</v>
       </c>
       <c r="L14" s="31" t="n">
-        <v>85</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -3677,22 +3677,22 @@
         </is>
       </c>
       <c r="G15" s="31" t="n">
-        <v>84.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="H15" s="31" t="n">
-        <v>84.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="I15" s="31" t="n">
-        <v>88.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J15" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K15" s="31" t="n">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="L15" s="31" t="n">
-        <v>67.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3742,7 +3742,7 @@
         <v>100</v>
       </c>
       <c r="L16" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>86.19999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3777,22 +3777,22 @@
         </is>
       </c>
       <c r="G17" s="31" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H17" s="31" t="n">
-        <v>83</v>
+        <v>83.2</v>
       </c>
       <c r="I17" s="31" t="n">
-        <v>85.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="J17" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K17" s="31" t="n">
-        <v>90.90000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="L17" s="31" t="n">
-        <v>66.59999999999999</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="18">
@@ -3830,19 +3830,19 @@
         <v>86.3</v>
       </c>
       <c r="H18" s="31" t="n">
-        <v>87.3</v>
+        <v>87.5</v>
       </c>
       <c r="I18" s="31" t="n">
-        <v>90.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J18" s="31" t="n">
         <v>80.5</v>
       </c>
       <c r="K18" s="31" t="n">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="L18" s="31" t="n">
-        <v>84.2</v>
+        <v>85.39999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -3877,22 +3877,22 @@
         </is>
       </c>
       <c r="G19" s="31" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H19" s="31" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I19" s="31" t="n">
-        <v>84.8</v>
+        <v>85</v>
       </c>
       <c r="J19" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K19" s="31" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L19" s="31" t="n">
-        <v>67.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -3942,7 +3942,7 @@
         <v>99</v>
       </c>
       <c r="L20" s="31" t="n">
-        <v>79.2</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="21">
@@ -3977,13 +3977,13 @@
         </is>
       </c>
       <c r="G21" s="31" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H21" s="31" t="n">
-        <v>86.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I21" s="31" t="n">
-        <v>89.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="J21" s="31" t="n">
         <v>80</v>
@@ -3992,7 +3992,7 @@
         <v>99</v>
       </c>
       <c r="L21" s="31" t="n">
-        <v>83.40000000000001</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22">
@@ -4027,22 +4027,22 @@
         </is>
       </c>
       <c r="G22" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="H22" s="31" t="n">
-        <v>85.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="I22" s="31" t="n">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="J22" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K22" s="31" t="n">
-        <v>93.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="L22" s="31" t="n">
-        <v>64.2</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="H2" s="31" t="n">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I2" s="31" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="J2" s="31" t="n">
-        <v>64.2</v>
+        <v>67</v>
       </c>
       <c r="K2" s="31" t="inlineStr">
         <is>
@@ -4273,17 +4273,17 @@
         <v>9</v>
       </c>
       <c r="N2" s="31" t="n">
-        <v>97.40000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="O2" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>89.8</v>
+        <v>90</v>
       </c>
       <c r="Q2" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="R2" s="31" t="n">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="U2" s="31" t="n">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="V2" s="31" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="W2" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="X2" s="31" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="H3" s="31" t="n">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="I3" s="31" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         </is>
       </c>
       <c r="J3" s="31" t="n">
-        <v>74.2</v>
+        <v>76.2</v>
       </c>
       <c r="K3" s="31" t="inlineStr">
         <is>
@@ -4378,13 +4378,13 @@
         <v>9</v>
       </c>
       <c r="N3" s="31" t="n">
-        <v>96.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="O3" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>89</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="Q3" s="31" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="U3" s="31" t="n">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="V3" s="31" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="W3" s="31" t="n">
-        <v>85.8</v>
+        <v>86.2</v>
       </c>
       <c r="X3" s="31" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="J4" s="31" t="n">
-        <v>75.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K4" s="31" t="inlineStr">
         <is>
@@ -4483,13 +4483,13 @@
         <v>9</v>
       </c>
       <c r="N4" s="31" t="n">
-        <v>97.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O4" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>89.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Q4" s="31" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="U4" s="31" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="V4" s="31" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="W4" s="31" t="n">
-        <v>84.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="X4" s="31" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="H5" s="31" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="I5" s="31" t="inlineStr">
         <is>
@@ -4588,17 +4588,17 @@
         <v>9</v>
       </c>
       <c r="N5" s="31" t="n">
-        <v>97.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O5" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P5" s="31" t="n">
-        <v>90</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="Q5" s="31" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="R5" s="31" t="n">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="U5" s="31" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="V5" s="31" t="inlineStr">
         <is>
@@ -4693,13 +4693,13 @@
         <v>9</v>
       </c>
       <c r="N6" s="31" t="n">
-        <v>97.7</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O6" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>89.7</v>
+        <v>89.8</v>
       </c>
       <c r="Q6" s="31" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="U6" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="V6" s="31" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="W6" s="31" t="n">
-        <v>87.2</v>
+        <v>87.3</v>
       </c>
       <c r="X6" s="31" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="H7" s="31" t="n">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="I7" s="31" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         </is>
       </c>
       <c r="J7" s="31" t="n">
-        <v>72.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="K7" s="31" t="inlineStr">
         <is>
@@ -4798,13 +4798,13 @@
         <v>9</v>
       </c>
       <c r="N7" s="31" t="n">
-        <v>98.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O7" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P7" s="31" t="n">
-        <v>90.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="Q7" s="31" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="U7" s="31" t="n">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="V7" s="31" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="W7" s="31" t="n">
-        <v>86</v>
+        <v>86.2</v>
       </c>
       <c r="X7" s="31" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="H8" s="31" t="n">
-        <v>93.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="I8" s="31" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="J8" s="31" t="n">
-        <v>73.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="K8" s="31" t="inlineStr">
         <is>
@@ -4903,13 +4903,13 @@
         <v>9</v>
       </c>
       <c r="N8" s="31" t="n">
-        <v>99.09999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="O8" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>90.7</v>
+        <v>90.8</v>
       </c>
       <c r="Q8" s="31" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="U8" s="31" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="V8" s="31" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="W8" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="X8" s="31" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="H9" s="31" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="I9" s="31" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="J9" s="31" t="n">
-        <v>67.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K9" s="31" t="inlineStr">
         <is>
@@ -5008,13 +5008,13 @@
         <v>9</v>
       </c>
       <c r="N9" s="31" t="n">
-        <v>95.5</v>
+        <v>95.7</v>
       </c>
       <c r="O9" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>89</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q9" s="31" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="W9" s="31" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="X9" s="31" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="J10" s="31" t="n">
-        <v>76.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K10" s="31" t="inlineStr">
         <is>
@@ -5113,17 +5113,17 @@
         <v>9</v>
       </c>
       <c r="N10" s="31" t="n">
-        <v>98.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O10" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>89.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Q10" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="R10" s="31" t="n">
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="U10" s="31" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="V10" s="31" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="W10" s="31" t="n">
-        <v>87.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="X10" s="31" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="H11" s="31" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="I11" s="31" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="J11" s="31" t="n">
-        <v>91.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="K11" s="31" t="inlineStr">
         <is>
@@ -5218,13 +5218,13 @@
         <v>9</v>
       </c>
       <c r="N11" s="31" t="n">
-        <v>98</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O11" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>90.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q11" s="31" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="U11" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="V11" s="31" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="W11" s="31" t="n">
-        <v>87.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="X11" s="31" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="H12" s="31" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I12" s="31" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="J12" s="31" t="n">
-        <v>65.8</v>
+        <v>67</v>
       </c>
       <c r="K12" s="31" t="inlineStr">
         <is>
@@ -5323,17 +5323,17 @@
         <v>9</v>
       </c>
       <c r="N12" s="31" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O12" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>90</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="Q12" s="31" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="R12" s="31" t="n">
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="U12" s="31" t="n">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="V12" s="31" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="H13" s="31" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="I13" s="31" t="inlineStr">
         <is>
@@ -5414,11 +5414,11 @@
         </is>
       </c>
       <c r="J13" s="31" t="n">
-        <v>69.2</v>
+        <v>70</v>
       </c>
       <c r="K13" s="31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L13" s="31" t="n">
@@ -5428,13 +5428,13 @@
         <v>9</v>
       </c>
       <c r="N13" s="31" t="n">
-        <v>93.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="O13" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>83.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Q13" s="31" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="U13" s="31" t="n">
-        <v>81.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="V13" s="31" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         </is>
       </c>
       <c r="W13" s="31" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="X13" s="31" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="H14" s="31" t="n">
-        <v>98</v>
+        <v>93.3</v>
       </c>
       <c r="I14" s="31" t="inlineStr">
         <is>
@@ -5519,11 +5519,11 @@
         </is>
       </c>
       <c r="J14" s="31" t="n">
-        <v>85</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K14" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L14" s="31" t="n">
@@ -5533,17 +5533,17 @@
         <v>9</v>
       </c>
       <c r="N14" s="31" t="n">
-        <v>98.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="O14" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>90.3</v>
+        <v>82.2</v>
       </c>
       <c r="Q14" s="31" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="R14" s="31" t="n">
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="U14" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="V14" s="31" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="W14" s="31" t="n">
-        <v>87.2</v>
+        <v>82.3</v>
       </c>
       <c r="X14" s="31" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="H15" s="31" t="n">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="I15" s="31" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         </is>
       </c>
       <c r="J15" s="31" t="n">
-        <v>67.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K15" s="31" t="inlineStr">
         <is>
@@ -5638,13 +5638,13 @@
         <v>9</v>
       </c>
       <c r="N15" s="31" t="n">
-        <v>94.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="O15" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>88.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q15" s="31" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="U15" s="31" t="n">
-        <v>84.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="V15" s="31" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="W15" s="31" t="n">
-        <v>84.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="X15" s="31" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         </is>
       </c>
       <c r="J16" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>86.19999999999999</v>
       </c>
       <c r="K16" s="31" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>99.5</v>
       </c>
       <c r="O16" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P16" s="31" t="n">
         <v>90.8</v>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="H17" s="31" t="n">
-        <v>90.90000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="I17" s="31" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="J17" s="31" t="n">
-        <v>66.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="K17" s="31" t="inlineStr">
         <is>
@@ -5848,13 +5848,13 @@
         <v>9</v>
       </c>
       <c r="N17" s="31" t="n">
-        <v>96.8</v>
+        <v>97.3</v>
       </c>
       <c r="O17" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P17" s="31" t="n">
-        <v>85.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="Q17" s="31" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="U17" s="31" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="V17" s="31" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="W17" s="31" t="n">
-        <v>83</v>
+        <v>83.2</v>
       </c>
       <c r="X17" s="31" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="H18" s="31" t="n">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I18" s="31" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="J18" s="31" t="n">
-        <v>84.2</v>
+        <v>85.39999999999999</v>
       </c>
       <c r="K18" s="31" t="inlineStr">
         <is>
@@ -5953,13 +5953,13 @@
         <v>9</v>
       </c>
       <c r="N18" s="31" t="n">
-        <v>98.3</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O18" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P18" s="31" t="n">
-        <v>90.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Q18" s="31" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="W18" s="31" t="n">
-        <v>87.3</v>
+        <v>87.5</v>
       </c>
       <c r="X18" s="31" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="H19" s="31" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I19" s="31" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="J19" s="31" t="n">
-        <v>67.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K19" s="31" t="inlineStr">
         <is>
@@ -6058,13 +6058,13 @@
         <v>9</v>
       </c>
       <c r="N19" s="31" t="n">
-        <v>96.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="O19" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P19" s="31" t="n">
-        <v>84.8</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="31" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="U19" s="31" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="V19" s="31" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="W19" s="31" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="X19" s="31" t="inlineStr">
         <is>
@@ -6149,11 +6149,11 @@
         </is>
       </c>
       <c r="J20" s="31" t="n">
-        <v>79.2</v>
+        <v>80.8</v>
       </c>
       <c r="K20" s="31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L20" s="31" t="n">
@@ -6166,7 +6166,7 @@
         <v>96.59999999999999</v>
       </c>
       <c r="O20" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P20" s="31" t="n">
         <v>89</v>
@@ -6254,7 +6254,7 @@
         </is>
       </c>
       <c r="J21" s="31" t="n">
-        <v>83.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="K21" s="31" t="inlineStr">
         <is>
@@ -6268,13 +6268,13 @@
         <v>9</v>
       </c>
       <c r="N21" s="31" t="n">
-        <v>96.8</v>
+        <v>97.3</v>
       </c>
       <c r="O21" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P21" s="31" t="n">
-        <v>89.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Q21" s="31" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="U21" s="31" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="V21" s="31" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         </is>
       </c>
       <c r="W21" s="31" t="n">
-        <v>86.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="X21" s="31" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="H22" s="31" t="n">
-        <v>93.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="I22" s="31" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="J22" s="31" t="n">
-        <v>64.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K22" s="31" t="inlineStr">
         <is>
@@ -6373,13 +6373,13 @@
         <v>9</v>
       </c>
       <c r="N22" s="31" t="n">
-        <v>97.7</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O22" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P22" s="31" t="n">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="Q22" s="31" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="U22" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="V22" s="31" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="W22" s="31" t="n">
-        <v>85.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="X22" s="31" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>96.2</v>
       </c>
       <c r="D2" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
     </row>
   </sheetData>

--- a/test/published_reports/pmq_client_dashboard.xlsx
+++ b/test/published_reports/pmq_client_dashboard.xlsx
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1351,11 +1351,11 @@
     </row>
     <row r="13">
       <c r="A13" s="19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="18" t="n"/>
       <c r="C13" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="18" t="n"/>
       <c r="E13" s="19" t="n">
@@ -1438,7 +1438,7 @@
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>100% of the active only cohort are deployment-ready.</t>
+          <t>95% of the active only cohort are deployment-ready.</t>
         </is>
       </c>
       <c r="B19" s="23" t="n"/>
@@ -1498,7 +1498,7 @@
     <row r="23">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>0% are in the B-grade progressing band.</t>
+          <t>5% are in the B-grade progressing band.</t>
         </is>
       </c>
       <c r="B23" s="23" t="n"/>
@@ -1618,7 +1618,7 @@
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>Average overall performance score is 85.8, which is currently stable.</t>
+          <t>Average overall performance score is 85.9, which is currently stable.</t>
         </is>
       </c>
       <c r="B31" s="23" t="n"/>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="B38" s="30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
@@ -1725,7 +1725,6 @@
 6209197 - Srishti Beaspal
 6209915 - Adish Jain
 6270470 - Arya Vajpai
-6280489 - Gautam Saraswat
 6285699 - Yash Mittal
 6745439 - Aditya Darda
 6753886 - Palak
@@ -1779,11 +1778,11 @@
         </is>
       </c>
       <c r="B42" s="30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>No candidates in this segment.</t>
+          <t>6280489 - Gautam Saraswat</t>
         </is>
       </c>
       <c r="D42" s="30" t="n"/>
@@ -2413,7 +2412,7 @@
         </is>
       </c>
       <c r="B9" s="31" t="n">
-        <v>88.8</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2443,7 +2442,7 @@
         </is>
       </c>
       <c r="B12" s="31" t="n">
-        <v>75.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2453,7 +2452,7 @@
         </is>
       </c>
       <c r="B13" s="31" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="14">
@@ -2463,7 +2462,7 @@
         </is>
       </c>
       <c r="B14" s="31" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2516,7 +2515,7 @@
         </is>
       </c>
       <c r="B2" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="31" t="inlineStr">
         <is>
@@ -2536,7 +2535,7 @@
         </is>
       </c>
       <c r="B3" s="31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="31" t="inlineStr">
         <is>
@@ -2754,7 +2753,7 @@
     <row r="2">
       <c r="A2" s="31" t="inlineStr">
         <is>
-          <t>100% of the active only cohort are deployment-ready.</t>
+          <t>95% of the active only cohort are deployment-ready.</t>
         </is>
       </c>
       <c r="B2" s="31" t="inlineStr">
@@ -2766,7 +2765,7 @@
     <row r="3">
       <c r="A3" s="31" t="inlineStr">
         <is>
-          <t>0% are in the B-grade progressing band.</t>
+          <t>5% are in the B-grade progressing band.</t>
         </is>
       </c>
       <c r="B3" s="31" t="inlineStr">
@@ -2790,7 +2789,7 @@
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
         <is>
-          <t>Average overall performance score is 85.8, which is currently stable.</t>
+          <t>Average overall performance score is 85.9, which is currently stable.</t>
         </is>
       </c>
       <c r="B5" s="31" t="inlineStr">
@@ -2843,7 +2842,7 @@
         </is>
       </c>
       <c r="B2" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="31" t="inlineStr">
         <is>
@@ -2859,7 +2858,6 @@
 6209197 - Srishti Beaspal
 6209915 - Adish Jain
 6270470 - Arya Vajpai
-6280489 - Gautam Saraswat
 6285699 - Yash Mittal
 6745439 - Aditya Darda
 6753886 - Palak
@@ -2878,9 +2876,13 @@
         </is>
       </c>
       <c r="B3" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>6280489 - Gautam Saraswat</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2924,7 +2926,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
@@ -3027,22 +3029,22 @@
         </is>
       </c>
       <c r="G2" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H2" s="31" t="n">
-        <v>86.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I2" s="31" t="n">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="J2" s="31" t="n">
         <v>80.5</v>
       </c>
       <c r="K2" s="31" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="L2" s="31" t="n">
-        <v>67</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="3">
@@ -3077,22 +3079,22 @@
         </is>
       </c>
       <c r="G3" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H3" s="31" t="n">
-        <v>86.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I3" s="31" t="n">
-        <v>89.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="J3" s="31" t="n">
         <v>81</v>
       </c>
       <c r="K3" s="31" t="n">
-        <v>93.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="L3" s="31" t="n">
-        <v>76.2</v>
+        <v>76.39999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -3127,22 +3129,22 @@
         </is>
       </c>
       <c r="G4" s="31" t="n">
-        <v>83.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="H4" s="31" t="n">
-        <v>84.7</v>
+        <v>85</v>
       </c>
       <c r="I4" s="31" t="n">
-        <v>89.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="J4" s="31" t="n">
         <v>74.5</v>
       </c>
       <c r="K4" s="31" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L4" s="31" t="n">
-        <v>77.59999999999999</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="5">
@@ -3177,22 +3179,22 @@
         </is>
       </c>
       <c r="G5" s="31" t="n">
-        <v>86.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H5" s="31" t="n">
-        <v>86.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I5" s="31" t="n">
-        <v>89.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="J5" s="31" t="n">
         <v>81</v>
       </c>
       <c r="K5" s="31" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="L5" s="31" t="n">
-        <v>77.59999999999999</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="6">
@@ -3227,22 +3229,22 @@
         </is>
       </c>
       <c r="G6" s="31" t="n">
-        <v>86.2</v>
+        <v>86.8</v>
       </c>
       <c r="H6" s="31" t="n">
-        <v>87.3</v>
+        <v>87.8</v>
       </c>
       <c r="I6" s="31" t="n">
-        <v>89.8</v>
+        <v>90.8</v>
       </c>
       <c r="J6" s="31" t="n">
         <v>81</v>
       </c>
       <c r="K6" s="31" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L6" s="31" t="n">
-        <v>82.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -3277,22 +3279,22 @@
         </is>
       </c>
       <c r="G7" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H7" s="31" t="n">
-        <v>86.2</v>
+        <v>86.5</v>
       </c>
       <c r="I7" s="31" t="n">
-        <v>90.7</v>
+        <v>91.3</v>
       </c>
       <c r="J7" s="31" t="n">
         <v>79.5</v>
       </c>
       <c r="K7" s="31" t="n">
-        <v>93.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="L7" s="31" t="n">
-        <v>73</v>
+        <v>73.60000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -3327,22 +3329,22 @@
         </is>
       </c>
       <c r="G8" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H8" s="31" t="n">
-        <v>86.7</v>
+        <v>87</v>
       </c>
       <c r="I8" s="31" t="n">
-        <v>90.8</v>
+        <v>91.3</v>
       </c>
       <c r="J8" s="31" t="n">
         <v>80.5</v>
       </c>
       <c r="K8" s="31" t="n">
-        <v>94.2</v>
+        <v>94.5</v>
       </c>
       <c r="L8" s="31" t="n">
-        <v>73.8</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="9">
@@ -3377,22 +3379,22 @@
         </is>
       </c>
       <c r="G9" s="31" t="n">
-        <v>85.09999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="H9" s="31" t="n">
-        <v>85.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I9" s="31" t="n">
-        <v>89.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="J9" s="31" t="n">
         <v>79.5</v>
       </c>
       <c r="K9" s="31" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="L9" s="31" t="n">
-        <v>68.40000000000001</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="10">
@@ -3427,13 +3429,13 @@
         </is>
       </c>
       <c r="G10" s="31" t="n">
-        <v>86.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="H10" s="31" t="n">
-        <v>87.3</v>
+        <v>87.7</v>
       </c>
       <c r="I10" s="31" t="n">
-        <v>90.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="J10" s="31" t="n">
         <v>81</v>
@@ -3442,7 +3444,7 @@
         <v>100</v>
       </c>
       <c r="L10" s="31" t="n">
-        <v>78.40000000000001</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -3477,22 +3479,22 @@
         </is>
       </c>
       <c r="G11" s="31" t="n">
-        <v>86.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H11" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="I11" s="31" t="n">
-        <v>90.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="J11" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K11" s="31" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="L11" s="31" t="n">
-        <v>90.8</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -3527,22 +3529,22 @@
         </is>
       </c>
       <c r="G12" s="31" t="n">
-        <v>86.40000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H12" s="31" t="n">
-        <v>86.5</v>
+        <v>87</v>
       </c>
       <c r="I12" s="31" t="n">
-        <v>89.90000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="J12" s="31" t="n">
         <v>81.5</v>
       </c>
       <c r="K12" s="31" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="L12" s="31" t="n">
-        <v>67</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="13">
@@ -3577,22 +3579,22 @@
         </is>
       </c>
       <c r="G13" s="31" t="n">
-        <v>82.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H13" s="31" t="n">
-        <v>83</v>
+        <v>83.7</v>
       </c>
       <c r="I13" s="31" t="n">
-        <v>83.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="J13" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K13" s="31" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="L13" s="31" t="n">
-        <v>70</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="14">
@@ -3623,26 +3625,26 @@
       </c>
       <c r="F14" s="31" t="inlineStr">
         <is>
-          <t>Deployable Candidates</t>
+          <t>Progressing Candidates</t>
         </is>
       </c>
       <c r="G14" s="31" t="n">
-        <v>81.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H14" s="31" t="n">
-        <v>82.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I14" s="31" t="n">
-        <v>82.2</v>
+        <v>72.2</v>
       </c>
       <c r="J14" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K14" s="31" t="n">
-        <v>93.3</v>
+        <v>89</v>
       </c>
       <c r="L14" s="31" t="n">
-        <v>78.40000000000001</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="15">
@@ -3677,22 +3679,22 @@
         </is>
       </c>
       <c r="G15" s="31" t="n">
-        <v>85.2</v>
+        <v>85.8</v>
       </c>
       <c r="H15" s="31" t="n">
-        <v>85.2</v>
+        <v>85.8</v>
       </c>
       <c r="I15" s="31" t="n">
-        <v>88.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="J15" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K15" s="31" t="n">
-        <v>93.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="L15" s="31" t="n">
-        <v>68.40000000000001</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="16">
@@ -3727,13 +3729,13 @@
         </is>
       </c>
       <c r="G16" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H16" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="I16" s="31" t="n">
-        <v>90.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J16" s="31" t="n">
         <v>79</v>
@@ -3742,7 +3744,7 @@
         <v>100</v>
       </c>
       <c r="L16" s="31" t="n">
-        <v>86.19999999999999</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="17">
@@ -3777,22 +3779,22 @@
         </is>
       </c>
       <c r="G17" s="31" t="n">
-        <v>83.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H17" s="31" t="n">
-        <v>83.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I17" s="31" t="n">
-        <v>85.3</v>
+        <v>85.8</v>
       </c>
       <c r="J17" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K17" s="31" t="n">
-        <v>91.3</v>
+        <v>91.7</v>
       </c>
       <c r="L17" s="31" t="n">
-        <v>69.2</v>
+        <v>71.39999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -3827,22 +3829,22 @@
         </is>
       </c>
       <c r="G18" s="31" t="n">
-        <v>86.3</v>
+        <v>86.8</v>
       </c>
       <c r="H18" s="31" t="n">
-        <v>87.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I18" s="31" t="n">
-        <v>90.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="J18" s="31" t="n">
         <v>80.5</v>
       </c>
       <c r="K18" s="31" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="L18" s="31" t="n">
-        <v>85.39999999999999</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -3877,22 +3879,22 @@
         </is>
       </c>
       <c r="G19" s="31" t="n">
-        <v>82.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H19" s="31" t="n">
-        <v>83.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="I19" s="31" t="n">
-        <v>85</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="J19" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K19" s="31" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="L19" s="31" t="n">
-        <v>68.40000000000001</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="20">
@@ -3927,22 +3929,22 @@
         </is>
       </c>
       <c r="G20" s="31" t="n">
-        <v>85.3</v>
+        <v>85.8</v>
       </c>
       <c r="H20" s="31" t="n">
-        <v>86.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="I20" s="31" t="n">
-        <v>89</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J20" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K20" s="31" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L20" s="31" t="n">
-        <v>80.8</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="21">
@@ -3977,22 +3979,22 @@
         </is>
       </c>
       <c r="G21" s="31" t="n">
-        <v>85.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="H21" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="I21" s="31" t="n">
-        <v>89.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="J21" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K21" s="31" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L21" s="31" t="n">
-        <v>83</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="22">
@@ -4027,22 +4029,22 @@
         </is>
       </c>
       <c r="G22" s="31" t="n">
-        <v>86</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H22" s="31" t="n">
-        <v>85.8</v>
+        <v>86.2</v>
       </c>
       <c r="I22" s="31" t="n">
-        <v>90.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J22" s="31" t="n">
         <v>80</v>
       </c>
       <c r="K22" s="31" t="n">
-        <v>94.2</v>
+        <v>94.5</v>
       </c>
       <c r="L22" s="31" t="n">
-        <v>65.40000000000001</v>
+        <v>66.39999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4084,7 +4086,7 @@
     <col width="19" customWidth="1" min="22" max="22"/>
     <col width="27" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="23" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4251,35 +4253,35 @@
         </is>
       </c>
       <c r="H2" s="31" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="J2" s="31" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="K2" s="31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L2" s="31" t="n">
+        <v>83</v>
+      </c>
+      <c r="M2" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" s="31" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="I2" s="31" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="J2" s="31" t="n">
-        <v>67</v>
-      </c>
-      <c r="K2" s="31" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L2" s="31" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="M2" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="N2" s="31" t="n">
-        <v>97.8</v>
-      </c>
       <c r="O2" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="Q2" s="31" t="inlineStr">
         <is>
@@ -4298,7 +4300,7 @@
         </is>
       </c>
       <c r="U2" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="V2" s="31" t="inlineStr">
         <is>
@@ -4306,7 +4308,7 @@
         </is>
       </c>
       <c r="W2" s="31" t="n">
-        <v>86.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="X2" s="31" t="inlineStr">
         <is>
@@ -4356,7 +4358,7 @@
         </is>
       </c>
       <c r="H3" s="31" t="n">
-        <v>93.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I3" s="31" t="inlineStr">
         <is>
@@ -4364,7 +4366,7 @@
         </is>
       </c>
       <c r="J3" s="31" t="n">
-        <v>76.2</v>
+        <v>76.39999999999999</v>
       </c>
       <c r="K3" s="31" t="inlineStr">
         <is>
@@ -4372,23 +4374,23 @@
         </is>
       </c>
       <c r="L3" s="31" t="n">
-        <v>82</v>
+        <v>83.2</v>
       </c>
       <c r="M3" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" s="31" t="n">
-        <v>96.8</v>
+        <v>97.2</v>
       </c>
       <c r="O3" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P3" s="31" t="n">
-        <v>89.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="Q3" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="R3" s="31" t="n">
@@ -4403,7 +4405,7 @@
         </is>
       </c>
       <c r="U3" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="V3" s="31" t="inlineStr">
         <is>
@@ -4411,7 +4413,7 @@
         </is>
       </c>
       <c r="W3" s="31" t="n">
-        <v>86.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="X3" s="31" t="inlineStr">
         <is>
@@ -4461,7 +4463,7 @@
         </is>
       </c>
       <c r="H4" s="31" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I4" s="31" t="inlineStr">
         <is>
@@ -4469,7 +4471,7 @@
         </is>
       </c>
       <c r="J4" s="31" t="n">
-        <v>77.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K4" s="31" t="inlineStr">
         <is>
@@ -4477,23 +4479,23 @@
         </is>
       </c>
       <c r="L4" s="31" t="n">
-        <v>81.2</v>
+        <v>82.3</v>
       </c>
       <c r="M4" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" s="31" t="n">
-        <v>97.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="O4" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P4" s="31" t="n">
-        <v>89.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="Q4" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="R4" s="31" t="n">
@@ -4508,7 +4510,7 @@
         </is>
       </c>
       <c r="U4" s="31" t="n">
-        <v>83.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="V4" s="31" t="inlineStr">
         <is>
@@ -4516,7 +4518,7 @@
         </is>
       </c>
       <c r="W4" s="31" t="n">
-        <v>84.7</v>
+        <v>85</v>
       </c>
       <c r="X4" s="31" t="inlineStr">
         <is>
@@ -4566,7 +4568,7 @@
         </is>
       </c>
       <c r="H5" s="31" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I5" s="31" t="inlineStr">
         <is>
@@ -4574,7 +4576,7 @@
         </is>
       </c>
       <c r="J5" s="31" t="n">
-        <v>77.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K5" s="31" t="inlineStr">
         <is>
@@ -4582,23 +4584,23 @@
         </is>
       </c>
       <c r="L5" s="31" t="n">
-        <v>82.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="M5" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" s="31" t="n">
-        <v>97.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="O5" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P5" s="31" t="n">
-        <v>89.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="Q5" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="R5" s="31" t="n">
@@ -4613,7 +4615,7 @@
         </is>
       </c>
       <c r="U5" s="31" t="n">
-        <v>86.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="V5" s="31" t="inlineStr">
         <is>
@@ -4621,7 +4623,7 @@
         </is>
       </c>
       <c r="W5" s="31" t="n">
-        <v>86.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="X5" s="31" t="inlineStr">
         <is>
@@ -4671,7 +4673,7 @@
         </is>
       </c>
       <c r="H6" s="31" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I6" s="31" t="inlineStr">
         <is>
@@ -4679,7 +4681,7 @@
         </is>
       </c>
       <c r="J6" s="31" t="n">
-        <v>82.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K6" s="31" t="inlineStr">
         <is>
@@ -4687,23 +4689,23 @@
         </is>
       </c>
       <c r="L6" s="31" t="n">
-        <v>81.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="M6" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" s="31" t="n">
-        <v>98.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="O6" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P6" s="31" t="n">
-        <v>89.8</v>
+        <v>90.8</v>
       </c>
       <c r="Q6" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="R6" s="31" t="n">
@@ -4718,7 +4720,7 @@
         </is>
       </c>
       <c r="U6" s="31" t="n">
-        <v>86.2</v>
+        <v>86.8</v>
       </c>
       <c r="V6" s="31" t="inlineStr">
         <is>
@@ -4726,7 +4728,7 @@
         </is>
       </c>
       <c r="W6" s="31" t="n">
-        <v>87.3</v>
+        <v>87.8</v>
       </c>
       <c r="X6" s="31" t="inlineStr">
         <is>
@@ -4776,7 +4778,7 @@
         </is>
       </c>
       <c r="H7" s="31" t="n">
-        <v>93.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I7" s="31" t="inlineStr">
         <is>
@@ -4784,7 +4786,7 @@
         </is>
       </c>
       <c r="J7" s="31" t="n">
-        <v>73</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="K7" s="31" t="inlineStr">
         <is>
@@ -4792,19 +4794,19 @@
         </is>
       </c>
       <c r="L7" s="31" t="n">
-        <v>82.3</v>
+        <v>83.5</v>
       </c>
       <c r="M7" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N7" s="31" t="n">
-        <v>99.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="O7" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P7" s="31" t="n">
-        <v>90.7</v>
+        <v>91.3</v>
       </c>
       <c r="Q7" s="31" t="inlineStr">
         <is>
@@ -4823,7 +4825,7 @@
         </is>
       </c>
       <c r="U7" s="31" t="n">
-        <v>86.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="V7" s="31" t="inlineStr">
         <is>
@@ -4831,7 +4833,7 @@
         </is>
       </c>
       <c r="W7" s="31" t="n">
-        <v>86.2</v>
+        <v>86.5</v>
       </c>
       <c r="X7" s="31" t="inlineStr">
         <is>
@@ -4881,7 +4883,7 @@
         </is>
       </c>
       <c r="H8" s="31" t="n">
-        <v>94.2</v>
+        <v>94.5</v>
       </c>
       <c r="I8" s="31" t="inlineStr">
         <is>
@@ -4889,7 +4891,7 @@
         </is>
       </c>
       <c r="J8" s="31" t="n">
-        <v>73.8</v>
+        <v>74.2</v>
       </c>
       <c r="K8" s="31" t="inlineStr">
         <is>
@@ -4897,19 +4899,19 @@
         </is>
       </c>
       <c r="L8" s="31" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="M8" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N8" s="31" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O8" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P8" s="31" t="n">
-        <v>90.8</v>
+        <v>91.3</v>
       </c>
       <c r="Q8" s="31" t="inlineStr">
         <is>
@@ -4928,7 +4930,7 @@
         </is>
       </c>
       <c r="U8" s="31" t="n">
-        <v>86.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="V8" s="31" t="inlineStr">
         <is>
@@ -4936,7 +4938,7 @@
         </is>
       </c>
       <c r="W8" s="31" t="n">
-        <v>86.7</v>
+        <v>87</v>
       </c>
       <c r="X8" s="31" t="inlineStr">
         <is>
@@ -4986,7 +4988,7 @@
         </is>
       </c>
       <c r="H9" s="31" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I9" s="31" t="inlineStr">
         <is>
@@ -4994,7 +4996,7 @@
         </is>
       </c>
       <c r="J9" s="31" t="n">
-        <v>68.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K9" s="31" t="inlineStr">
         <is>
@@ -5002,23 +5004,23 @@
         </is>
       </c>
       <c r="L9" s="31" t="n">
-        <v>82.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M9" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N9" s="31" t="n">
-        <v>95.7</v>
+        <v>96.3</v>
       </c>
       <c r="O9" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P9" s="31" t="n">
-        <v>89.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="Q9" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="R9" s="31" t="n">
@@ -5033,7 +5035,7 @@
         </is>
       </c>
       <c r="U9" s="31" t="n">
-        <v>85.09999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="V9" s="31" t="inlineStr">
         <is>
@@ -5041,7 +5043,7 @@
         </is>
       </c>
       <c r="W9" s="31" t="n">
-        <v>85.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="X9" s="31" t="inlineStr">
         <is>
@@ -5099,27 +5101,27 @@
         </is>
       </c>
       <c r="J10" s="31" t="n">
-        <v>78.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="K10" s="31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L10" s="31" t="n">
-        <v>81.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="M10" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N10" s="31" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="O10" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P10" s="31" t="n">
-        <v>90.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="Q10" s="31" t="inlineStr">
         <is>
@@ -5138,7 +5140,7 @@
         </is>
       </c>
       <c r="U10" s="31" t="n">
-        <v>86.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="V10" s="31" t="inlineStr">
         <is>
@@ -5146,7 +5148,7 @@
         </is>
       </c>
       <c r="W10" s="31" t="n">
-        <v>87.3</v>
+        <v>87.7</v>
       </c>
       <c r="X10" s="31" t="inlineStr">
         <is>
@@ -5196,7 +5198,7 @@
         </is>
       </c>
       <c r="H11" s="31" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I11" s="31" t="inlineStr">
         <is>
@@ -5204,7 +5206,7 @@
         </is>
       </c>
       <c r="J11" s="31" t="n">
-        <v>90.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K11" s="31" t="inlineStr">
         <is>
@@ -5212,19 +5214,19 @@
         </is>
       </c>
       <c r="L11" s="31" t="n">
-        <v>82.8</v>
+        <v>83.7</v>
       </c>
       <c r="M11" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N11" s="31" t="n">
-        <v>98.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O11" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P11" s="31" t="n">
-        <v>90.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="Q11" s="31" t="inlineStr">
         <is>
@@ -5243,7 +5245,7 @@
         </is>
       </c>
       <c r="U11" s="31" t="n">
-        <v>86.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="V11" s="31" t="inlineStr">
         <is>
@@ -5251,7 +5253,7 @@
         </is>
       </c>
       <c r="W11" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="X11" s="31" t="inlineStr">
         <is>
@@ -5301,7 +5303,7 @@
         </is>
       </c>
       <c r="H12" s="31" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="I12" s="31" t="inlineStr">
         <is>
@@ -5309,7 +5311,7 @@
         </is>
       </c>
       <c r="J12" s="31" t="n">
-        <v>67</v>
+        <v>67.8</v>
       </c>
       <c r="K12" s="31" t="inlineStr">
         <is>
@@ -5317,23 +5319,23 @@
         </is>
       </c>
       <c r="L12" s="31" t="n">
-        <v>82.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M12" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N12" s="31" t="n">
-        <v>97.40000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="O12" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P12" s="31" t="n">
-        <v>89.90000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="Q12" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="R12" s="31" t="n">
@@ -5348,7 +5350,7 @@
         </is>
       </c>
       <c r="U12" s="31" t="n">
-        <v>86.40000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="V12" s="31" t="inlineStr">
         <is>
@@ -5356,7 +5358,7 @@
         </is>
       </c>
       <c r="W12" s="31" t="n">
-        <v>86.5</v>
+        <v>87</v>
       </c>
       <c r="X12" s="31" t="inlineStr">
         <is>
@@ -5406,7 +5408,7 @@
         </is>
       </c>
       <c r="H13" s="31" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I13" s="31" t="inlineStr">
         <is>
@@ -5414,7 +5416,7 @@
         </is>
       </c>
       <c r="J13" s="31" t="n">
-        <v>70</v>
+        <v>70.8</v>
       </c>
       <c r="K13" s="31" t="inlineStr">
         <is>
@@ -5422,19 +5424,19 @@
         </is>
       </c>
       <c r="L13" s="31" t="n">
-        <v>73.3</v>
+        <v>75</v>
       </c>
       <c r="M13" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N13" s="31" t="n">
-        <v>94.5</v>
+        <v>95.3</v>
       </c>
       <c r="O13" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P13" s="31" t="n">
-        <v>83.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="Q13" s="31" t="inlineStr">
         <is>
@@ -5453,7 +5455,7 @@
         </is>
       </c>
       <c r="U13" s="31" t="n">
-        <v>82.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="V13" s="31" t="inlineStr">
         <is>
@@ -5461,7 +5463,7 @@
         </is>
       </c>
       <c r="W13" s="31" t="n">
-        <v>83</v>
+        <v>83.7</v>
       </c>
       <c r="X13" s="31" t="inlineStr">
         <is>
@@ -5511,15 +5513,15 @@
         </is>
       </c>
       <c r="H14" s="31" t="n">
-        <v>93.3</v>
+        <v>89</v>
       </c>
       <c r="I14" s="31" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J14" s="31" t="n">
-        <v>78.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="K14" s="31" t="inlineStr">
         <is>
@@ -5527,23 +5529,23 @@
         </is>
       </c>
       <c r="L14" s="31" t="n">
-        <v>82.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M14" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N14" s="31" t="n">
-        <v>82</v>
+        <v>70.3</v>
       </c>
       <c r="O14" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>82.2</v>
+        <v>72.2</v>
       </c>
       <c r="Q14" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="R14" s="31" t="n">
@@ -5558,24 +5560,24 @@
         </is>
       </c>
       <c r="U14" s="31" t="n">
-        <v>81.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="V14" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="W14" s="31" t="n">
-        <v>82.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="X14" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y14" s="31" t="inlineStr">
         <is>
-          <t>Deployable Candidates</t>
+          <t>Progressing Candidates</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5618,7 @@
         </is>
       </c>
       <c r="H15" s="31" t="n">
-        <v>93.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I15" s="31" t="inlineStr">
         <is>
@@ -5624,27 +5626,27 @@
         </is>
       </c>
       <c r="J15" s="31" t="n">
-        <v>68.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="K15" s="31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L15" s="31" t="n">
-        <v>82.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M15" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N15" s="31" t="n">
-        <v>95.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O15" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>88.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="Q15" s="31" t="inlineStr">
         <is>
@@ -5663,7 +5665,7 @@
         </is>
       </c>
       <c r="U15" s="31" t="n">
-        <v>85.2</v>
+        <v>85.8</v>
       </c>
       <c r="V15" s="31" t="inlineStr">
         <is>
@@ -5671,7 +5673,7 @@
         </is>
       </c>
       <c r="W15" s="31" t="n">
-        <v>85.2</v>
+        <v>85.8</v>
       </c>
       <c r="X15" s="31" t="inlineStr">
         <is>
@@ -5729,7 +5731,7 @@
         </is>
       </c>
       <c r="J16" s="31" t="n">
-        <v>86.19999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="K16" s="31" t="inlineStr">
         <is>
@@ -5737,19 +5739,19 @@
         </is>
       </c>
       <c r="L16" s="31" t="n">
-        <v>82</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M16" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N16" s="31" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="O16" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P16" s="31" t="n">
-        <v>90.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="Q16" s="31" t="inlineStr">
         <is>
@@ -5768,7 +5770,7 @@
         </is>
       </c>
       <c r="U16" s="31" t="n">
-        <v>85.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="V16" s="31" t="inlineStr">
         <is>
@@ -5776,7 +5778,7 @@
         </is>
       </c>
       <c r="W16" s="31" t="n">
-        <v>87.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="X16" s="31" t="inlineStr">
         <is>
@@ -5826,7 +5828,7 @@
         </is>
       </c>
       <c r="H17" s="31" t="n">
-        <v>91.3</v>
+        <v>91.7</v>
       </c>
       <c r="I17" s="31" t="inlineStr">
         <is>
@@ -5834,27 +5836,27 @@
         </is>
       </c>
       <c r="J17" s="31" t="n">
-        <v>69.2</v>
+        <v>71.39999999999999</v>
       </c>
       <c r="K17" s="31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L17" s="31" t="n">
-        <v>73.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M17" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N17" s="31" t="n">
-        <v>97.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O17" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P17" s="31" t="n">
-        <v>85.3</v>
+        <v>85.8</v>
       </c>
       <c r="Q17" s="31" t="inlineStr">
         <is>
@@ -5873,7 +5875,7 @@
         </is>
       </c>
       <c r="U17" s="31" t="n">
-        <v>83.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="V17" s="31" t="inlineStr">
         <is>
@@ -5881,7 +5883,7 @@
         </is>
       </c>
       <c r="W17" s="31" t="n">
-        <v>83.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="X17" s="31" t="inlineStr">
         <is>
@@ -5931,7 +5933,7 @@
         </is>
       </c>
       <c r="H18" s="31" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="I18" s="31" t="inlineStr">
         <is>
@@ -5939,7 +5941,7 @@
         </is>
       </c>
       <c r="J18" s="31" t="n">
-        <v>85.39999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K18" s="31" t="inlineStr">
         <is>
@@ -5947,19 +5949,19 @@
         </is>
       </c>
       <c r="L18" s="31" t="n">
-        <v>82.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M18" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N18" s="31" t="n">
-        <v>98.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="O18" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P18" s="31" t="n">
-        <v>90.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="Q18" s="31" t="inlineStr">
         <is>
@@ -5978,7 +5980,7 @@
         </is>
       </c>
       <c r="U18" s="31" t="n">
-        <v>86.3</v>
+        <v>86.8</v>
       </c>
       <c r="V18" s="31" t="inlineStr">
         <is>
@@ -5986,7 +5988,7 @@
         </is>
       </c>
       <c r="W18" s="31" t="n">
-        <v>87.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X18" s="31" t="inlineStr">
         <is>
@@ -6036,7 +6038,7 @@
         </is>
       </c>
       <c r="H19" s="31" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="I19" s="31" t="inlineStr">
         <is>
@@ -6044,7 +6046,7 @@
         </is>
       </c>
       <c r="J19" s="31" t="n">
-        <v>68.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K19" s="31" t="inlineStr">
         <is>
@@ -6052,19 +6054,19 @@
         </is>
       </c>
       <c r="L19" s="31" t="n">
-        <v>73.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="M19" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N19" s="31" t="n">
-        <v>97</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O19" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P19" s="31" t="n">
-        <v>85</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Q19" s="31" t="inlineStr">
         <is>
@@ -6083,7 +6085,7 @@
         </is>
       </c>
       <c r="U19" s="31" t="n">
-        <v>82.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="V19" s="31" t="inlineStr">
         <is>
@@ -6091,7 +6093,7 @@
         </is>
       </c>
       <c r="W19" s="31" t="n">
-        <v>83.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="X19" s="31" t="inlineStr">
         <is>
@@ -6141,7 +6143,7 @@
         </is>
       </c>
       <c r="H20" s="31" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I20" s="31" t="inlineStr">
         <is>
@@ -6149,7 +6151,7 @@
         </is>
       </c>
       <c r="J20" s="31" t="n">
-        <v>80.8</v>
+        <v>82.2</v>
       </c>
       <c r="K20" s="31" t="inlineStr">
         <is>
@@ -6157,19 +6159,19 @@
         </is>
       </c>
       <c r="L20" s="31" t="n">
-        <v>81.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="M20" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N20" s="31" t="n">
-        <v>96.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O20" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P20" s="31" t="n">
-        <v>89</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="Q20" s="31" t="inlineStr">
         <is>
@@ -6188,7 +6190,7 @@
         </is>
       </c>
       <c r="U20" s="31" t="n">
-        <v>85.3</v>
+        <v>85.8</v>
       </c>
       <c r="V20" s="31" t="inlineStr">
         <is>
@@ -6196,7 +6198,7 @@
         </is>
       </c>
       <c r="W20" s="31" t="n">
-        <v>86.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="X20" s="31" t="inlineStr">
         <is>
@@ -6246,7 +6248,7 @@
         </is>
       </c>
       <c r="H21" s="31" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I21" s="31" t="inlineStr">
         <is>
@@ -6254,7 +6256,7 @@
         </is>
       </c>
       <c r="J21" s="31" t="n">
-        <v>83</v>
+        <v>84.2</v>
       </c>
       <c r="K21" s="31" t="inlineStr">
         <is>
@@ -6262,23 +6264,23 @@
         </is>
       </c>
       <c r="L21" s="31" t="n">
-        <v>81.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="M21" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N21" s="31" t="n">
-        <v>97.3</v>
+        <v>97.7</v>
       </c>
       <c r="O21" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P21" s="31" t="n">
-        <v>89.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="Q21" s="31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="R21" s="31" t="n">
@@ -6293,7 +6295,7 @@
         </is>
       </c>
       <c r="U21" s="31" t="n">
-        <v>85.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="V21" s="31" t="inlineStr">
         <is>
@@ -6301,7 +6303,7 @@
         </is>
       </c>
       <c r="W21" s="31" t="n">
-        <v>86.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="X21" s="31" t="inlineStr">
         <is>
@@ -6351,7 +6353,7 @@
         </is>
       </c>
       <c r="H22" s="31" t="n">
-        <v>94.2</v>
+        <v>94.5</v>
       </c>
       <c r="I22" s="31" t="inlineStr">
         <is>
@@ -6359,7 +6361,7 @@
         </is>
       </c>
       <c r="J22" s="31" t="n">
-        <v>65.40000000000001</v>
+        <v>66.39999999999999</v>
       </c>
       <c r="K22" s="31" t="inlineStr">
         <is>
@@ -6367,19 +6369,19 @@
         </is>
       </c>
       <c r="L22" s="31" t="n">
-        <v>82.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="M22" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N22" s="31" t="n">
-        <v>98.09999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O22" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P22" s="31" t="n">
-        <v>90.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q22" s="31" t="inlineStr">
         <is>
@@ -6398,7 +6400,7 @@
         </is>
       </c>
       <c r="U22" s="31" t="n">
-        <v>86</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="V22" s="31" t="inlineStr">
         <is>
@@ -6406,7 +6408,7 @@
         </is>
       </c>
       <c r="W22" s="31" t="n">
-        <v>85.8</v>
+        <v>86.2</v>
       </c>
       <c r="X22" s="31" t="inlineStr">
         <is>
@@ -6475,7 +6477,7 @@
         <v>96.2</v>
       </c>
       <c r="D2" s="31" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
   </sheetData>
